--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -83,8 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.18</v>
+        <v>0.165</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4791200</v>
+        <v>35242600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>64.31999999999999</v>
+        <v>21.75</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.16</v>
+        <v>0.239</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.124</v>
+        <v>0.449</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.275</v>
+        <v>0.175</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0185</v>
+        <v>-0.0278</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4312100</v>
+        <v>18224500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>66.65000000000001</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+        <v>61.42</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.243</v>
+        <v>0.16</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.234</v>
+        <v>0.124</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-0.0267</v>
+        <v>0.135</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2567800</v>
+        <v>15822600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.06</v>
+        <v>6.18</v>
       </c>
       <c r="H4" t="n">
-        <v>66.84</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+        <v>79.41</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.339</v>
+        <v>0.096</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.209</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.785</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.068</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1483700</v>
+        <v>12642700</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="n">
-        <v>37.86</v>
+        <v>61.68</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.266</v>
+        <v>0.741</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.317</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>610200</v>
+        <v>11820000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
-        <v>60.57</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>69.36</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.896</v>
+        <v>0.244</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.855</v>
+        <v>0.234</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>550000</v>
+        <v>9776200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.635</v>
+        <v>0.476</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.601</v>
+        <v>0.473</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,45 +813,2776 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.375</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>506400</v>
+        <v>7568600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="H8" t="n">
-        <v>56.84</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.16</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.748</v>
+        <v>0.34</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.574</v>
+        <v>0.209</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7346700</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0163</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAREPLS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6883200</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5096200</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3984100</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3925400</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H13" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SYSTECH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3795600</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HHRG</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3763200</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H15" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3675800</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3535700</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H17" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0095</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3249700</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3238100</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H20" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3179300</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H21" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>3.621</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2690200</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2679800</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H23" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2436100</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2382500</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2380700</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H26" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2109100</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H27" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2094900</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H28" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2002800</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H29" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0475</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0475.KL</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1930400</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1812300</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H31" t="n">
+        <v>61.11</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1766200</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1747000</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H33" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1720200</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>2.277</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1698600</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H35" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1596400</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1292300</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1235300</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1198300</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H39" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1143900</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1133400</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H41" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1121100</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H42" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1076200</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H43" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H44" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1053100</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H45" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>WCT</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1025200</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H46" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1016400</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H47" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>2.199</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>965100</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H48" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>6.739</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>6.579</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>961400</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H49" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>960800</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>904900</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>2.666</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>878100</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H52" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.04389999999999999</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>873500</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H53" t="n">
+        <v>82.41</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>856400</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H54" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>778900</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H55" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>727500</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H56" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>727200</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H57" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>726000</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H58" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>713800</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H59" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4.865</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>4.581</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>712200</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H60" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>677300</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>622500</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H62" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>614300</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H63" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H64" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>593800</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H65" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.718</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>585600</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>5.631</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>5.741</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>571700</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>13.102</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>554100</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H68" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H69" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
-    </font>
-    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,9 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.0278</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>35242600</v>
+        <v>37493200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H2" t="n">
-        <v>21.75</v>
+        <v>61.42</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.239</v>
+        <v>0.16</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.449</v>
+        <v>0.124</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.175</v>
+        <v>0.165</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0278</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>18224500</v>
+        <v>36159400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="H3" t="n">
-        <v>61.42</v>
+        <v>21.75</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.16</v>
+        <v>0.239</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.124</v>
+        <v>0.449</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.135</v>
+        <v>0.28</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.08</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15822600</v>
+        <v>21511500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6.18</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>68.06</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.096</v>
+        <v>0.244</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.234</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.068</v>
+        <v>0.375</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>12642700</v>
+        <v>19628700</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H5" t="n">
-        <v>61.68</v>
+        <v>71.16</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.741</v>
+        <v>0.34</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.285</v>
+        <v>0.13</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0556</v>
+        <v>0.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11820000</v>
+        <v>19257800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.33</v>
+        <v>7.52</v>
       </c>
       <c r="H6" t="n">
-        <v>69.36</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>77.94</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.244</v>
+        <v>0.096</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.234</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.51</v>
+        <v>0.79</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9776200</v>
+        <v>16706000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H7" t="n">
-        <v>64.04000000000001</v>
+        <v>62.44</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.476</v>
+        <v>0.741</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.473</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7568600</v>
+        <v>11246600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.18</v>
+        <v>0.46</v>
       </c>
       <c r="H8" t="n">
-        <v>71.16</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.34</v>
+        <v>0.476</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.209</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.425</v>
+        <v>0.59</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7346700</v>
+        <v>10779400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>63.2</v>
+        <v>63.72</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.389</v>
+        <v>0.54</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.331</v>
+        <v>0.493</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.425</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0.0625</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6883200</v>
+        <v>8210000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.74</v>
+        <v>0.38</v>
       </c>
       <c r="H10" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+        <v>63.2</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.081</v>
+        <v>0.389</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.077</v>
+        <v>0.331</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,33 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.26</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0625</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5096200</v>
+        <v>7833400</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
+      </c>
+      <c r="H11" t="n">
+        <v>57.03</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.077</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.83</v>
+        <v>0.265</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.0392</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3984100</v>
+        <v>6042000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H12" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>0.45</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.698</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,39 +1031,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.395</v>
+        <v>0.075</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3925400</v>
+        <v>5928400</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.35</v>
+        <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+        <v>47.39</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.406</v>
+        <v>0.076</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.411</v>
+        <v>0.078</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.195</v>
+        <v>0.825</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.1143</v>
+        <v>0.0248</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3795600</v>
+        <v>5395800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="H14" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.165</v>
+        <v>0.743</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.165</v>
+        <v>0.698</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3763200</v>
+        <v>4615600</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>54.4</v>
+        <v>28.59</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.159</v>
+        <v>0.594</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.148</v>
+        <v>0.804</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0154</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3675800</v>
+        <v>4147100</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="H16" t="n">
-        <v>29.72</v>
+        <v>53.89</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.595</v>
+        <v>0.32</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.804</v>
+        <v>0.337</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0154</v>
+        <v>0.165</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3535700</v>
+        <v>3991700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.66</v>
+        <v>0.1</v>
       </c>
       <c r="H17" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+        <v>54.4</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.32</v>
+        <v>0.159</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.337</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0313</v>
+        <v>0.19</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3450000</v>
+        <v>3968100</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="H18" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
+        <v>67.62</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.156</v>
+        <v>0.165</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.158</v>
+        <v>0.165</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.395</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3249700</v>
+        <v>3926400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>75.12</v>
+        <v>38.65</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.406</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.496</v>
+        <v>0.411</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.575</v>
+        <v>0.245</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0208</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3238100</v>
+        <v>3603000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="H20" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+        <v>35.11</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.538</v>
+        <v>0.265</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.493</v>
+        <v>0.317</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1400,30 +1400,30 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0302</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3179300</v>
+        <v>3582800</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>58.48</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
+        <v>57.65</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.621</v>
+        <v>3.616</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.544</v>
+        <v>2.543</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2690200</v>
+        <v>3450000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H22" t="n">
-        <v>52.67</v>
+        <v>46.33</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.07</v>
+        <v>0.156</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.027</v>
+        <v>0.158</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,40 +1481,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.11</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2679800</v>
+        <v>3412400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H23" t="n">
-        <v>71.3</v>
+        <v>0.11</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0.272</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1526,39 +1519,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2436100</v>
+        <v>3346200</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>30.64</v>
+        <v>63.57</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.546</v>
+        <v>0.282</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.582</v>
+        <v>0.272</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1582,19 +1575,19 @@
       <c r="D25" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2382500</v>
+        <v>3287700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H25" t="n">
         <v>51.26</v>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1616,39 +1609,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.245</v>
+        <v>0.61</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2380700</v>
+        <v>3265700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H26" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
+        <v>75.12</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.265</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.317</v>
+        <v>0.496</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1654,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.78</v>
+        <v>1.82</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0282</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2109100</v>
+        <v>3185300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H27" t="n">
-        <v>52.97</v>
+        <v>59.78</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.774</v>
+        <v>1.752</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.775</v>
+        <v>1.575</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2094900</v>
+        <v>3110000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="H28" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
+        <v>52.67</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.157</v>
+        <v>1.07</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.108</v>
+        <v>1.027</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.8</v>
+        <v>0.78</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2002800</v>
+        <v>2649100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="H29" t="n">
-        <v>58.36</v>
+        <v>52.97</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.75</v>
+        <v>0.774</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1.575</v>
+        <v>0.775</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,33 +1789,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.21</v>
+        <v>0.515</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.0198</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1930400</v>
+        <v>2467200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
+        <v>0.39</v>
+      </c>
+      <c r="H30" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.582</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
     </row>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.39</v>
+        <v>1.18</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.013</v>
+        <v>0.0351</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1812300</v>
+        <v>2336400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
-        <v>61.11</v>
+        <v>54.88</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.378</v>
+        <v>1.157</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.372</v>
+        <v>1.108</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0382</v>
+        <v>0.026</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1766200</v>
+        <v>2307300</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H32" t="n">
-        <v>77.39</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
+        <v>63.81</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.71</v>
+        <v>0.378</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.637</v>
+        <v>0.372</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,39 +1924,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.735</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.0138</v>
+        <v>0.0382</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1747000</v>
+        <v>2283200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H33" t="n">
-        <v>33.42</v>
+        <v>77.39</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.777</v>
+        <v>0.71</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.834</v>
+        <v>0.637</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,39 +1969,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.25</v>
+        <v>0.355</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>-0.0044</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1720200</v>
+        <v>2281700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H34" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
+        <v>62.52</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.277</v>
+        <v>0.336</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2.207</v>
+        <v>0.317</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,40 +2014,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1698600</v>
+        <v>2259500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="H35" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>0.265</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
     </row>
@@ -2074,15 +2067,15 @@
         <v>0.0377</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1596400</v>
+        <v>2150100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H36" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2104,39 +2097,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.02</v>
+        <v>2.25</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1292300</v>
+        <v>1821500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H37" t="n">
-        <v>63.2</v>
+        <v>48.43</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.236</v>
+        <v>2.277</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.212</v>
+        <v>2.207</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2142,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.0069</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1235300</v>
+        <v>1812700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="H38" t="n">
-        <v>64.22</v>
+        <v>31.5</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.337</v>
+        <v>0.777</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.317</v>
+        <v>0.834</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,39 +2187,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0484</v>
+        <v>0.26</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1198300</v>
+        <v>1698600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.15</v>
+        <v>2.01</v>
       </c>
       <c r="H39" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
+        <v>45.51</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.467</v>
+        <v>0.261</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.504</v>
+        <v>0.265</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,39 +2232,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1143900</v>
+        <v>1655700</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="H40" t="n">
-        <v>49.23</v>
+        <v>50.19</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.295</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.296</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,39 +2277,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.0388</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1133400</v>
+        <v>1522400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H41" t="n">
-        <v>52.92</v>
+        <v>60.11</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.367</v>
+        <v>0.639</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.367</v>
+        <v>0.586</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,39 +2322,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1121100</v>
+        <v>1475700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="H42" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
+        <v>52.92</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.196</v>
+        <v>0.367</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.18</v>
+        <v>0.367</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,39 +2367,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.64</v>
+        <v>4.32</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1076200</v>
+        <v>1419600</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="H43" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
+        <v>44.63</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.635</v>
+        <v>4.467</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.601</v>
+        <v>4.504</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,39 +2412,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0186</v>
+        <v>0.54</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1062500</v>
+        <v>1419000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="n">
-        <v>49.68</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.806</v>
+        <v>0.437</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.736</v>
+        <v>0.418</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2457,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.865</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1053100</v>
+        <v>1400000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>45.4</v>
+        <v>47.02</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.256</v>
+        <v>0.868</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.296</v>
+        <v>0.87</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,39 +2502,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.0435</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1025200</v>
+        <v>1365700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="H46" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.371</v>
+        <v>0.222</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.388</v>
+        <v>0.193</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,39 +2547,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>-0.0109</v>
+        <v>0.26</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.04</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1016400</v>
+        <v>1359100</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>76.67</v>
+        <v>64.91</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.554</v>
+        <v>0.236</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.199</v>
+        <v>0.213</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,39 +2592,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.8</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>965100</v>
+        <v>1357400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="H48" t="n">
-        <v>64.69</v>
+        <v>51.99</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6.739</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>6.579</v>
+        <v>0.737</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,39 +2637,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>961400</v>
+        <v>1318600</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H49" t="n">
-        <v>64.37</v>
+        <v>44.45</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.757</v>
+        <v>0.771</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2689,39 +2682,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.765</v>
+        <v>0.605</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.0614</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>960800</v>
+        <v>1219400</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.15</v>
+        <v>1.59</v>
       </c>
       <c r="H50" t="n">
-        <v>47.53</v>
+        <v>84.13</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.769</v>
+        <v>0.544</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.771</v>
+        <v>0.531</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2743,30 +2736,30 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0036</v>
+        <v>2.83</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>904900</v>
+        <v>1211800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H51" t="n">
-        <v>53.83</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
+        <v>56.71</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.794</v>
+        <v>2.797</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.666</v>
+        <v>2.667</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2779,39 +2772,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0155</v>
+        <v>0.2</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>878100</v>
+        <v>1171100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H52" t="n">
-        <v>57.27</v>
+        <v>56.71</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.637</v>
+        <v>0.196</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.586</v>
+        <v>0.18</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2824,39 +2817,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>873500</v>
+        <v>1143900</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H53" t="n">
-        <v>82.41</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+        <v>49.23</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.543</v>
+        <v>0.295</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.531</v>
+        <v>0.296</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2869,39 +2862,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E54" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>856400</v>
+        <v>1140400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.895</v>
+        <v>0.772</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.855</v>
+        <v>0.757</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2914,39 +2907,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0327</v>
+        <v>2.71</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>778900</v>
+        <v>1139600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H55" t="n">
-        <v>51.3</v>
+        <v>75.14</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.207</v>
+        <v>2.553</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.113</v>
+        <v>2.198</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2959,39 +2952,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.1</v>
+        <v>0.64</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>727500</v>
+        <v>1081600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.11</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
+        <v>59.82</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.156</v>
+        <v>0.635</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.154</v>
+        <v>0.601</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3004,39 +2997,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.0138</v>
+        <v>1.23</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>727200</v>
+        <v>1076600</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H57" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
+        <v>43.49</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.466</v>
+        <v>1.255</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.47</v>
+        <v>1.295</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3049,39 +3042,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.1</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>726000</v>
+        <v>1073900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H58" t="n">
-        <v>47.02</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.868</v>
+        <v>1.032</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.87</v>
+        <v>0.876</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3094,39 +3087,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5.14</v>
+        <v>1.1</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0092</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>713800</v>
+        <v>1069400</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="H59" t="n">
-        <v>71.48999999999999</v>
+        <v>41.4</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.865</v>
+        <v>1.156</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.581</v>
+        <v>1.154</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3139,39 +3132,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.3</v>
+        <v>7.23</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0183</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>712200</v>
+        <v>1053300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H60" t="n">
-        <v>44.54</v>
+        <v>64.69</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.35</v>
+        <v>6.739</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.3</v>
+        <v>6.579</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3184,39 +3177,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.67</v>
+        <v>0.36</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0141</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>677300</v>
+        <v>1045000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="H61" t="n">
-        <v>48.44</v>
+        <v>39.92</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.678</v>
+        <v>0.371</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.667</v>
+        <v>0.388</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3229,39 +3222,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.85</v>
+        <v>0.36</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0035</v>
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>622500</v>
+        <v>1038600</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H62" t="n">
-        <v>71.64</v>
+        <v>68.02</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.444</v>
+        <v>0.336</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.887</v>
+        <v>0.314</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3274,39 +3267,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3.48</v>
+        <v>0.47</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0235</v>
+        <v>0.0217</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>614300</v>
+        <v>1001400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>41.66</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
+        <v>56.91</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3.557</v>
+        <v>0.452</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3.685</v>
+        <v>0.417</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3319,39 +3312,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.17</v>
+        <v>5.14</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.0039</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>607700</v>
+        <v>955600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H64" t="n">
-        <v>72.72</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.986</v>
+        <v>4.865</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.775</v>
+        <v>4.581</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3364,39 +3357,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0138</v>
+        <v>0.67</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>593800</v>
+        <v>922300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.06</v>
+        <v>0.76</v>
       </c>
       <c r="H65" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
+        <v>63.59</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.718</v>
+        <v>0.633</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.545</v>
+        <v>0.606</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3409,39 +3402,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>5.36</v>
+        <v>1.31</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.019</v>
+        <v>0.0155</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>585600</v>
+        <v>920900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H66" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
+        <v>45.82</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5.631</v>
+        <v>1.351</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>5.741</v>
+        <v>1.3</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3454,39 +3447,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.0016</v>
+        <v>1.45</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>571700</v>
+        <v>920900</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>37.98</v>
+        <v>43.47</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13.102</v>
+        <v>1.468</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>13.69</v>
+        <v>1.47</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3499,39 +3492,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>554100</v>
+        <v>894400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H68" t="n">
-        <v>61.25</v>
+        <v>51.95</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.632</v>
+        <v>2.208</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.606</v>
+        <v>2.114</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3544,45 +3537,945 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>500000</v>
+        <v>888400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.49</v>
+        <v>0.06</v>
       </c>
       <c r="H69" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
+        <v>54.66</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.629</v>
+        <v>2.446</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.636</v>
+        <v>2.312</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>856700</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H70" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>856400</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H71" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>838700</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H72" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>810900</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H73" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>804400</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H74" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>5.628</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>770800</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H75" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>769200</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H76" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>741800</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H77" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>701500</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H78" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>5.687</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>698600</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H79" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>13.106</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>13.691</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>691900</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H80" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>10.112</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>10.268</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>684000</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H81" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>670900</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H82" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>647500</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H83" t="n">
+        <v>63.03</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>549400</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H84" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>7.813</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>537200</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H85" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>528800</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H86" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>518200</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H87" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>515100</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H88" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>7.787</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H89" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M69"/>
+  <autoFilter ref="A1:M89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="3">
@@ -83,7 +83,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0278</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>37493200</v>
+        <v>39094200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H2" t="n">
-        <v>61.42</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>-0.0303</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>36159400</v>
+        <v>37075500</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0.08</v>
       </c>
       <c r="H3" t="n">
-        <v>21.75</v>
+        <v>21.26</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.449</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.375</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>21511500</v>
+        <v>23354200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
-        <v>68.06</v>
+        <v>71.16</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.244</v>
+        <v>0.34</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.234</v>
+        <v>0.209</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>19628700</v>
+        <v>22450100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="H5" t="n">
-        <v>71.16</v>
+        <v>69.36</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.244</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.209</v>
+        <v>0.234</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19257800</v>
+        <v>21005300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>7.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>77.94</v>
+        <v>79.41</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.79</v>
+        <v>0.605</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0901</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>16706000</v>
+        <v>19275300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.37</v>
+        <v>1.23</v>
       </c>
       <c r="H7" t="n">
-        <v>62.44</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.87</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.741</v>
+        <v>0.541</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.493</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.51</v>
+        <v>0.785</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.068</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11246600</v>
+        <v>17898100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.68</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.476</v>
+        <v>0.741</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.473</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10779400</v>
+        <v>11998600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H9" t="n">
-        <v>63.72</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.54</v>
+        <v>0.476</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.493</v>
+        <v>0.473</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.155</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8210000</v>
+        <v>11570000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.389</v>
+        <v>0.156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.331</v>
+        <v>0.158</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,28 +948,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7833400</v>
+        <v>8657100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="n">
-        <v>57.03</v>
+        <v>62.22</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.081</v>
+        <v>0.388</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.077</v>
+        <v>0.331</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,33 +993,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.265</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0392</v>
+        <v>0.0625</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6042000</v>
+        <v>7865400</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+        <v>0.85</v>
+      </c>
+      <c r="H12" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.077</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,40 +1038,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5928400</v>
+        <v>6615700</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.078</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.075</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5395800</v>
+        <v>5929400</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.48</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.39</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.743</v>
+        <v>0.076</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.698</v>
+        <v>0.078</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.515</v>
+        <v>0.83</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.0311</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4615600</v>
+        <v>5785400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="H15" t="n">
-        <v>28.59</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.28</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.594</v>
+        <v>0.743</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.804</v>
+        <v>0.698</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1175,19 +1175,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0154</v>
+        <v>0.0308</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4147100</v>
+        <v>5585300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="H16" t="n">
-        <v>53.89</v>
+        <v>56.04</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0.337</v>
@@ -1211,28 +1211,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E17" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3991700</v>
+        <v>5171700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
       <c r="H17" t="n">
-        <v>54.4</v>
+        <v>68.89</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.159</v>
+        <v>0.282</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.148</v>
+        <v>0.272</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.0196</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3968100</v>
+        <v>4744600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="H18" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.72</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.165</v>
+        <v>0.595</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.165</v>
+        <v>0.804</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.0125</v>
+        <v>1.82</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3926400</v>
+        <v>4194100</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="H19" t="n">
-        <v>38.65</v>
+        <v>59.78</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.406</v>
+        <v>1.752</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.411</v>
+        <v>1.575</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.245</v>
+        <v>0.195</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.1143</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3603000</v>
+        <v>4102700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>35.11</v>
+        <v>69.47</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.265</v>
+        <v>0.165</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.317</v>
+        <v>0.165</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0302</v>
+        <v>0.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3582800</v>
+        <v>4037400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="H21" t="n">
-        <v>57.65</v>
+        <v>56.71</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.616</v>
+        <v>0.196</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.543</v>
+        <v>0.18</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0313</v>
+        <v>0.16</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3450000</v>
+        <v>4018400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H22" t="n">
-        <v>46.33</v>
+        <v>51.88</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.158</v>
+        <v>0.147</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,33 +1481,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.11</v>
+        <v>0.395</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0</v>
+        <v>-0.0125</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3412400</v>
+        <v>3949000</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
+      </c>
+      <c r="H23" t="n">
+        <v>38.65</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+      <c r="J23" s="2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.411</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1519,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0167</v>
+        <v>3.78</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3346200</v>
+        <v>3896800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="H24" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.15</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.282</v>
+        <v>3.619</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.272</v>
+        <v>2.544</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1564,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3287700</v>
+        <v>3711500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H25" t="n">
-        <v>51.26</v>
+        <v>35.11</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1593,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.607</v>
+        <v>0.265</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.607</v>
+        <v>0.317</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,28 +1616,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3265700</v>
+        <v>3677000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="H26" t="n">
-        <v>75.12</v>
+        <v>52.97</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1638,10 +1645,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.496</v>
+        <v>0.775</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0282</v>
+        <v>0.61</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3185300</v>
+        <v>3548400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.26</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.752</v>
+        <v>0.607</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.575</v>
+        <v>0.607</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,40 +1706,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.08</v>
+        <v>0.115</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3110000</v>
+        <v>3455400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H28" t="n">
-        <v>52.67</v>
+        <v>0.12</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>1.027</v>
-      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2649100</v>
+        <v>3267700</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H29" t="n">
-        <v>52.97</v>
+        <v>75.12</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.774</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.775</v>
+        <v>0.496</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.515</v>
+        <v>1.08</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.0198</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2467200</v>
+        <v>3183800</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="H30" t="n">
-        <v>33.36</v>
+        <v>52.67</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.546</v>
+        <v>1.07</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.582</v>
+        <v>1.027</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,28 +1834,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.13</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2336400</v>
+        <v>3167700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="H31" t="n">
-        <v>54.88</v>
+        <v>35.71</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.157</v>
+        <v>0.142</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.108</v>
+        <v>0.15</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.395</v>
+        <v>0.51</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.026</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2307300</v>
+        <v>3041500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.21</v>
+        <v>0.48</v>
       </c>
       <c r="H32" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.64</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.378</v>
+        <v>0.546</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.372</v>
+        <v>0.582</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1933,19 +1933,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.0382</v>
+        <v>0.0255</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2283200</v>
+        <v>2915500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="H33" t="n">
-        <v>77.39</v>
+        <v>76.41</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.637</v>
+        <v>0.636</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.026</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2281700</v>
+        <v>2835900</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H34" t="n">
-        <v>62.52</v>
+        <v>63.81</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.336</v>
+        <v>0.378</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.317</v>
+        <v>0.372</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,33 +2014,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0244</v>
+        <v>2.23</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2259500</v>
+        <v>2480200</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
+        <v>0.16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>2.206</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
     </row>
@@ -2052,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.55</v>
+        <v>1.18</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.0377</v>
+        <v>0.0351</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2150100</v>
+        <v>2420200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H36" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5</v>
+        <v>1.157</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.419</v>
+        <v>1.108</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2097,28 +2104,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-0.0044</v>
+        <v>0.545</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1821500</v>
+        <v>2388000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.12</v>
+        <v>0.85</v>
       </c>
       <c r="H37" t="n">
-        <v>48.43</v>
+        <v>80.28</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2126,10 +2133,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.277</v>
+        <v>0.437</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2.207</v>
+        <v>0.418</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2142,40 +2149,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.73</v>
+        <v>0.215</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.0488</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1812700</v>
+        <v>2372000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H38" t="n">
-        <v>31.5</v>
+        <v>0.03</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0.834</v>
-      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2187,39 +2187,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1698600</v>
+        <v>2311100</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.01</v>
+        <v>0.15</v>
       </c>
       <c r="H39" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.64</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.261</v>
+        <v>0.499</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.265</v>
+        <v>0.418</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2232,39 +2232,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E40" s="8" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1655700</v>
+        <v>2284200</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.336</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2277,39 +2277,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.0388</v>
+        <v>0.0137</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1522400</v>
+        <v>2192400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="H41" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.92</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.639</v>
+        <v>0.367</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.586</v>
+        <v>0.367</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2322,39 +2322,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.0388</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1475700</v>
+        <v>2181700</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.22</v>
       </c>
       <c r="H42" t="n">
-        <v>52.92</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.11</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.367</v>
+        <v>0.639</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.367</v>
+        <v>0.586</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2367,28 +2367,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4.32</v>
+        <v>0.255</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.046</v>
+        <v>0.02</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1419600</v>
+        <v>1933800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="H43" t="n">
-        <v>44.63</v>
+        <v>63.2</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.467</v>
+        <v>0.236</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.504</v>
+        <v>0.212</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2412,39 +2412,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.54</v>
+        <v>1.65</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.0385</v>
+        <v>0.0185</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1419000</v>
+        <v>1923300</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="H44" t="n">
-        <v>79.79000000000001</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.86</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.437</v>
+        <v>1.701</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.418</v>
+        <v>1.818</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2457,39 +2457,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.805</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1400000</v>
+        <v>1887700</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H45" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.868</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.87</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2502,28 +2502,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.0297</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1365700</v>
+        <v>1840500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.9</v>
+        <v>0.29</v>
       </c>
       <c r="H46" t="n">
-        <v>65.26000000000001</v>
+        <v>49.36</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.222</v>
+        <v>0.521</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.193</v>
+        <v>0.532</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2547,28 +2547,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.26</v>
+        <v>0.73</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.04</v>
+        <v>0.0069</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1359100</v>
+        <v>1824500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H47" t="n">
-        <v>64.91</v>
+        <v>31.5</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.236</v>
+        <v>0.777</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.213</v>
+        <v>0.834</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2592,28 +2592,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.0062</v>
+        <v>0.76</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1357400</v>
+        <v>1784400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="H48" t="n">
-        <v>51.99</v>
+        <v>44.45</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.737</v>
+        <v>0.771</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2637,28 +2637,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.285</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1318600</v>
+        <v>1728000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H49" t="n">
-        <v>44.45</v>
+        <v>35.15</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.769</v>
+        <v>0.294</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.771</v>
+        <v>0.31</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2682,28 +2682,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0614</v>
+        <v>0.865</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1219400</v>
+        <v>1701200</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.59</v>
+        <v>0.09</v>
       </c>
       <c r="H50" t="n">
-        <v>84.13</v>
+        <v>47.02</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.544</v>
+        <v>0.868</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.531</v>
+        <v>0.87</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2727,39 +2727,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0071</v>
+        <v>0.26</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1211800</v>
+        <v>1698600</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.08</v>
+        <v>2.01</v>
       </c>
       <c r="H51" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.797</v>
+        <v>0.261</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.667</v>
+        <v>0.265</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,39 +2772,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1171100</v>
+        <v>1677500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.05</v>
+        <v>0.41</v>
       </c>
       <c r="H52" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.6</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.196</v>
+        <v>0.519</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.18</v>
+        <v>0.476</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1143900</v>
+        <v>1643100</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="H53" t="n">
-        <v>49.23</v>
+        <v>65.63</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.295</v>
+        <v>0.389</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.296</v>
+        <v>0.352</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.79</v>
+        <v>5.67</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1140400</v>
+        <v>1600700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H54" t="n">
-        <v>64.37</v>
+        <v>53.03</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.772</v>
+        <v>5.681</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.757</v>
+        <v>5.218</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,39 +2907,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.0145</v>
+        <v>4.32</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.046</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1139600</v>
+        <v>1510500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.63</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.553</v>
+        <v>4.467</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.198</v>
+        <v>4.504</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.64</v>
+        <v>0.24</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0435</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1081600</v>
+        <v>1470500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.34</v>
+        <v>0.97</v>
       </c>
       <c r="H56" t="n">
-        <v>59.82</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.635</v>
+        <v>0.222</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.601</v>
+        <v>0.193</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2997,39 +2997,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.025</v>
+        <v>0.31</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1076600</v>
+        <v>1458900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="H57" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.67</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.255</v>
+        <v>0.29</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.295</v>
+        <v>0.278</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,28 +3042,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.805</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1073900</v>
+        <v>1407500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="H58" t="n">
-        <v>73.45999999999999</v>
+        <v>53.23</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.032</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.876</v>
+        <v>0.737</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.0702</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1069400</v>
+        <v>1391200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.16</v>
+        <v>1.81</v>
       </c>
       <c r="H59" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.87</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.156</v>
+        <v>0.545</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.154</v>
+        <v>0.531</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3132,28 +3132,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0183</v>
+        <v>2.81</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1053300</v>
+        <v>1372100</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="H60" t="n">
-        <v>64.69</v>
+        <v>54.93</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6.739</v>
+        <v>2.795</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>6.579</v>
+        <v>2.666</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,39 +3177,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.0141</v>
+        <v>5.12</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1045000</v>
+        <v>1290700</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="H61" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.8</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.371</v>
+        <v>4.863</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.388</v>
+        <v>4.581</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3231,19 +3231,19 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1038600</v>
+        <v>1275600</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H62" t="n">
-        <v>68.02</v>
+        <v>69.73</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0.314</v>
@@ -3267,39 +3267,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0217</v>
+        <v>0.0226</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1001400</v>
+        <v>1205100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H63" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.47</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.452</v>
+        <v>0.679</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.417</v>
+        <v>0.667</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,39 +3312,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>5.14</v>
+        <v>1.1</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0092</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>955600</v>
+        <v>1199800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="H64" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4.865</v>
+        <v>1.156</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4.581</v>
+        <v>1.154</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,28 +3357,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.67</v>
+        <v>7.27</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0152</v>
+        <v>0.0239</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>922300</v>
+        <v>1184700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="H65" t="n">
-        <v>63.59</v>
+        <v>65.39</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.633</v>
+        <v>6.742</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.606</v>
+        <v>6.58</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.0155</v>
+        <v>0.0185</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>920900</v>
+        <v>1175600</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H66" t="n">
-        <v>45.82</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.351</v>
+        <v>1.032</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.3</v>
+        <v>0.876</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.45</v>
+        <v>2.72</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0</v>
+        <v>-0.0109</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>920900</v>
+        <v>1168000</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H67" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.67</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.468</v>
+        <v>2.554</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.47</v>
+        <v>2.199</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3492,39 +3492,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0374</v>
+        <v>0.295</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>894400</v>
+        <v>1143900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="H68" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.208</v>
+        <v>0.295</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.114</v>
+        <v>0.296</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0165</v>
+        <v>0.79</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>888400</v>
+        <v>1140600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="H69" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.446</v>
+        <v>0.772</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.312</v>
+        <v>0.757</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,28 +3582,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.015</v>
+        <v>0.26</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>856700</v>
+        <v>1133500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H70" t="n">
-        <v>49.48</v>
+        <v>42.84</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.678</v>
+        <v>0.267</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.667</v>
+        <v>0.308</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3627,39 +3627,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>856400</v>
+        <v>1118100</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H71" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.49</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.895</v>
+        <v>1.255</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.855</v>
+        <v>1.295</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3672,39 +3672,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.18</v>
+        <v>0.64</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>838700</v>
+        <v>1081600</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H72" t="n">
-        <v>73.19</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.82</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.987</v>
+        <v>0.635</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.776</v>
+        <v>0.601</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3717,28 +3717,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0141</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>810900</v>
+        <v>1045000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H73" t="n">
-        <v>45.86</v>
+        <v>39.92</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.52</v>
+        <v>0.371</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.532</v>
+        <v>0.388</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3762,39 +3762,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>5.32</v>
+        <v>1.18</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0351</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>804400</v>
+        <v>1036400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H74" t="n">
-        <v>40.43</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.19</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>5.628</v>
+        <v>0.987</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.74</v>
+        <v>0.776</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3807,39 +3807,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.47</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>770800</v>
+        <v>1030000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H75" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.91</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.72</v>
+        <v>0.452</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.545</v>
+        <v>0.417</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.87</v>
+        <v>2.22</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0374</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>769200</v>
+        <v>1011200</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H76" t="n">
-        <v>72.38</v>
+        <v>51.95</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.446</v>
+        <v>2.208</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.888</v>
+        <v>2.114</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3897,39 +3897,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.52</v>
+        <v>0.505</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>0.004</v>
+        <v>0.0202</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>741800</v>
+        <v>1009600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.04</v>
+        <v>0.71</v>
       </c>
       <c r="H77" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.44</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.562</v>
+        <v>0.477</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.46</v>
+        <v>0.472</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3942,39 +3942,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5.74</v>
+        <v>2.47</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0207</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>701500</v>
+        <v>998100</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H78" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.69</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>5.687</v>
+        <v>2.447</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>5.22</v>
+        <v>2.313</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3987,28 +3987,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>2.88</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>698600</v>
+        <v>985500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H79" t="n">
-        <v>39.78</v>
+        <v>61.2</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>13.106</v>
+        <v>2.72</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>13.691</v>
+        <v>2.545</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4032,39 +4032,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10</v>
+        <v>0.67</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0152</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>691900</v>
+        <v>963100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.06</v>
+        <v>0.79</v>
       </c>
       <c r="H80" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.59</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10.112</v>
+        <v>0.633</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>10.268</v>
+        <v>0.606</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4077,28 +4077,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>-0.0189</v>
+        <v>13</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>684000</v>
+        <v>953300</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H81" t="n">
-        <v>70.01000000000001</v>
+        <v>41.47</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.947</v>
+        <v>13.109</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.79</v>
+        <v>13.692</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4122,28 +4122,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.0235</v>
+        <v>1.45</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>670900</v>
+        <v>938700</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H82" t="n">
-        <v>41.66</v>
+        <v>43.47</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3.557</v>
+        <v>1.468</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3.685</v>
+        <v>1.47</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4167,39 +4167,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0155</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>647500</v>
+        <v>927000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="H83" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.82</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.513</v>
+        <v>1.351</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.424</v>
+        <v>1.3</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4212,28 +4212,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0054</v>
+        <v>5.28</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>549400</v>
+        <v>921300</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H84" t="n">
-        <v>24.04</v>
+        <v>39.12</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>7.813</v>
+        <v>5.624</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4257,28 +4257,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.09</v>
+        <v>2.89</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>0.0187</v>
+        <v>0.0105</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>537200</v>
+        <v>861800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>73.56</v>
+        <v>72.78</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.008</v>
+        <v>2.448</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.841</v>
+        <v>1.888</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4302,39 +4302,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.23</v>
+        <v>0.91</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>528800</v>
+        <v>856400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H86" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.349</v>
+        <v>0.895</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.318</v>
+        <v>0.855</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4347,28 +4347,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0</v>
+        <v>2.52</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.004</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>518200</v>
+        <v>838000</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H87" t="n">
-        <v>65.81999999999999</v>
+        <v>47.67</v>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.989</v>
+        <v>2.562</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.983</v>
+        <v>2.46</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4392,39 +4392,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.04</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>515100</v>
+        <v>806400</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H88" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.01000000000001</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>7.787</v>
+        <v>0.947</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>7.75</v>
+        <v>0.79</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4437,45 +4437,900 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>500000</v>
+        <v>795000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="H89" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.03</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.629</v>
+        <v>0.513</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.636</v>
+        <v>0.424</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>791600</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H90" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>10.111</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>10.268</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>715600</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>3.805</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>3.327</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H92" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>687500</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H93" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>671600</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H94" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>629600</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H95" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>621100</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H96" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>594500</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H97" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>9.696</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>9.237</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>593900</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H98" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>593700</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H99" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>593200</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H100" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>7.813</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>575700</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H101" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>559400</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H102" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H103" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>537500</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H104" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>524000</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H105" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>7.787</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>518200</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H106" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>517100</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H107" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H108" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M89"/>
+  <autoFilter ref="A1:M108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
-    </font>
-    <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00D03B3B"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,13 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>39094200</v>
+        <v>53430700</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H2" t="n">
-        <v>64.31999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.124</v>
@@ -603,10 +603,10 @@
         <v>-0.0303</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>37075500</v>
+        <v>46987800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="n">
         <v>21.26</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.375</v>
+        <v>0.28</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>23354200</v>
+        <v>27414300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H4" t="n">
-        <v>71.16</v>
+        <v>68.06</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.34</v>
+        <v>0.244</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.209</v>
+        <v>0.234</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.285</v>
+        <v>0.375</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.0556</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>22450100</v>
+        <v>23404200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H5" t="n">
-        <v>69.36</v>
+        <v>71.16</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.244</v>
+        <v>0.34</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.234</v>
+        <v>0.209</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.08</v>
+        <v>0.785</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.068</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21005300</v>
+        <v>22184900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H6" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.68</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.096</v>
+        <v>0.741</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -779,14 +779,14 @@
       <c r="D7" s="2" t="n">
         <v>0.605</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.0901</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>19275300</v>
+        <v>22183800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="H7" t="n">
         <v>65.87</v>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.068</v>
+        <v>0.135</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.08</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17898100</v>
+        <v>21623200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>61.68</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.41</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.741</v>
+        <v>0.096</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -869,14 +869,14 @@
       <c r="D9" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.0303</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11998600</v>
+        <v>12633500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H9" t="n">
         <v>64.04000000000001</v>
@@ -918,10 +918,10 @@
         <v>-0.0313</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11570000</v>
+        <v>11870000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H10" t="n">
         <v>46.33</v>
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.05</v>
+        <v>0.425</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8657100</v>
+        <v>10709000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H11" t="n">
-        <v>62.22</v>
+        <v>63.2</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.331</v>
@@ -993,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7865400</v>
+        <v>8570000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.85</v>
+        <v>4.64</v>
       </c>
       <c r="H12" t="n">
-        <v>57.03</v>
+        <v>58.68</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.081</v>
+        <v>0.008</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.077</v>
+        <v>0.008</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,33 +1038,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.0392</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6615700</v>
+        <v>7953500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+        <v>0.86</v>
+      </c>
+      <c r="H13" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.077</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,40 +1083,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.075</v>
+        <v>0.26</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5929400</v>
+        <v>6898500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.078</v>
-      </c>
+        <v>0.52</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.83</v>
+        <v>0.2</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0311</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5785400</v>
+        <v>6750700</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.743</v>
+        <v>0.196</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.698</v>
+        <v>0.18</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.0308</v>
+        <v>0.82</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5585300</v>
+        <v>6543900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H16" t="n">
-        <v>56.04</v>
+        <v>65.22</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.321</v>
+        <v>0.742</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.337</v>
+        <v>0.697</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,28 +1211,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E17" s="3" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5171700</v>
+        <v>6280500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.84</v>
+        <v>0.24</v>
       </c>
       <c r="H17" t="n">
-        <v>68.89</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.282</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.272</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.33</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4744600</v>
+        <v>6143800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.12</v>
+        <v>1.14</v>
       </c>
       <c r="H18" t="n">
-        <v>29.72</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.89</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.595</v>
+        <v>0.32</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.804</v>
+        <v>0.337</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.82</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.0282</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4194100</v>
+        <v>6067200</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.19</v>
+        <v>0.99</v>
       </c>
       <c r="H19" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.89</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.752</v>
+        <v>0.282</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.575</v>
+        <v>0.272</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.195</v>
+        <v>0.075</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.1143</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4102700</v>
+        <v>5929400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="H20" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.39</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.165</v>
+        <v>0.076</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.165</v>
+        <v>0.078</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.2</v>
+        <v>0.78</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4037400</v>
+        <v>5743300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H21" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.196</v>
+        <v>0.774</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.18</v>
+        <v>0.775</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0303</v>
+        <v>1.81</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4018400</v>
+        <v>5150600</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H22" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.08</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.158</v>
+        <v>1.751</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.147</v>
+        <v>1.575</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,28 +1481,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0.515</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3949000</v>
+        <v>5115700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="H23" t="n">
-        <v>38.65</v>
+        <v>28.59</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.406</v>
+        <v>0.594</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.411</v>
+        <v>0.804</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,40 +1526,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0385</v>
+        <v>0.115</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3896800</v>
+        <v>5083400</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H24" t="n">
-        <v>58.15</v>
+        <v>0.17</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n">
-        <v>3.619</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>2.544</v>
-      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1571,28 +1564,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.245</v>
+        <v>0.61</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3711500</v>
+        <v>4872000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="H25" t="n">
-        <v>35.11</v>
+        <v>51.26</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1600,10 +1593,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.265</v>
+        <v>0.607</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.317</v>
+        <v>0.607</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,28 +1609,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.013</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3677000</v>
+        <v>4745400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="H26" t="n">
-        <v>52.97</v>
+        <v>61.11</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1645,10 +1638,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.774</v>
+        <v>0.378</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.775</v>
+        <v>0.372</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1654,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.61</v>
+        <v>0.375</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>0.0274</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3548400</v>
+        <v>4362700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="H27" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.607</v>
+        <v>0.368</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.607</v>
+        <v>0.367</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,33 +1699,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0455</v>
+        <v>5.58</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0245</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3455400</v>
+        <v>4322600</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
+        <v>0.31</v>
+      </c>
+      <c r="H28" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>5.672</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>5.217</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.0083</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3267700</v>
+        <v>4282100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H29" t="n">
-        <v>75.12</v>
+        <v>32.12</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.265</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.496</v>
+        <v>0.317</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.04849999999999999</v>
+        <v>3.72</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.022</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3183800</v>
+        <v>4275000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="H30" t="n">
-        <v>52.67</v>
+        <v>57.14</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.07</v>
+        <v>3.613</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.027</v>
+        <v>2.542</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.8</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3167700</v>
+        <v>4214900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="H31" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.142</v>
+        <v>0.709</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.15</v>
+        <v>0.636</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.19</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3041500</v>
+        <v>4108700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>30.64</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.62</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.546</v>
+        <v>0.165</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.582</v>
+        <v>0.165</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.805</v>
+        <v>0.165</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2915500</v>
+        <v>4074000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="H33" t="n">
-        <v>76.41</v>
+        <v>54.4</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.709</v>
+        <v>0.159</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.636</v>
+        <v>0.148</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,39 +1969,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.026</v>
+        <v>1.07</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2835900</v>
+        <v>4041700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H34" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.22</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.378</v>
+        <v>1.069</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.372</v>
+        <v>1.027</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,39 +2014,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.23</v>
+        <v>0.395</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0133</v>
+        <v>-0.0125</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2480200</v>
+        <v>3949500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H35" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.65</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.275</v>
+        <v>0.406</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.206</v>
+        <v>0.411</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,28 +2059,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.18</v>
+        <v>0.505</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2420200</v>
+        <v>3747800</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="H36" t="n">
-        <v>54.88</v>
+        <v>27.69</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.157</v>
+        <v>0.545</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.108</v>
+        <v>0.582</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.545</v>
+        <v>0.725</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0481</v>
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2388000</v>
+        <v>3526800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="H37" t="n">
-        <v>80.28</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.47</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.437</v>
+        <v>0.776</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.418</v>
+        <v>0.834</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,33 +2149,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.215</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2372000</v>
+        <v>3371200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50.19</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+      <c r="J38" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2187,28 +2194,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0283</v>
+        <v>2.22</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2311100</v>
+        <v>3316500</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H39" t="n">
-        <v>63.64</v>
+        <v>46.18</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2216,10 +2223,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.499</v>
+        <v>2.274</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.418</v>
+        <v>2.206</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2232,39 +2239,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2284200</v>
+        <v>3265500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.3</v>
+        <v>0.83</v>
       </c>
       <c r="H40" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.71</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.336</v>
+        <v>0.142</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.317</v>
+        <v>0.15</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2277,28 +2284,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.16</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2192400</v>
+        <v>3225800</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="H41" t="n">
-        <v>52.92</v>
+        <v>35.9</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2306,10 +2313,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.367</v>
+        <v>0.174</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.367</v>
+        <v>0.21</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2322,28 +2329,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0388</v>
+        <v>0.54</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2181700</v>
+        <v>3127900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="H42" t="n">
-        <v>60.11</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2351,10 +2358,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.639</v>
+        <v>0.437</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.586</v>
+        <v>0.418</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2367,28 +2374,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.255</v>
+        <v>0.305</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1933800</v>
+        <v>2799900</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.6</v>
+        <v>0.14</v>
       </c>
       <c r="H43" t="n">
-        <v>63.2</v>
+        <v>53.61</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2396,10 +2403,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.236</v>
+        <v>0.304</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.212</v>
+        <v>0.293</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2412,28 +2419,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0185</v>
+        <v>1.17</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1923300</v>
+        <v>2788200</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H44" t="n">
-        <v>39.86</v>
+        <v>53.57</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2441,10 +2448,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.701</v>
+        <v>1.156</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.818</v>
+        <v>1.108</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2457,39 +2464,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.0062</v>
+        <v>0.355</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1887700</v>
+        <v>2622500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.336</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2502,39 +2509,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.66</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1840500</v>
+        <v>2544700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H46" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.26</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.521</v>
+        <v>0.638</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.532</v>
+        <v>0.586</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2547,28 +2554,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.76</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1824500</v>
+        <v>2515100</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>0.38</v>
       </c>
       <c r="H47" t="n">
-        <v>31.5</v>
+        <v>44.45</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2576,10 +2583,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.777</v>
+        <v>0.769</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.834</v>
+        <v>0.771</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2592,39 +2599,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.54</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1784400</v>
+        <v>2502700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H48" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.9</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.769</v>
+        <v>0.499</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.771</v>
+        <v>0.418</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2637,40 +2644,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.285</v>
+        <v>0.21</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>0.0244</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1728000</v>
+        <v>2499200</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H49" t="n">
-        <v>35.15</v>
+        <v>0.04</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2697,10 +2697,10 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1701200</v>
+        <v>2441300</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H50" t="n">
         <v>47.02</v>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.26</v>
+        <v>1.65</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0</v>
+        <v>0.0185</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1698600</v>
+        <v>2363800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2.01</v>
+        <v>0.36</v>
       </c>
       <c r="H51" t="n">
-        <v>45.51</v>
+        <v>39.86</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.261</v>
+        <v>1.701</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.265</v>
+        <v>1.818</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,40 +2772,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.555</v>
+        <v>0.475</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.0374</v>
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1677500</v>
+        <v>2299100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H52" t="n">
-        <v>63.6</v>
+        <v>0.15</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>0.476</v>
-      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2817,39 +2810,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.51</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1643100</v>
+        <v>2180500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.62</v>
+        <v>0.35</v>
       </c>
       <c r="H53" t="n">
-        <v>65.63</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.86</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.389</v>
+        <v>0.52</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.352</v>
+        <v>0.532</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,28 +2855,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>5.15</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1600700</v>
+        <v>2162200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H54" t="n">
-        <v>53.03</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2891,10 +2884,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.681</v>
+        <v>4.866</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.218</v>
+        <v>4.582</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,28 +2900,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.32</v>
+        <v>0.285</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1510500</v>
+        <v>2127200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>44.63</v>
+        <v>35.15</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2936,10 +2929,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.467</v>
+        <v>0.294</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.504</v>
+        <v>0.31</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,28 +2945,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.255</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1470500</v>
+        <v>2115900</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H56" t="n">
-        <v>65.26000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2981,10 +2974,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.222</v>
+        <v>0.236</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.193</v>
+        <v>0.212</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2997,28 +2990,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.31</v>
+        <v>0.545</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1458900</v>
+        <v>2078400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
       </c>
       <c r="H57" t="n">
-        <v>58.67</v>
+        <v>61.4</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3026,10 +3019,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.29</v>
+        <v>0.518</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.278</v>
+        <v>0.475</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,39 +3035,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.805</v>
+        <v>0.615</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1407500</v>
+        <v>1974700</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.44</v>
+        <v>2.58</v>
       </c>
       <c r="H58" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.55</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.737</v>
+        <v>0.531</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3087,39 +3080,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.0702</v>
+        <v>1.28</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1391200</v>
+        <v>1923700</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.81</v>
+        <v>0.16</v>
       </c>
       <c r="H59" t="n">
-        <v>84.87</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.17</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.545</v>
+        <v>1.348</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.531</v>
+        <v>1.3</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3132,28 +3125,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1372100</v>
+        <v>1791500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.09</v>
+        <v>0.68</v>
       </c>
       <c r="H60" t="n">
-        <v>54.93</v>
+        <v>62.45</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3161,10 +3154,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.795</v>
+        <v>0.388</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.666</v>
+        <v>0.352</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,28 +3170,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="E61" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1290700</v>
+        <v>1790000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H61" t="n">
-        <v>70.8</v>
+        <v>58.67</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3206,10 +3199,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4.863</v>
+        <v>0.29</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>4.581</v>
+        <v>0.278</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3222,39 +3215,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0139</v>
+        <v>4.3</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1275600</v>
+        <v>1743200</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H62" t="n">
-        <v>69.73</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.94</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.337</v>
+        <v>4.465</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.314</v>
+        <v>4.504</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3267,28 +3260,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0.0226</v>
+        <v>2.83</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1205100</v>
+        <v>1723800</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H63" t="n">
-        <v>50.47</v>
+        <v>56.71</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3296,10 +3289,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.679</v>
+        <v>2.797</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.667</v>
+        <v>2.667</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,39 +3305,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.0092</v>
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1199800</v>
+        <v>1722400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H64" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.156</v>
+        <v>0.772</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.154</v>
+        <v>0.757</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,39 +3350,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>7.27</v>
+        <v>1.08</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0239</v>
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1184700</v>
+        <v>1722000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="H65" t="n">
-        <v>65.39</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.742</v>
+        <v>1.03</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>6.58</v>
+        <v>0.876</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3395,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.255</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1175600</v>
+        <v>1698800</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.1</v>
+        <v>2.01</v>
       </c>
       <c r="H66" t="n">
-        <v>73.45999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -3431,10 +3424,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.032</v>
+        <v>0.26</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.876</v>
+        <v>0.265</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,28 +3440,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>-0.0109</v>
+        <v>4.31</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1168000</v>
+        <v>1674800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H67" t="n">
-        <v>76.67</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3476,10 +3469,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.554</v>
+        <v>3.804</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.199</v>
+        <v>3.327</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3492,28 +3485,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.295</v>
+        <v>7.28</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.0254</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1143900</v>
+        <v>1660200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="H68" t="n">
-        <v>49.23</v>
+        <v>65.56</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3521,10 +3514,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.295</v>
+        <v>6.743</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.296</v>
+        <v>6.58</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3537,39 +3530,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1140600</v>
+        <v>1612600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="H69" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.81</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.772</v>
+        <v>0.806</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.757</v>
+        <v>0.736</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,28 +3575,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1133500</v>
+        <v>1603800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H70" t="n">
-        <v>42.84</v>
+        <v>48.44</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3611,10 +3604,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.267</v>
+        <v>0.678</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.308</v>
+        <v>0.667</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3627,28 +3620,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.025</v>
+        <v>0.36</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1118100</v>
+        <v>1536500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="H71" t="n">
-        <v>43.49</v>
+        <v>39.92</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -3656,10 +3649,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.255</v>
+        <v>0.371</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.295</v>
+        <v>0.388</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3672,28 +3665,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.24</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1081600</v>
+        <v>1480700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.34</v>
+        <v>0.97</v>
       </c>
       <c r="H72" t="n">
-        <v>59.82</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3701,10 +3694,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.635</v>
+        <v>0.222</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.601</v>
+        <v>0.193</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3717,28 +3710,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.36</v>
+        <v>1.09</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.0141</v>
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1045000</v>
+        <v>1472500</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="H73" t="n">
-        <v>39.92</v>
+        <v>39.73</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -3746,10 +3739,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.371</v>
+        <v>1.155</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.388</v>
+        <v>1.153</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3762,28 +3755,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0351</v>
+        <v>2.69</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0218</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1036400</v>
+        <v>1441200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="H74" t="n">
-        <v>73.19</v>
+        <v>72.27</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3791,10 +3784,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.987</v>
+        <v>2.551</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.776</v>
+        <v>2.198</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3807,28 +3800,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0217</v>
+        <v>5.17</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1030000</v>
+        <v>1405900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H75" t="n">
-        <v>56.91</v>
+        <v>36.62</v>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
@@ -3836,10 +3829,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.452</v>
+        <v>5.613</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.417</v>
+        <v>5.737</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3852,28 +3845,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.0374</v>
+        <v>0.655</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.0397</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1011200</v>
+        <v>1371400</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.17</v>
+        <v>1.25</v>
       </c>
       <c r="H76" t="n">
-        <v>51.95</v>
+        <v>51.46</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -3881,10 +3874,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.208</v>
+        <v>0.646</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.114</v>
+        <v>0.66</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3897,28 +3890,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.37</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1009600</v>
+        <v>1369200</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.71</v>
+        <v>0.17</v>
       </c>
       <c r="H77" t="n">
-        <v>60.44</v>
+        <v>71.27</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3926,10 +3919,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.477</v>
+        <v>0.337</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.472</v>
+        <v>0.314</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3942,39 +3935,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0207</v>
+        <v>0.5</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>998100</v>
+        <v>1366300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.06</v>
+        <v>0.96</v>
       </c>
       <c r="H78" t="n">
-        <v>55.69</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.08</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.447</v>
+        <v>0.477</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.313</v>
+        <v>0.472</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3996,19 +3989,19 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>-0.0069</v>
+        <v>-0.0138</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>985500</v>
+        <v>1365000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H79" t="n">
-        <v>61.2</v>
+        <v>59.96</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4016,7 +4009,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.72</v>
+        <v>2.718</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>2.545</v>
@@ -4032,39 +4025,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.0152</v>
+        <v>1.02</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>963100</v>
+        <v>1361800</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.79</v>
+        <v>0.17</v>
       </c>
       <c r="H80" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.25</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.633</v>
+        <v>0.945</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.606</v>
+        <v>0.789</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4077,28 +4070,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.255</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>953300</v>
+        <v>1322200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H81" t="n">
-        <v>41.47</v>
+        <v>40.85</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4106,10 +4099,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>13.109</v>
+        <v>0.266</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>13.692</v>
+        <v>0.308</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4122,39 +4115,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>938700</v>
+        <v>1274100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H82" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.19</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.468</v>
+        <v>0.987</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.47</v>
+        <v>0.776</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4167,28 +4160,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0155</v>
+        <v>2.89</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>927000</v>
+        <v>1259200</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="H83" t="n">
-        <v>45.82</v>
+        <v>72.78</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4196,10 +4189,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.351</v>
+        <v>2.448</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.3</v>
+        <v>1.888</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4212,28 +4205,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.0038</v>
+        <v>1.23</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>921300</v>
+        <v>1251500</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="H84" t="n">
-        <v>39.12</v>
+        <v>43.49</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4241,10 +4234,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5.624</v>
+        <v>1.255</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>5.74</v>
+        <v>1.295</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4257,28 +4250,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0105</v>
+        <v>3.47</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>861800</v>
+        <v>1248600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>72.78</v>
+        <v>40.84</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4286,10 +4279,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.448</v>
+        <v>3.556</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.888</v>
+        <v>3.685</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4302,39 +4295,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E86" s="3" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>856400</v>
+        <v>1244100</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="H86" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.895</v>
+        <v>0.237</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.855</v>
+        <v>0.243</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4347,39 +4340,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.004</v>
+        <v>13</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>838000</v>
+        <v>1238800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H87" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.47</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.562</v>
+        <v>13.109</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.46</v>
+        <v>13.692</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4392,28 +4385,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.0189</v>
+        <v>2.83</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>806400</v>
+        <v>1224600</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="H88" t="n">
-        <v>70.01000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4421,10 +4414,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.947</v>
+        <v>2.455</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.79</v>
+        <v>2.035</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4437,39 +4430,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.03700000000000001</v>
+        <v>2.46</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>795000</v>
+        <v>1197300</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
       <c r="H89" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.66</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.513</v>
+        <v>2.446</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.424</v>
+        <v>2.312</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4482,28 +4475,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.004</v>
+        <v>2.06</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>791600</v>
+        <v>1177100</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>0.06</v>
       </c>
       <c r="H90" t="n">
-        <v>38.48</v>
+        <v>43.4</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -4511,10 +4504,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>10.111</v>
+        <v>2.108</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>10.268</v>
+        <v>2.071</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4527,39 +4520,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.0286</v>
+        <v>0.47</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>715600</v>
+        <v>1169700</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H91" t="n">
-        <v>71.64</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.91</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>3.805</v>
+        <v>0.452</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3.327</v>
+        <v>0.417</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4572,28 +4565,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.645</v>
+        <v>0.295</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>710000</v>
+        <v>1143900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>59.07</v>
+        <v>49.23</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4601,10 +4594,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.61</v>
+        <v>0.295</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.609</v>
+        <v>0.296</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4617,28 +4610,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>3.48</v>
+        <v>0.635</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>687500</v>
+        <v>1124600</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H93" t="n">
-        <v>41.66</v>
+        <v>56.51</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
@@ -4646,10 +4639,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>3.557</v>
+        <v>0.635</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3.685</v>
+        <v>0.601</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4662,28 +4655,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>-0.024</v>
+        <v>-0.0069</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>671600</v>
+        <v>1101500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H94" t="n">
-        <v>31.16</v>
+        <v>40.6</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4691,10 +4684,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.348</v>
+        <v>1.467</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.318</v>
+        <v>1.47</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4707,28 +4700,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.008</v>
+        <v>2.2</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.028</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>629600</v>
+        <v>1099500</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H95" t="n">
-        <v>34.24</v>
+        <v>50.63</v>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
@@ -4736,10 +4729,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.31</v>
+        <v>2.206</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.416</v>
+        <v>2.113</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4752,28 +4745,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>-0.0105</v>
+        <v>9.98</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.003</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>621100</v>
+        <v>1097900</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="H96" t="n">
-        <v>37.18</v>
+        <v>37.63</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4781,10 +4774,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.934</v>
+        <v>10.11</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.056</v>
+        <v>10.268</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4797,28 +4790,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0.016</v>
+        <v>0.635</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>594500</v>
+        <v>1069500</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H97" t="n">
-        <v>68.34999999999999</v>
+        <v>57.04</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4826,10 +4819,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>9.696</v>
+        <v>0.609</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>9.237</v>
+        <v>0.609</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4842,39 +4835,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0.023</v>
+        <v>7.43</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>593900</v>
+        <v>1050700</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H98" t="n">
-        <v>62.37</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.04</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.925</v>
+        <v>7.813</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.74</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4887,39 +4880,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.67</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>593700</v>
+        <v>1049800</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.15</v>
+        <v>0.87</v>
       </c>
       <c r="H99" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.59</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.246</v>
+        <v>0.633</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.16</v>
+        <v>0.606</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4932,39 +4925,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>7.43</v>
+        <v>0.9</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>-0.0054</v>
+        <v>-0.011</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>593200</v>
+        <v>995900</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="H100" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>7.813</v>
+        <v>0.894</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>0.854</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4977,39 +4970,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>2.52</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>575700</v>
+        <v>993500</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="H101" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.573</v>
+        <v>2.562</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.576</v>
+        <v>2.46</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5022,39 +5015,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.0069</v>
+        <v>1.27</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0.016</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>559400</v>
+        <v>956400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H102" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.83</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.51</v>
+        <v>1.416</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5067,39 +5060,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.028</v>
+        <v>0.555</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>557500</v>
+        <v>955100</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="H103" t="n">
-        <v>74.51000000000001</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.009</v>
+        <v>0.512</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.841</v>
+        <v>0.424</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5112,28 +5105,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>-0.0048</v>
+        <v>0.62</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>537500</v>
+        <v>923800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.03</v>
+        <v>0.39</v>
       </c>
       <c r="H104" t="n">
-        <v>43.4</v>
+        <v>44.55</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5141,10 +5134,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.108</v>
+        <v>0.629</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.071</v>
+        <v>0.637</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5157,28 +5150,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.88</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>524000</v>
+        <v>831100</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="H105" t="n">
-        <v>48.68</v>
+        <v>37.18</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -5186,10 +5179,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>7.787</v>
+        <v>1.934</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>7.75</v>
+        <v>2.056</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5202,28 +5195,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>1.84</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.0366</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>518200</v>
+        <v>802000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="H106" t="n">
-        <v>65.81999999999999</v>
+        <v>31.44</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -5231,10 +5224,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.989</v>
+        <v>1.943</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.983</v>
+        <v>2.007</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5247,28 +5240,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>517100</v>
+        <v>801700</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H107" t="n">
-        <v>23.51</v>
+        <v>35.66</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5276,10 +5269,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.087</v>
+        <v>1.957</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.139</v>
+        <v>1.967</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5292,28 +5285,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.625</v>
+        <v>1.24</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>500000</v>
+        <v>798200</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="H108" t="n">
-        <v>41.61</v>
+        <v>51.53</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
@@ -5321,16 +5314,916 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.629</v>
+        <v>1.244</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.636</v>
+        <v>1.16</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>798000</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H109" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>797700</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H110" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>759100</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H111" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>9.696999999999999</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>9.237</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>743400</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H112" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>734500</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H113" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>680100</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H114" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>677000</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H115" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>7.783</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>7.749</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>669400</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H116" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>663700</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H117" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>663600</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H118" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>637100</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H119" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>4.603</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>4.923</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>623700</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H120" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>4.795</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H121" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>621300</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H122" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>2.971</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>3.034</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>-0.0361</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>586800</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H123" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.722</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>544000</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H124" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>533500</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H125" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>524700</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H126" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>506600</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H127" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M108"/>
+  <autoFilter ref="A1:M128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.0556</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>53430700</v>
+        <v>64030300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="n">
-        <v>65.93000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         <v>-0.0303</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46987800</v>
+        <v>51545600</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H3" t="n">
         <v>21.26</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.28</v>
+        <v>0.635</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.1441</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>27414300</v>
+        <v>35275400</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.76</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>68.06</v>
+        <v>69.5</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.244</v>
+        <v>0.544</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.234</v>
+        <v>0.494</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>23404200</v>
+        <v>32632000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>71.16</v>
+        <v>68.06</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.244</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.209</v>
+        <v>0.234</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.068</v>
+        <v>0.37</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22184900</v>
+        <v>23589200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H6" t="n">
-        <v>61.68</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.93000000000001</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.741</v>
+        <v>0.34</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.605</v>
+        <v>0.785</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0901</v>
+        <v>0.068</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22183800</v>
+        <v>22815000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.42</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.68</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.541</v>
+        <v>0.741</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.493</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -828,10 +828,10 @@
         <v>0.08</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>21623200</v>
+        <v>21720700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="H8" t="n">
         <v>79.41</v>
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.0202</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12633500</v>
+        <v>13846700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>64.04000000000001</v>
+        <v>62.69</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0.473</v>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0313</v>
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11870000</v>
+        <v>13570000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.45</v>
+        <v>7.35</v>
       </c>
       <c r="H10" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.68</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.156</v>
+        <v>0.008</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.158</v>
+        <v>0.008</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.605</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10709000</v>
+        <v>12434900</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.389</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.331</v>
+        <v>0.496</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8570000</v>
+        <v>11980000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>4.64</v>
+        <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>58.68</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.25</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.008</v>
+        <v>0.155</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.008</v>
+        <v>0.158</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7953500</v>
+        <v>11083100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.86</v>
+        <v>0.51</v>
       </c>
       <c r="H13" t="n">
-        <v>57.03</v>
+        <v>62.22</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.081</v>
+        <v>0.388</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.077</v>
+        <v>0.331</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,33 +1083,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.0196</v>
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6898500</v>
+        <v>8796700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+        <v>0.39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1121,28 +1128,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6750700</v>
+        <v>8082700</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.3</v>
+        <v>0.87</v>
       </c>
       <c r="H15" t="n">
-        <v>56.71</v>
+        <v>57.03</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1150,10 +1157,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.196</v>
+        <v>0.081</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.18</v>
+        <v>0.077</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,40 +1173,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.0186</v>
+        <v>0.005</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6543900</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H16" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0.697</v>
-      </c>
+        <v>8046000</v>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1211,28 +1209,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0105</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ASIAPLY</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.605</v>
+        <v>0.095</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6280500</v>
+        <v>7916400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.24</v>
+        <v>5.46</v>
       </c>
       <c r="H17" t="n">
-        <v>74.09999999999999</v>
+        <v>53.98</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1240,10 +1238,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.496</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,40 +1254,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.0196</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6143800</v>
+        <v>7616900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H18" t="n">
-        <v>53.89</v>
+        <v>0.57</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.337</v>
-      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1301,28 +1292,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6067200</v>
+        <v>7309700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H19" t="n">
-        <v>68.89</v>
+        <v>52.97</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1330,10 +1321,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.282</v>
+        <v>0.774</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.272</v>
+        <v>0.775</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1337,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5929400</v>
+        <v>7211900</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.2</v>
+        <v>0.64</v>
       </c>
       <c r="H20" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.67</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.076</v>
+        <v>0.742</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.078</v>
+        <v>0.697</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1382,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.78</v>
+        <v>0.33</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5743300</v>
+        <v>6859800</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.42</v>
+        <v>1.27</v>
       </c>
       <c r="H21" t="n">
-        <v>52.97</v>
+        <v>53.89</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1411,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.774</v>
+        <v>0.32</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.775</v>
+        <v>0.337</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1427,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1.81</v>
+        <v>0.305</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0226</v>
+        <v>0.0167</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5150600</v>
+        <v>6661000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.23</v>
+        <v>1.09</v>
       </c>
       <c r="H22" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.3</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.751</v>
+        <v>0.283</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.575</v>
+        <v>0.272</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,28 +1472,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0098</v>
+        <v>5.53</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0332</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5115700</v>
+        <v>6560300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>28.59</v>
+        <v>47.74</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1510,10 +1501,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.594</v>
+        <v>5.667</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.804</v>
+        <v>5.216</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,33 +1517,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.115</v>
+        <v>0.515</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.0098</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5083400</v>
+        <v>6404000</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.17</v>
       </c>
+      <c r="H24" t="n">
+        <v>28.59</v>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+      <c r="J24" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.804</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1564,39 +1562,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.61</v>
+        <v>0.075</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4872000</v>
+        <v>5929400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.46</v>
+        <v>1.2</v>
       </c>
       <c r="H25" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.39</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.607</v>
+        <v>0.076</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.607</v>
+        <v>0.078</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,39 +1607,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.39</v>
+        <v>1.8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.013</v>
+        <v>0.0169</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4745400</v>
+        <v>5887300</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="H26" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.36</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.378</v>
+        <v>1.75</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.372</v>
+        <v>1.575</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,39 +1652,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0.0274</v>
+        <v>0.61</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4362700</v>
+        <v>5603800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.26</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.368</v>
+        <v>0.607</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.367</v>
+        <v>0.607</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,28 +1697,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0245</v>
+        <v>0.39</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.013</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4322600</v>
+        <v>5595700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="H28" t="n">
-        <v>49.51</v>
+        <v>61.11</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1728,10 +1726,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5.672</v>
+        <v>0.378</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>5.217</v>
+        <v>0.372</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,39 +1742,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.24</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4282100</v>
+        <v>5453200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="H29" t="n">
-        <v>32.12</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.265</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.317</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,39 +1787,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0.022</v>
+        <v>0.165</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4275000</v>
+        <v>5386800</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="H30" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.613</v>
+        <v>0.159</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.542</v>
+        <v>0.148</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,40 +1832,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0191</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4214900</v>
+        <v>5166000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H31" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0.636</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
     </row>
@@ -1879,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.0857</v>
+        <v>0.505</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4108700</v>
+        <v>5103200</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.69</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.165</v>
+        <v>0.545</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.165</v>
+        <v>0.582</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4074000</v>
+        <v>4842800</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.1</v>
+        <v>0.82</v>
       </c>
       <c r="H33" t="n">
-        <v>54.4</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.159</v>
+        <v>0.708</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.148</v>
+        <v>0.636</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1960,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.07</v>
+        <v>0.37</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.0388</v>
+        <v>0.0137</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4041700</v>
+        <v>4817700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="H34" t="n">
-        <v>51.22</v>
+        <v>52.92</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1998,10 +1989,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.069</v>
+        <v>0.367</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1.027</v>
+        <v>0.367</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0.24</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3949500</v>
+        <v>4671000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="H35" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.12</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.406</v>
+        <v>0.265</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.411</v>
+        <v>0.317</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>3.74</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3747800</v>
+        <v>4573300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H36" t="n">
-        <v>27.69</v>
+        <v>57.48</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -2088,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.545</v>
+        <v>3.615</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.582</v>
+        <v>2.543</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3526800</v>
+        <v>4463500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="H37" t="n">
-        <v>29.47</v>
+        <v>51.22</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -2133,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.776</v>
+        <v>1.069</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.834</v>
+        <v>1.027</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,28 +2140,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0221</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3371200</v>
+        <v>4425500</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H38" t="n">
-        <v>50.19</v>
+        <v>45.48</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -2178,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.273</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.206</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,28 +2185,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.0177</v>
+        <v>0.195</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.1143</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3316500</v>
+        <v>4337100</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.21</v>
+        <v>0.85</v>
       </c>
       <c r="H39" t="n">
-        <v>46.18</v>
+        <v>69.47</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2223,10 +2214,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.274</v>
+        <v>0.165</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.206</v>
+        <v>0.165</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,39 +2230,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.13</v>
+        <v>0.865</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3265500</v>
+        <v>4243300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.83</v>
+        <v>0.22</v>
       </c>
       <c r="H40" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.142</v>
+        <v>0.868</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.15</v>
+        <v>0.87</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.0323</v>
+        <v>0.395</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3225800</v>
+        <v>4057300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H41" t="n">
-        <v>35.9</v>
+        <v>38.65</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2313,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.174</v>
+        <v>0.406</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.21</v>
+        <v>0.411</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,28 +2320,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.0385</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3127900</v>
+        <v>4015000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="H42" t="n">
-        <v>79.79000000000001</v>
+        <v>61.81</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2358,10 +2349,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.437</v>
+        <v>0.64</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.418</v>
+        <v>0.586</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2799900</v>
+        <v>3883500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>53.61</v>
+        <v>28.63</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2403,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.304</v>
+        <v>0.776</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.293</v>
+        <v>0.834</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.0263</v>
+        <v>1.01</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0472</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2788200</v>
+        <v>3788400</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H44" t="n">
-        <v>53.57</v>
+        <v>64.52</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2448,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.156</v>
+        <v>0.944</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.108</v>
+        <v>0.789</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2622500</v>
+        <v>3744000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H45" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.336</v>
+        <v>1.347</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.317</v>
+        <v>1.3</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2500,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0233</v>
+        <v>0.0192</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2544700</v>
+        <v>3672800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.25</v>
+        <v>1.3</v>
       </c>
       <c r="H46" t="n">
-        <v>58.26</v>
+        <v>78.73</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2538,10 +2529,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.638</v>
+        <v>0.436</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.586</v>
+        <v>0.418</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.76</v>
+        <v>0.16</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.0323</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2515100</v>
+        <v>3306500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="H47" t="n">
-        <v>44.45</v>
+        <v>35.9</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2583,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.769</v>
+        <v>0.174</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.771</v>
+        <v>0.21</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.0189</v>
+        <v>0.355</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2502700</v>
+        <v>3303000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H48" t="n">
-        <v>62.9</v>
+        <v>62.52</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2628,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.499</v>
+        <v>0.336</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.418</v>
+        <v>0.317</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,33 +2635,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.0244</v>
+        <v>0.13</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2499200</v>
+        <v>3268800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.04</v>
+        <v>0.83</v>
+      </c>
+      <c r="H49" t="n">
+        <v>35.71</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
+      <c r="J49" s="2" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.15</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2682,39 +2680,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.52</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2441300</v>
+        <v>3206900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="H50" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.868</v>
+        <v>0.521</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.87</v>
+        <v>0.532</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2727,28 +2725,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.185</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2363800</v>
+        <v>3037300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H51" t="n">
-        <v>39.86</v>
+        <v>42.14</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2756,10 +2754,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.701</v>
+        <v>0.193</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.818</v>
+        <v>0.197</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,33 +2770,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>5.13</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.002</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2299100</v>
+        <v>2958900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
+      </c>
+      <c r="H52" t="n">
+        <v>71.15000000000001</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+      <c r="J52" s="2" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>4.581</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2810,28 +2815,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2180500</v>
+        <v>2948900</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H53" t="n">
-        <v>45.86</v>
+        <v>44.45</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -2839,10 +2844,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.52</v>
+        <v>0.769</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.532</v>
+        <v>0.771</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2855,39 +2860,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.305</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2162200</v>
+        <v>2899900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="H54" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.866</v>
+        <v>0.304</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4.582</v>
+        <v>0.293</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2900,28 +2905,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2127200</v>
+        <v>2894200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H55" t="n">
-        <v>35.15</v>
+        <v>64.67</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2929,10 +2934,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.294</v>
+        <v>1.028</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.31</v>
+        <v>0.875</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2945,39 +2950,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.255</v>
+        <v>2.82</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0036</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2115900</v>
+        <v>2887000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.66</v>
+        <v>0.19</v>
       </c>
       <c r="H56" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.236</v>
+        <v>2.796</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.212</v>
+        <v>2.667</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2990,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.545</v>
+        <v>1.18</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.0187</v>
+        <v>0.0351</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2078400</v>
+        <v>2871400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="H57" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.518</v>
+        <v>1.157</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.475</v>
+        <v>1.108</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3035,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.615</v>
+        <v>0.545</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.0789</v>
+        <v>0.0283</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1974700</v>
+        <v>2861800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>2.58</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>85.55</v>
+        <v>63.64</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.545</v>
+        <v>0.499</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.531</v>
+        <v>0.418</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3080,40 +3085,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.475</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1923700</v>
+        <v>2759100</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H59" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>1.3</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
     </row>
@@ -3125,40 +3123,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.0119</v>
+        <v>0.21</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1791500</v>
+        <v>2728200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H60" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>0.352</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
     </row>
@@ -3170,39 +3161,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.31</v>
+        <v>0.285</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1790000</v>
+        <v>2509400</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H61" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.29</v>
+        <v>0.294</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.278</v>
+        <v>0.31</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3215,39 +3206,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.305</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1743200</v>
+        <v>2413500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H62" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4.465</v>
+        <v>0.29</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.504</v>
+        <v>0.278</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3260,39 +3251,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2.83</v>
+        <v>1.65</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.0071</v>
+        <v>0.0185</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1723800</v>
+        <v>2385900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H63" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.86</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.797</v>
+        <v>1.701</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2.667</v>
+        <v>1.818</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3305,39 +3296,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.04</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1722400</v>
+        <v>2374100</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.28</v>
+        <v>0.74</v>
       </c>
       <c r="H64" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.91</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.772</v>
+        <v>0.236</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.757</v>
+        <v>0.213</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3350,28 +3341,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1722000</v>
+        <v>2291800</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H65" t="n">
-        <v>70.90000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3379,10 +3370,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.03</v>
+        <v>2.108</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.876</v>
+        <v>2.071</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3395,39 +3386,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>-0.0192</v>
+        <v>0.55</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.028</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1698800</v>
+        <v>2275900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>2.01</v>
+        <v>0.55</v>
       </c>
       <c r="H66" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.53</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.26</v>
+        <v>0.519</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.265</v>
+        <v>0.475</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3440,28 +3431,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0.0262</v>
+        <v>0.79</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1674800</v>
+        <v>2266900</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H67" t="n">
-        <v>71.45999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3469,10 +3460,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>3.804</v>
+        <v>0.772</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3.327</v>
+        <v>0.757</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3485,28 +3476,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7.28</v>
+        <v>4.23</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0254</v>
+        <v>0.0071</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1660200</v>
+        <v>2213500</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
       <c r="H68" t="n">
-        <v>65.56</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3514,10 +3505,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6.743</v>
+        <v>3.797</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>6.58</v>
+        <v>3.325</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3530,39 +3521,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0124</v>
+        <v>7.28</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1612600</v>
+        <v>2191400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H69" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.56</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.806</v>
+        <v>6.743</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.736</v>
+        <v>6.58</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3575,28 +3566,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.0702</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1603800</v>
+        <v>2134900</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.24</v>
+        <v>2.79</v>
       </c>
       <c r="H70" t="n">
-        <v>48.44</v>
+        <v>84.87</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3604,10 +3595,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.678</v>
+        <v>0.545</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.667</v>
+        <v>0.531</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3620,39 +3611,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.0488</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1536500</v>
+        <v>2087900</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>0.37</v>
       </c>
       <c r="H71" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.43</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.371</v>
+        <v>0.407</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.388</v>
+        <v>0.405</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3665,28 +3656,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>0.0435</v>
+        <v>0.865</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1480700</v>
+        <v>2082500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H72" t="n">
-        <v>65.26000000000001</v>
+        <v>54.49</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3694,10 +3685,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.222</v>
+        <v>0.861</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.193</v>
+        <v>0.857</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3710,28 +3701,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>5.16</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1472500</v>
+        <v>2037700</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.21</v>
+        <v>0.64</v>
       </c>
       <c r="H73" t="n">
-        <v>39.73</v>
+        <v>36.42</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -3739,10 +3730,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.155</v>
+        <v>5.612</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.153</v>
+        <v>5.737</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3755,39 +3746,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2.69</v>
+        <v>1.44</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0218</v>
+        <v>-0.0069</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1441200</v>
+        <v>2034600</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H74" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.6</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2.551</v>
+        <v>1.467</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2.198</v>
+        <v>1.47</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3800,39 +3791,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5.17</v>
+        <v>2.85</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0171</v>
+        <v>-0.0172</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1405900</v>
+        <v>1940000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="H75" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.37</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>5.613</v>
+        <v>2.717</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>5.737</v>
+        <v>2.545</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3845,39 +3836,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0.0397</v>
+        <v>0.415</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1371400</v>
+        <v>1930100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.25</v>
+        <v>0.73</v>
       </c>
       <c r="H76" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.45</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.646</v>
+        <v>0.388</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.66</v>
+        <v>0.352</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3890,28 +3881,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0.0278</v>
+        <v>2.71</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1369200</v>
+        <v>1924100</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H77" t="n">
-        <v>71.27</v>
+        <v>75.14</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3919,10 +3910,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.337</v>
+        <v>2.553</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.314</v>
+        <v>2.198</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3935,39 +3926,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.0141</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1366300</v>
+        <v>1905400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.96</v>
+        <v>0.46</v>
       </c>
       <c r="H78" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.477</v>
+        <v>0.371</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.472</v>
+        <v>0.388</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3980,28 +3971,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.0138</v>
+        <v>0.37</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1365000</v>
+        <v>1871500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="H79" t="n">
-        <v>59.96</v>
+        <v>71.27</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4009,10 +4000,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.718</v>
+        <v>0.337</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.545</v>
+        <v>0.314</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4025,28 +4016,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>-0.0377</v>
+        <v>4.3</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1361800</v>
+        <v>1842300</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H80" t="n">
-        <v>66.25</v>
+        <v>43.94</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -4054,10 +4045,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.945</v>
+        <v>4.465</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.789</v>
+        <v>4.504</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4070,39 +4061,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>-0.0192</v>
+        <v>2.49</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.0289</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1322200</v>
+        <v>1834900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H81" t="n">
-        <v>40.85</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.61</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.266</v>
+        <v>2.449</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.308</v>
+        <v>2.313</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4115,39 +4106,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.8</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1274100</v>
+        <v>1815000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="H82" t="n">
-        <v>73.19</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.99</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.987</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.776</v>
+        <v>0.737</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4160,39 +4151,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.89</v>
+        <v>0.675</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.015</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1259200</v>
+        <v>1806900</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="H83" t="n">
-        <v>72.78</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.48</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.448</v>
+        <v>0.678</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.888</v>
+        <v>0.667</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4205,39 +4196,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.23</v>
+        <v>0.57</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.025</v>
+        <v>0.0556</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1251500</v>
+        <v>1728800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="H84" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.255</v>
+        <v>0.514</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.295</v>
+        <v>0.424</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4250,39 +4241,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.0206</v>
+        <v>0.26</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1248600</v>
+        <v>1727100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H85" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.84</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3.556</v>
+        <v>0.267</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.685</v>
+        <v>0.308</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4295,28 +4286,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0</v>
+        <v>3.43</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1244100</v>
+        <v>1718400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="H86" t="n">
-        <v>39.48</v>
+        <v>37.28</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
@@ -4324,10 +4315,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.237</v>
+        <v>3.553</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.243</v>
+        <v>3.684</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4340,39 +4331,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.255</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1238800</v>
+        <v>1698800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.15</v>
+        <v>2.01</v>
       </c>
       <c r="H87" t="n">
-        <v>41.47</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.4</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>13.109</v>
+        <v>0.26</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>13.692</v>
+        <v>0.265</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4385,28 +4376,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2.83</v>
+        <v>13.04</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.0109</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1224600</v>
+        <v>1658100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="H88" t="n">
-        <v>75.59999999999999</v>
+        <v>43.08</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4414,10 +4405,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.455</v>
+        <v>13.113</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2.035</v>
+        <v>13.693</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4430,39 +4421,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.495</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1197300</v>
+        <v>1608800</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.08</v>
+        <v>1.13</v>
       </c>
       <c r="H89" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.63</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.446</v>
+        <v>0.476</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.312</v>
+        <v>0.472</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4475,28 +4466,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0048</v>
+        <v>0.24</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1177100</v>
+        <v>1582800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.06</v>
+        <v>1.04</v>
       </c>
       <c r="H90" t="n">
-        <v>43.4</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -4504,10 +4495,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.108</v>
+        <v>0.222</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.071</v>
+        <v>0.193</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4520,28 +4511,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0.0217</v>
+        <v>1.09</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1169700</v>
+        <v>1501000</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H91" t="n">
-        <v>56.91</v>
+        <v>39.73</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4549,10 +4540,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.452</v>
+        <v>1.155</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.417</v>
+        <v>1.153</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4565,39 +4556,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1143900</v>
+        <v>1492800</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H92" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.82</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.295</v>
+        <v>0.635</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.296</v>
+        <v>0.601</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4610,28 +4601,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1124600</v>
+        <v>1484100</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H93" t="n">
-        <v>56.51</v>
+        <v>45.4</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
@@ -4639,10 +4630,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.635</v>
+        <v>1.256</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.601</v>
+        <v>1.296</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4655,28 +4646,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.46</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1101500</v>
+        <v>1473600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H94" t="n">
-        <v>40.6</v>
+        <v>54.58</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4684,10 +4675,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.467</v>
+        <v>0.451</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.47</v>
+        <v>0.417</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4700,28 +4691,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>0.028</v>
+        <v>2.84</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1099500</v>
+        <v>1461300</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H95" t="n">
-        <v>50.63</v>
+        <v>71.11</v>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
@@ -4729,10 +4720,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.206</v>
+        <v>2.443</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2.113</v>
+        <v>1.887</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4745,39 +4736,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>9.98</v>
+        <v>1.17</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.003</v>
+        <v>0.0263</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1097900</v>
+        <v>1450400</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="H96" t="n">
-        <v>37.63</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.72</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>10.11</v>
+        <v>0.986</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>10.268</v>
+        <v>0.775</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4790,28 +4781,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.635</v>
+        <v>0.22</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0732</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1069500</v>
+        <v>1443700</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.31</v>
+        <v>1.87</v>
       </c>
       <c r="H97" t="n">
-        <v>57.04</v>
+        <v>61.31</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4819,10 +4810,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.609</v>
+        <v>0.208</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.609</v>
+        <v>0.201</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4835,28 +4826,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0054</v>
+        <v>0.65</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1050700</v>
+        <v>1413700</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="H98" t="n">
-        <v>24.04</v>
+        <v>50.4</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -4864,10 +4855,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>7.813</v>
+        <v>0.646</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4880,39 +4871,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.67</v>
+        <v>9.99</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.004</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1049800</v>
+        <v>1368800</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="H99" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.48</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.633</v>
+        <v>10.111</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.606</v>
+        <v>10.268</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4925,28 +4916,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>-0.011</v>
+        <v>2.8</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>995900</v>
+        <v>1354500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="H100" t="n">
-        <v>55.08</v>
+        <v>74.86</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4954,10 +4945,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.894</v>
+        <v>2.452</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.854</v>
+        <v>2.035</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4970,39 +4961,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2.52</v>
+        <v>0.675</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0227</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>993500</v>
+        <v>1315200</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.06</v>
+        <v>1.09</v>
       </c>
       <c r="H101" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.66</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.562</v>
+        <v>0.634</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2.46</v>
+        <v>0.606</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5015,28 +5006,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>0.016</v>
+        <v>7.41</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>956400</v>
+        <v>1310800</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H102" t="n">
-        <v>36.83</v>
+        <v>23.55</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
@@ -5044,10 +5035,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.31</v>
+        <v>7.811</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.416</v>
+        <v>8.196</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5060,28 +5051,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.555</v>
+        <v>0.635</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>955100</v>
+        <v>1305500</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="H103" t="n">
-        <v>62.32</v>
+        <v>57.04</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5089,10 +5080,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.512</v>
+        <v>0.609</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.424</v>
+        <v>0.609</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5105,28 +5096,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0.0164</v>
+        <v>0.225</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>923800</v>
+        <v>1244100</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.39</v>
+        <v>0.76</v>
       </c>
       <c r="H104" t="n">
-        <v>44.55</v>
+        <v>39.48</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5134,10 +5125,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.629</v>
+        <v>0.237</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.637</v>
+        <v>0.243</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5150,28 +5141,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>-0.0105</v>
+        <v>2.19</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>831100</v>
+        <v>1233000</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H105" t="n">
-        <v>37.18</v>
+        <v>49.94</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -5179,10 +5170,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.934</v>
+        <v>2.205</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.056</v>
+        <v>2.113</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5195,39 +5186,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>-0.0366</v>
+        <v>10.16</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.016</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>802000</v>
+        <v>1230200</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="H106" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.34999999999999</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.943</v>
+        <v>9.696</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.007</v>
+        <v>9.237</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5240,28 +5231,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>-0.0053</v>
+        <v>2.52</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>801700</v>
+        <v>1192200</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>35.66</v>
+        <v>47.67</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5269,10 +5260,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.957</v>
+        <v>2.562</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.967</v>
+        <v>2.46</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5285,39 +5276,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>798200</v>
+        <v>1188100</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H108" t="n">
-        <v>51.53</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.92</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.244</v>
+        <v>0.445</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1.16</v>
+        <v>0.44</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5330,28 +5321,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.865</v>
+        <v>1.86</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>798000</v>
+        <v>1171700</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="H109" t="n">
-        <v>54.49</v>
+        <v>34.65</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -5359,10 +5350,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.861</v>
+        <v>1.956</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.857</v>
+        <v>1.967</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5375,39 +5366,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>0.0131</v>
+        <v>0.215</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>797700</v>
+        <v>1157400</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="H110" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.72</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.922</v>
+        <v>0.23</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.739</v>
+        <v>0.245</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5420,28 +5411,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>10.18</v>
+        <v>0.625</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.018</v>
+        <v>0.0246</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>759100</v>
+        <v>1145000</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>68.70999999999999</v>
+        <v>46.91</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5449,10 +5440,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>9.696999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>9.237</v>
+        <v>0.637</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5465,39 +5456,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>-0.024</v>
+        <v>0.295</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>743400</v>
+        <v>1143900</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="H112" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.348</v>
+        <v>0.295</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.318</v>
+        <v>0.296</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5510,28 +5501,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.595</v>
+        <v>0.41</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0123</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>734500</v>
+        <v>1121000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="H113" t="n">
-        <v>56.79</v>
+        <v>57.1</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5539,10 +5530,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.573</v>
+        <v>0.4</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.576</v>
+        <v>0.383</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5555,39 +5546,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.028</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>680100</v>
+        <v>1068200</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H114" t="n">
-        <v>43.02</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>74.51000000000001</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.469</v>
+        <v>1.009</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1.51</v>
+        <v>0.841</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5600,28 +5591,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0.0026</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>677000</v>
+        <v>1067900</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H115" t="n">
-        <v>46.6</v>
+        <v>30.54</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -5629,10 +5620,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>7.783</v>
+        <v>0.58</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>7.749</v>
+        <v>0.585</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5645,39 +5636,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.755</v>
+        <v>7.68</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>-0.0066</v>
+        <v>-0.0013</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>669400</v>
+        <v>1013500</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="H116" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.03</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.759</v>
+        <v>7.781</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.742</v>
+        <v>7.748</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5690,28 +5681,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.91</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>663700</v>
+        <v>1007000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H117" t="n">
-        <v>52.78</v>
+        <v>59.12</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5719,10 +5710,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.093</v>
+        <v>0.895</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.119</v>
+        <v>0.855</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5735,28 +5726,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.028</v>
+        <v>0.016</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>663600</v>
+        <v>981600</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="H118" t="n">
-        <v>74.51000000000001</v>
+        <v>36.83</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -5764,10 +5755,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.009</v>
+        <v>1.31</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.841</v>
+        <v>1.416</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5780,28 +5771,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0115</v>
+        <v>-0.0105</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>637100</v>
+        <v>934100</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="H119" t="n">
-        <v>26.72</v>
+        <v>37.18</v>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
@@ -5809,10 +5800,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>4.603</v>
+        <v>1.934</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>4.923</v>
+        <v>2.056</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5825,28 +5816,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>0.0043</v>
+        <v>1.85</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0314</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>623700</v>
+        <v>922100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.04</v>
+        <v>0.52</v>
       </c>
       <c r="H120" t="n">
-        <v>32.83</v>
+        <v>32.4</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -5854,10 +5845,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>4.795</v>
+        <v>1.944</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>4.93</v>
+        <v>2.008</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5870,28 +5861,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>622900</v>
+        <v>916900</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H121" t="n">
-        <v>42.23</v>
+        <v>51.53</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
@@ -5899,10 +5890,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2.055</v>
+        <v>1.244</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.095</v>
+        <v>1.16</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5915,39 +5906,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.9</v>
+        <v>0.595</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>621300</v>
+        <v>907100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H122" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.79</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.971</v>
+        <v>0.573</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3.034</v>
+        <v>0.576</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5960,28 +5951,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>-0.0361</v>
+        <v>-0.0049</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>586800</v>
+        <v>899500</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H123" t="n">
-        <v>31.04</v>
+        <v>40.49</v>
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
@@ -5989,10 +5980,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.722</v>
+        <v>2.054</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1.839</v>
+        <v>2.095</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6005,39 +5996,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0</v>
+        <v>3.07</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>544000</v>
+        <v>890300</v>
       </c>
       <c r="G124" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="H124" t="n">
-        <v>23.51</v>
-      </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.29</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.087</v>
+        <v>2.92</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.139</v>
+        <v>2.739</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6050,39 +6041,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1</v>
+        <v>7.21</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.0309</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>533500</v>
+        <v>863400</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="H125" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.08</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.021</v>
+        <v>7.563</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.021</v>
+        <v>7.793</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6095,28 +6086,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0</v>
+        <v>1.47</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>524700</v>
+        <v>847100</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.82</v>
+        <v>0.38</v>
       </c>
       <c r="H126" t="n">
-        <v>65.81999999999999</v>
+        <v>31.03</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
@@ -6124,10 +6115,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.989</v>
+        <v>1.534</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.983</v>
+        <v>1.649</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6140,28 +6131,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0</v>
+        <v>4.3</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>506600</v>
+        <v>836200</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>28.3</v>
+        <v>26.72</v>
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
@@ -6169,10 +6160,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.629</v>
+        <v>4.603</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.761</v>
+        <v>4.923</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6185,28 +6176,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>6.43</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>500000</v>
+        <v>832900</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="H128" t="n">
-        <v>41.61</v>
+        <v>30.75</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -6214,16 +6205,1231 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.629</v>
+        <v>6.624</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.636</v>
+        <v>6.869</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>792400</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H129" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>773600</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H130" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>758500</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H131" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>743200</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H132" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>730700</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>3.438</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>726700</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>705200</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H135" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>4.795</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>695400</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H137" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>2.972</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>3.034</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>687200</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H138" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>685600</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H139" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>682800</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H140" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>673200</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H141" t="n">
+        <v>45.27</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>7.872</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>669000</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H142" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>667000</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H143" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>657600</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>630000</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H145" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1.948</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>629500</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H146" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>606800</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H147" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>596800</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H148" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>567200</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H149" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>564200</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H150" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>552100</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>544200</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H152" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>536500</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H153" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>2.664</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>533300</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H154" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>529000</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H155" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M128"/>
+  <autoFilter ref="A1:M155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00898781"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0556</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>64030300</v>
+        <v>206290000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.1</v>
+        <v>0.44</v>
       </c>
       <c r="H2" t="n">
-        <v>67.40000000000001</v>
+        <v>20.35</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.161</v>
+        <v>0.237</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.124</v>
+        <v>0.449</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.16</v>
+        <v>0.185</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0303</v>
+        <v>0.0278</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>51545600</v>
+        <v>74105400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.11</v>
+        <v>1.27</v>
       </c>
       <c r="H3" t="n">
-        <v>21.26</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.238</v>
+        <v>0.161</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.449</v>
+        <v>0.124</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -642,27 +642,27 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.1441</v>
+        <v>0.645</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.1622</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>35275400</v>
+        <v>56411300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.25</v>
+        <v>3.61</v>
       </c>
       <c r="H4" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+        <v>70.55</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.494</v>
@@ -689,19 +689,19 @@
       <c r="D5" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>0.03700000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>32632000</v>
+        <v>38767700</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="H5" t="n">
         <v>68.06</v>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -734,19 +734,19 @@
       <c r="D6" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="3" t="n">
         <v>-0.0133</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>23589200</v>
+        <v>26621000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H6" t="n">
         <v>68.93000000000001</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -777,30 +777,30 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.068</v>
+        <v>0.775</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0544</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22815000</v>
+        <v>25969700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="H7" t="n">
-        <v>61.68</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>60.07</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -822,27 +822,27 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>21720700</v>
+        <v>24160300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>8.48</v>
+        <v>9.44</v>
       </c>
       <c r="H8" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+        <v>76.25</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.08799999999999999</v>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.0202</v>
+        <v>0.605</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13846700</v>
+        <v>17721100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H9" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.475</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.473</v>
+        <v>0.496</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.51</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13570000</v>
+        <v>17159800</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>7.35</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>58.68</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.008</v>
+        <v>0.476</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.008</v>
+        <v>0.473</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.605</v>
+        <v>0.01</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12434900</v>
+        <v>16570000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.48</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>74.09999999999999</v>
+        <v>58.68</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.496</v>
+        <v>0.008</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-0.0625</v>
+        <v>0.0244</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11980000</v>
+        <v>15648500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H12" t="n">
-        <v>37.25</v>
+        <v>0.22</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.158</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1049,19 +1042,19 @@
       <c r="D13" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11083100</v>
+        <v>12248200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="n">
         <v>62.22</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1083,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8796700</v>
+        <v>12080000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H14" t="n">
-        <v>56.71</v>
+        <v>37.25</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.196</v>
+        <v>0.155</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.18</v>
+        <v>0.158</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1128,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.695</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.0775</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8082700</v>
+        <v>10695700</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.87</v>
+        <v>1.07</v>
       </c>
       <c r="H15" t="n">
-        <v>57.03</v>
+        <v>64.09</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.081</v>
+        <v>0.641</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.077</v>
+        <v>0.586</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1173,31 +1166,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8046000</v>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+        <v>9043500</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H16" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1209,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0105</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASIAPLY</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>5.51</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7916400</v>
+        <v>8918800</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>5.46</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>53.98</v>
+        <v>47.07</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.094</v>
+        <v>5.665</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>5.215</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,33 +1256,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.0196</v>
+        <v>0.78</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7616900</v>
+        <v>8654700</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
+        <v>0.63</v>
+      </c>
+      <c r="H18" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="J18" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.775</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1292,40 +1301,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.005</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7309700</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H19" t="n">
-        <v>52.97</v>
-      </c>
+        <v>8246000</v>
+      </c>
+      <c r="G19" s="5" t="n"/>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0.775</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
     </row>
@@ -1337,39 +1337,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0124</v>
+        <v>-0.0382</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7211900</v>
+        <v>8160200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.64</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
+        <v>65.02</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.742</v>
+        <v>0.704</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.697</v>
+        <v>0.635</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1382,39 +1382,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6859800</v>
+        <v>8139900</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
       <c r="H21" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
+        <v>64.67</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.32</v>
+        <v>0.742</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.337</v>
+        <v>0.697</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1427,39 +1427,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6661000</v>
+        <v>8103200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H22" t="n">
-        <v>71.3</v>
+        <v>57.03</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.283</v>
+        <v>0.081</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.272</v>
+        <v>0.077</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,39 +1472,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0105</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ASIAPLY</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0332</v>
+        <v>0.095</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6560300</v>
+        <v>8030400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.47</v>
+        <v>5.54</v>
       </c>
       <c r="H23" t="n">
-        <v>47.74</v>
+        <v>53.98</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.667</v>
+        <v>0.094</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5.216</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1517,39 +1517,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6404000</v>
+        <v>7766600</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="H24" t="n">
-        <v>28.59</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+        <v>50.19</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.594</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.804</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,40 +1562,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5929400</v>
+        <v>7756200</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>47.39</v>
+        <v>0.58</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0.078</v>
-      </c>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1607,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.8</v>
+        <v>0.865</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.0169</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5887300</v>
+        <v>7665700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>58.36</v>
+        <v>47.02</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.75</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.575</v>
+        <v>0.87</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1652,39 +1645,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.97</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.0849</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5603800</v>
+        <v>7660400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="H27" t="n">
-        <v>51.26</v>
+        <v>58.41</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.607</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.607</v>
+        <v>0.788</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.013</v>
+        <v>1.82</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5595700</v>
+        <v>7565700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.51</v>
+        <v>0.33</v>
       </c>
       <c r="H28" t="n">
-        <v>61.11</v>
+        <v>59.78</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.378</v>
+        <v>1.752</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.372</v>
+        <v>1.575</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1742,39 +1735,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5453200</v>
+        <v>7565500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.37</v>
+        <v>1.4</v>
       </c>
       <c r="H29" t="n">
-        <v>50.19</v>
+        <v>53.89</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.337</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1787,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5386800</v>
+        <v>7481500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H30" t="n">
-        <v>54.4</v>
+        <v>28.59</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.159</v>
+        <v>0.594</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.148</v>
+        <v>0.804</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1832,33 +1825,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.37</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5166000</v>
+        <v>7423000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.367</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
     </row>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.505</v>
+        <v>0.3</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5103200</v>
+        <v>7341400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="H32" t="n">
-        <v>27.69</v>
+        <v>68.89</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.545</v>
+        <v>0.282</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.582</v>
+        <v>0.272</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4842800</v>
+        <v>7081200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.82</v>
+        <v>1.39</v>
       </c>
       <c r="H33" t="n">
-        <v>75.34999999999999</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
+        <v>71.11</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.708</v>
+        <v>0.166</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.636</v>
+        <v>0.165</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.37</v>
+        <v>5.11</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.0137</v>
+        <v>-0.002</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4817700</v>
+        <v>6946700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="H34" t="n">
-        <v>52.92</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.367</v>
+        <v>4.862</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.367</v>
+        <v>4.581</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.026</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4671000</v>
+        <v>6773500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="H35" t="n">
-        <v>32.12</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
+        <v>63.81</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.265</v>
+        <v>0.378</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.317</v>
+        <v>0.372</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,39 +2050,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.61</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4573300</v>
+        <v>6713300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="H36" t="n">
-        <v>57.48</v>
+        <v>51.26</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.615</v>
+        <v>0.607</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2.543</v>
+        <v>0.607</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.0388</v>
+        <v>0.725</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4463500</v>
+        <v>6457200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="H37" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
+        <v>29.47</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.069</v>
+        <v>0.776</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.027</v>
+        <v>0.834</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,39 +2140,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0221</v>
+        <v>0.305</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4425500</v>
+        <v>6371400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="H38" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
+        <v>53.61</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.273</v>
+        <v>0.304</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.206</v>
+        <v>0.293</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.195</v>
+        <v>0.16</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.1143</v>
+        <v>-0.0303</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4337100</v>
+        <v>5971900</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="H39" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
+        <v>51.88</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.165</v>
+        <v>0.147</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,39 +2230,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.075</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4243300</v>
+        <v>5929400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="H40" t="n">
-        <v>47.02</v>
+        <v>47.39</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.868</v>
+        <v>0.076</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.87</v>
+        <v>0.078</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,39 +2275,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0.505</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4057300</v>
+        <v>5755100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.36</v>
+        <v>0.91</v>
       </c>
       <c r="H41" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+        <v>27.69</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.406</v>
+        <v>0.545</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.411</v>
+        <v>0.582</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.68</v>
+        <v>2.2</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.05429999999999999</v>
+        <v>-0.0265</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4015000</v>
+        <v>5709000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>61.81</v>
+        <v>44.8</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.64</v>
+        <v>2.272</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.586</v>
+        <v>2.206</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,39 +2365,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.0282</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>5423700</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="E43" s="8" t="n">
-        <v>-0.0069</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>3883500</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="H43" t="n">
-        <v>28.63</v>
+        <v>57.1</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.776</v>
+        <v>0.336</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.834</v>
+        <v>0.317</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,40 +2410,33 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.01</v>
+        <v>0.115</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0472</v>
+        <v>0.0455</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3788400</v>
+        <v>5416000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H44" t="n">
-        <v>64.52</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0.789</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
     </row>
@@ -2455,39 +2448,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.0291</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3744000</v>
+        <v>5031800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H45" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
+        <v>49.67</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.347</v>
+        <v>1.069</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.3</v>
+        <v>1.027</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,39 +2493,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.0192</v>
+        <v>1.29</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3672800</v>
+        <v>4985000</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H46" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="K46" s="2" t="n">
         <v>1.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>78.73</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0.418</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,39 +2538,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0.0323</v>
+        <v>3.76</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.033</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3306500</v>
+        <v>4881300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="H47" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+        <v>57.82</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.174</v>
+        <v>3.617</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.21</v>
+        <v>2.543</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,36 +2583,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.355</v>
+        <v>0.24</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3303000</v>
+        <v>4858900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="H48" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
+        <v>32.12</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.336</v>
+        <v>0.265</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0.317</v>
@@ -2635,39 +2628,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>1.06</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3268800</v>
+        <v>4767300</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
       <c r="H49" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
+        <v>64.67</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.142</v>
+        <v>1.028</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.15</v>
+        <v>0.875</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,39 +2673,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>0.0297</v>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3206900</v>
+        <v>4414500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.51</v>
+        <v>1.56</v>
       </c>
       <c r="H50" t="n">
-        <v>49.36</v>
+        <v>77.55</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.521</v>
+        <v>0.435</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.532</v>
+        <v>0.418</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,39 +2718,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.185</v>
+        <v>2.81</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3037300</v>
+        <v>4206100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H51" t="n">
-        <v>42.14</v>
+        <v>54.93</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.193</v>
+        <v>2.795</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.197</v>
+        <v>2.666</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,39 +2763,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5.13</v>
+        <v>0.395</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.002</v>
+        <v>-0.0125</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2958900</v>
+        <v>4097600</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H52" t="n">
-        <v>71.15000000000001</v>
+        <v>38.65</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.864</v>
+        <v>0.406</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4.581</v>
+        <v>0.411</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,39 +2808,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.1</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2948900</v>
+        <v>4053100</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="H53" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+        <v>36.77</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.769</v>
+        <v>0.121</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.771</v>
+        <v>0.156</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,39 +2853,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2899900</v>
+        <v>3948600</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H54" t="n">
-        <v>53.61</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
+        <v>35.9</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.304</v>
+        <v>0.174</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.293</v>
+        <v>0.21</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,39 +2898,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0185</v>
+        <v>0.125</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2894200</v>
+        <v>3835000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.24</v>
+        <v>4.32</v>
       </c>
       <c r="H55" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
+        <v>39.37</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.028</v>
+        <v>0.13</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.875</v>
+        <v>0.131</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,39 +2943,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0.0036</v>
+        <v>0.515</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0198</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2887000</v>
+        <v>3638800</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H56" t="n">
-        <v>55.84</v>
+        <v>47.67</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.796</v>
+        <v>0.521</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.667</v>
+        <v>0.532</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,39 +2988,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.18</v>
+        <v>2.81</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.0351</v>
+        <v>-0.031</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2871400</v>
+        <v>3628500</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="H57" t="n">
-        <v>54.88</v>
+        <v>57.09</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.157</v>
+        <v>2.713</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.108</v>
+        <v>2.544</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,39 +3033,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.0283</v>
+        <v>4.2</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2861800</v>
+        <v>3389900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H58" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
+        <v>69.31</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.499</v>
+        <v>3.794</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.418</v>
+        <v>3.325</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,33 +3078,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.475</v>
+        <v>0.79</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2759100</v>
+        <v>3343600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
+        <v>0.54</v>
+      </c>
+      <c r="H59" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
+      <c r="J59" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.757</v>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
     </row>
@@ -3123,33 +3123,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.0244</v>
+        <v>1.11</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2728200</v>
+        <v>3315100</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
+        <v>0.48</v>
+      </c>
+      <c r="H60" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1.154</v>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
     </row>
@@ -3161,39 +3168,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>0.13</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2509400</v>
+        <v>3298800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.36</v>
+        <v>0.84</v>
       </c>
       <c r="H61" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
+        <v>35.71</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.294</v>
+        <v>0.142</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3206,39 +3213,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.305</v>
+        <v>1.17</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0161</v>
+        <v>0.0263</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2413500</v>
+        <v>3221100</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H62" t="n">
-        <v>56.71</v>
+        <v>53.57</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.29</v>
+        <v>1.156</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.278</v>
+        <v>1.108</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3260,27 +3267,27 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.0185</v>
+        <v>1.66</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2385900</v>
+        <v>3196100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H63" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
+        <v>41.29</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.701</v>
+        <v>1.702</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>1.818</v>
@@ -3296,39 +3303,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0.04</v>
+        <v>0.37</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2374100</v>
+        <v>3174700</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="H64" t="n">
-        <v>64.91</v>
+        <v>71.27</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.236</v>
+        <v>0.337</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.213</v>
+        <v>0.314</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3341,39 +3348,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>-0.0048</v>
+        <v>0.012</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2291800</v>
+        <v>3169000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H65" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
+        <v>49.37</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.108</v>
+        <v>2.564</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.071</v>
+        <v>2.461</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3386,39 +3393,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.028</v>
+        <v>0.76</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2275900</v>
+        <v>3146000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H66" t="n">
-        <v>62.53</v>
+        <v>44.45</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.519</v>
+        <v>0.769</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.475</v>
+        <v>0.771</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3431,39 +3438,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.79</v>
+        <v>0.185</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2266900</v>
+        <v>3137300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H67" t="n">
-        <v>64.37</v>
+        <v>42.14</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.757</v>
+        <v>0.197</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3476,39 +3483,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0.0071</v>
+        <v>0.545</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2213500</v>
+        <v>3076100</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H68" t="n">
-        <v>69.93000000000001</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
+        <v>63.64</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.797</v>
+        <v>0.499</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>3.325</v>
+        <v>0.418</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3521,39 +3528,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0.0254</v>
+        <v>2.49</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.0289</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2191400</v>
+        <v>2989600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>65.56</v>
+        <v>57.61</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6.743</v>
+        <v>2.449</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.58</v>
+        <v>2.313</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3566,40 +3573,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0.0702</v>
+        <v>0.475</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2134900</v>
+        <v>2911000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="H70" t="n">
-        <v>84.87</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
+        <v>0.19</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J70" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>0.531</v>
-      </c>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
     </row>
@@ -3611,39 +3611,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.0488</v>
+        <v>0.285</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2087900</v>
+        <v>2862100</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H71" t="n">
-        <v>57.43</v>
+        <v>35.15</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.407</v>
+        <v>0.294</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.405</v>
+        <v>0.31</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3656,39 +3656,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>2.06</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2082500</v>
+        <v>2862000</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.68</v>
+        <v>0.16</v>
       </c>
       <c r="H72" t="n">
-        <v>54.49</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
+        <v>43.4</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.861</v>
+        <v>2.108</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.857</v>
+        <v>2.071</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3712,19 +3712,19 @@
       <c r="D73" s="2" t="n">
         <v>5.16</v>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="3" t="n">
         <v>-0.019</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2037700</v>
+        <v>2644000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H73" t="n">
         <v>36.42</v>
       </c>
-      <c r="I73" s="9" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3746,39 +3746,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.44</v>
+        <v>0.545</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.0187</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2034600</v>
+        <v>2617000</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H74" t="n">
-        <v>40.6</v>
+        <v>61.4</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.467</v>
+        <v>0.518</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.47</v>
+        <v>0.475</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3791,39 +3791,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.85</v>
+        <v>7.32</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0172</v>
+        <v>0.031</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1940000</v>
+        <v>2582900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="H75" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
+        <v>66.22</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.717</v>
+        <v>6.747</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.545</v>
+        <v>6.581</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3836,39 +3836,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.415</v>
+        <v>0.255</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0119</v>
+        <v>0.02</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1930100</v>
+        <v>2563500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="H76" t="n">
-        <v>62.45</v>
+        <v>63.2</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.388</v>
+        <v>0.236</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.352</v>
+        <v>0.212</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3881,39 +3881,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.71</v>
+        <v>0.425</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>-0.0145</v>
+        <v>0.0366</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1924100</v>
+        <v>2554500</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H77" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
+        <v>56.26</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.553</v>
+        <v>0.407</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.198</v>
+        <v>0.405</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3926,39 +3926,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.775</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1905400</v>
+        <v>2539000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="H78" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
+        <v>41.4</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.371</v>
+        <v>0.797</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.388</v>
+        <v>0.806</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3971,39 +3971,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.57</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1871500</v>
+        <v>2512400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.23</v>
+        <v>1.32</v>
       </c>
       <c r="H79" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.337</v>
+        <v>0.514</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.314</v>
+        <v>0.424</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4016,39 +4016,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4.3</v>
+        <v>0.305</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0412</v>
+        <v>-0.0161</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1842300</v>
+        <v>2506000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H80" t="n">
-        <v>43.94</v>
+        <v>56.71</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4.465</v>
+        <v>0.29</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>4.504</v>
+        <v>0.278</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4061,39 +4061,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.49</v>
+        <v>0.785</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.0289</v>
+        <v>-0.0248</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1834900</v>
+        <v>2494200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.12</v>
+        <v>0.78</v>
       </c>
       <c r="H81" t="n">
-        <v>57.61</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
+        <v>48.6</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.449</v>
+        <v>0.805</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.313</v>
+        <v>0.736</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4106,39 +4106,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.8</v>
+        <v>0.675</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>-0.0062</v>
+        <v>0.015</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1815000</v>
+        <v>2346800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.57</v>
+        <v>0.34</v>
       </c>
       <c r="H82" t="n">
-        <v>51.99</v>
+        <v>49.48</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.737</v>
+        <v>0.667</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4151,39 +4151,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0.015</v>
+        <v>10.26</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.026</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1806900</v>
+        <v>2339400</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.27</v>
+        <v>0.72</v>
       </c>
       <c r="H83" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
+        <v>70.08</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.678</v>
+        <v>9.705</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.667</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4196,39 +4196,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.0556</v>
+        <v>-0.0109</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1728800</v>
+        <v>2310900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.91</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>64.37</v>
+        <v>53.14</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.514</v>
+        <v>0.451</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.424</v>
+        <v>0.417</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4241,39 +4241,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1727100</v>
+        <v>2275200</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.17</v>
+        <v>0.82</v>
       </c>
       <c r="H85" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
+        <v>56.79</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.267</v>
+        <v>0.573</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.308</v>
+        <v>0.576</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4286,39 +4286,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.36</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1718400</v>
+        <v>2273700</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H86" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
+        <v>39.92</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.553</v>
+        <v>0.371</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3.684</v>
+        <v>0.388</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4331,39 +4331,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.255</v>
+        <v>3.42</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-0.0192</v>
+        <v>0.0059</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1698800</v>
+        <v>2258600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>2.01</v>
+        <v>0.39</v>
       </c>
       <c r="H87" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
+        <v>36.32</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.26</v>
+        <v>3.552</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.265</v>
+        <v>3.684</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4376,39 +4376,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>0.0109</v>
+        <v>4.3</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1658100</v>
+        <v>2249300</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H88" t="n">
-        <v>43.08</v>
+        <v>43.94</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>13.113</v>
+        <v>4.465</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>13.693</v>
+        <v>4.504</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4421,39 +4421,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.0614</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1608800</v>
+        <v>2238500</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1.13</v>
+        <v>2.92</v>
       </c>
       <c r="H89" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
+        <v>84.13</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.476</v>
+        <v>0.544</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.472</v>
+        <v>0.531</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4466,39 +4466,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.24</v>
+        <v>3.77</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.0435</v>
+        <v>-0.0383</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1582800</v>
+        <v>2212800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="H90" t="n">
-        <v>65.26000000000001</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
+        <v>52</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.222</v>
+        <v>3.798</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.193</v>
+        <v>3.476</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4511,39 +4511,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1501000</v>
+        <v>2193600</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.22</v>
+        <v>0.72</v>
       </c>
       <c r="H91" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
+        <v>54.49</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.155</v>
+        <v>0.861</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.153</v>
+        <v>0.857</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4556,39 +4556,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.64</v>
+        <v>1.44</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0069</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1492800</v>
+        <v>2168900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H92" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
+        <v>40.6</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.635</v>
+        <v>1.467</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.601</v>
+        <v>1.47</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4601,39 +4601,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.0333</v>
+        <v>13.02</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1484100</v>
+        <v>2154000</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H93" t="n">
-        <v>45.4</v>
+        <v>42.29</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.256</v>
+        <v>13.111</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.296</v>
+        <v>13.692</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4646,39 +4646,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0</v>
+        <v>2.8</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.021</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1473600</v>
+        <v>2140700</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="H94" t="n">
-        <v>54.58</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
+        <v>69.08</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.451</v>
+        <v>2.439</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.417</v>
+        <v>1.886</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4691,39 +4691,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>2.84</v>
+        <v>10.06</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.0111</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1461300</v>
+        <v>2126700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="H95" t="n">
-        <v>71.11</v>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
+        <v>43.84</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.443</v>
+        <v>10.118</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.887</v>
+        <v>10.27</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4736,39 +4736,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>0.0263</v>
+        <v>0.26</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1450400</v>
+        <v>2116700</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H96" t="n">
-        <v>72.72</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
+        <v>42.84</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.986</v>
+        <v>0.267</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.775</v>
+        <v>0.308</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4781,39 +4781,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0.0732</v>
+        <v>7.2</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1443700</v>
+        <v>2098100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1.87</v>
+        <v>0.3</v>
       </c>
       <c r="H97" t="n">
-        <v>61.31</v>
+        <v>31.52</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.208</v>
+        <v>7.562</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.201</v>
+        <v>7.793</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4826,39 +4826,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.65</v>
+        <v>0.415</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.0317</v>
+        <v>-0.0119</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1413700</v>
+        <v>2082400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1.29</v>
+        <v>0.79</v>
       </c>
       <c r="H98" t="n">
-        <v>50.4</v>
+        <v>62.45</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.646</v>
+        <v>0.388</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.66</v>
+        <v>0.352</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4871,39 +4871,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>9.99</v>
+        <v>7.44</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1368800</v>
+        <v>2026400</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H99" t="n">
-        <v>38.48</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
+        <v>24.29</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>10.111</v>
+        <v>7.814</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>10.268</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4916,39 +4916,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.0036</v>
+        <v>-0.0218</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1354500</v>
+        <v>2000400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="H100" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
+        <v>72.27</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.452</v>
+        <v>2.551</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.035</v>
+        <v>2.198</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4961,39 +4961,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>0.0227</v>
+        <v>1.27</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0.016</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1315200</v>
+        <v>1950200</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.09</v>
+        <v>0.17</v>
       </c>
       <c r="H101" t="n">
-        <v>64.66</v>
+        <v>36.83</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.634</v>
+        <v>1.31</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.606</v>
+        <v>1.416</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5006,39 +5006,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.008</v>
+        <v>1.86</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1310800</v>
+        <v>1928400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.13</v>
+        <v>0.45</v>
       </c>
       <c r="H102" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
+        <v>35.1</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>7.811</v>
+        <v>1.932</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>8.196</v>
+        <v>2.055</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5051,39 +5051,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.15</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1305500</v>
+        <v>1870100</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H103" t="n">
-        <v>57.04</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
+        <v>71.72</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.609</v>
+        <v>0.984</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.609</v>
+        <v>0.775</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>3.09</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1244100</v>
+        <v>1803400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="H104" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
+        <v>31.73</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.237</v>
+        <v>3.235</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.243</v>
+        <v>3.439</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5141,39 +5141,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>0.0234</v>
+        <v>7.69</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1233000</v>
+        <v>1754000</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="H105" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
+        <v>45.49</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.205</v>
+        <v>7.782</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.113</v>
+        <v>7.749</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5186,39 +5186,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>0.016</v>
+        <v>2.79</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1230200</v>
+        <v>1718900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="H106" t="n">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>9.696</v>
+        <v>2.451</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>9.237</v>
+        <v>2.034</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5231,39 +5231,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2.52</v>
+        <v>0.255</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.004</v>
+        <v>-0.0192</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1192200</v>
+        <v>1698800</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="H107" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
+        <v>37.4</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.562</v>
+        <v>0.26</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2.46</v>
+        <v>0.265</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5276,39 +5276,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1188100</v>
+        <v>1674600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H108" t="n">
-        <v>57.92</v>
+        <v>27.52</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.445</v>
+        <v>0.615</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.44</v>
+        <v>0.653</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5321,39 +5321,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.86</v>
+        <v>0.5</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1171700</v>
+        <v>1641000</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.17</v>
+        <v>1.16</v>
       </c>
       <c r="H109" t="n">
-        <v>34.65</v>
+        <v>59.08</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.956</v>
+        <v>0.477</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.967</v>
+        <v>0.472</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5366,39 +5366,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1157400</v>
+        <v>1619200</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.06</v>
+        <v>1.06</v>
       </c>
       <c r="H110" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.23</v>
+        <v>0.222</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.245</v>
+        <v>0.193</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5411,39 +5411,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>0.0246</v>
+        <v>0.22</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1145000</v>
+        <v>1612800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.49</v>
+        <v>2.09</v>
       </c>
       <c r="H111" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
+        <v>61.31</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.63</v>
+        <v>0.208</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.637</v>
+        <v>0.201</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5456,39 +5456,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.295</v>
+        <v>0.215</v>
       </c>
       <c r="E112" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1143900</v>
+        <v>1577400</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="H112" t="n">
-        <v>49.23</v>
+        <v>36.72</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.295</v>
+        <v>0.23</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.296</v>
+        <v>0.245</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5501,39 +5501,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>0.0123</v>
+        <v>1.24</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1121000</v>
+        <v>1549100</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="H113" t="n">
-        <v>57.1</v>
+        <v>45.4</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4</v>
+        <v>1.256</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.383</v>
+        <v>1.296</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5546,39 +5546,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.1</v>
+        <v>0.625</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.028</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1068200</v>
+        <v>1545200</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="H114" t="n">
-        <v>74.51000000000001</v>
+        <v>54.56</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.009</v>
+        <v>0.608</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.841</v>
+        <v>0.609</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5591,39 +5591,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1067900</v>
+        <v>1528200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H115" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
+        <v>59.82</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.58</v>
+        <v>0.635</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.585</v>
+        <v>0.601</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5636,39 +5636,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.68</v>
+        <v>4.7</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>-0.0013</v>
+        <v>0.0064</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1013500</v>
+        <v>1516800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H116" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
+        <v>34.44</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>7.781</v>
+        <v>4.796</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>7.748</v>
+        <v>4.93</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5681,39 +5681,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1007000</v>
+        <v>1489700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.19</v>
+        <v>1.36</v>
       </c>
       <c r="H117" t="n">
-        <v>59.12</v>
+        <v>49.29</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.895</v>
+        <v>0.646</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.855</v>
+        <v>0.66</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5726,39 +5726,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.016</v>
+        <v>-0.0163</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>981600</v>
+        <v>1446200</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H118" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
+        <v>48.44</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.31</v>
+        <v>1.242</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.416</v>
+        <v>1.159</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5771,39 +5771,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.0152</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>934100</v>
+        <v>1423800</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.22</v>
+        <v>1.18</v>
       </c>
       <c r="H119" t="n">
-        <v>37.18</v>
+        <v>63.59</v>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.934</v>
+        <v>0.633</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2.056</v>
+        <v>0.606</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5816,39 +5816,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>-0.0314</v>
+        <v>0.028</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>922100</v>
+        <v>1416300</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
       <c r="H120" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
+        <v>50.63</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.944</v>
+        <v>2.206</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.008</v>
+        <v>2.113</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5861,39 +5861,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.615</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>916900</v>
+        <v>1414300</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="H121" t="n">
-        <v>51.53</v>
+        <v>60.46</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.244</v>
+        <v>0.612</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.16</v>
+        <v>0.594</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5906,39 +5906,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.595</v>
+        <v>1.86</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0106</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>907100</v>
+        <v>1351800</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H122" t="n">
-        <v>56.79</v>
+        <v>34.65</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.573</v>
+        <v>1.956</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.576</v>
+        <v>1.967</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5951,39 +5951,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E123" s="8" t="n">
-        <v>-0.0049</v>
+        <v>0.225</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>899500</v>
+        <v>1349100</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.31</v>
+        <v>0.82</v>
       </c>
       <c r="H123" t="n">
-        <v>40.49</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
+        <v>39.48</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.054</v>
+        <v>0.237</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2.095</v>
+        <v>0.243</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5996,39 +5996,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>0.0066</v>
+        <v>1.08</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>890300</v>
+        <v>1338100</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H124" t="n">
-        <v>60.29</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.92</v>
+        <v>1.008</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.739</v>
+        <v>0.84</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6041,39 +6041,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.465</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>863400</v>
+        <v>1333500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.12</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>32.08</v>
+        <v>57.92</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>7.563</v>
+        <v>0.445</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>7.793</v>
+        <v>0.44</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6086,39 +6086,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E126" s="8" t="n">
-        <v>-0.0134</v>
+        <v>0.76</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>847100</v>
+        <v>1302300</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="H126" t="n">
-        <v>31.03</v>
+        <v>51.06</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.534</v>
+        <v>0.759</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.649</v>
+        <v>0.742</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6131,39 +6131,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>-0.0115</v>
+        <v>0.555</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>836200</v>
+        <v>1299200</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H127" t="n">
-        <v>26.72</v>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
+        <v>28.18</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>4.603</v>
+        <v>0.579</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>4.923</v>
+        <v>0.585</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6176,39 +6176,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>0.0063</v>
+        <v>0.41</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>832900</v>
+        <v>1279600</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.2</v>
+        <v>0.54</v>
       </c>
       <c r="H128" t="n">
-        <v>30.75</v>
+        <v>57.1</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>6.624</v>
+        <v>0.4</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>6.869</v>
+        <v>0.383</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6221,39 +6221,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1.22</v>
+        <v>0.265</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>-0.024</v>
+        <v>0.1042</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>792400</v>
+        <v>1275700</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
+        <v>53.45</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.348</v>
+        <v>0.263</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>1.318</v>
+        <v>0.225</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6266,39 +6266,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>-0.0102</v>
+        <v>2.02</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>773600</v>
+        <v>1268300</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="H130" t="n">
-        <v>58.26</v>
+        <v>40.49</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>3.808</v>
+        <v>2.054</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>3.478</v>
+        <v>2.095</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6311,39 +6311,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.735</v>
+        <v>4.29</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.0068</v>
+        <v>-0.0138</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>758500</v>
+        <v>1233400</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="H131" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
+        <v>26.42</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.732</v>
+        <v>4.602</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.75</v>
+        <v>4.922</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6356,39 +6356,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.62</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>743200</v>
+        <v>1206700</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
       <c r="H132" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
+        <v>44.55</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.092</v>
+        <v>0.629</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1.119</v>
+        <v>0.637</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6401,39 +6401,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>0.0033</v>
+        <v>2.91</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>0.0319</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>730700</v>
+        <v>1191800</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H133" t="n">
-        <v>26.4</v>
+        <v>57.97</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>3.231</v>
+        <v>2.809</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>3.438</v>
+        <v>2.724</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6446,39 +6446,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>3.06</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>0.0033</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>726700</v>
+        <v>1163300</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H134" t="n">
-        <v>29.84</v>
+        <v>59.85</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.024</v>
+        <v>2.919</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1.076</v>
+        <v>2.739</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6491,39 +6491,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>0.0043</v>
+        <v>0.295</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>705200</v>
+        <v>1158900</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.04</v>
+        <v>0.51</v>
       </c>
       <c r="H135" t="n">
-        <v>32.83</v>
+        <v>49.23</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>4.795</v>
+        <v>0.295</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>4.93</v>
+        <v>0.296</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6536,39 +6536,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>700000</v>
+        <v>1078200</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="H136" t="n">
-        <v>41.61</v>
+        <v>54.49</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.629</v>
+        <v>1.094</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.636</v>
+        <v>1.12</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6581,39 +6581,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.91</v>
+        <v>1.23</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>0.0069</v>
+        <v>-0.016</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>695400</v>
+        <v>1053100</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H137" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
+        <v>32.02</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>2.972</v>
+        <v>1.349</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>3.034</v>
+        <v>1.318</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6626,39 +6626,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>687200</v>
+        <v>1042000</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H138" t="n">
-        <v>43.02</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
+        <v>55.08</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.469</v>
+        <v>0.894</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.51</v>
+        <v>0.854</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6671,39 +6671,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E139" s="8" t="n">
-        <v>-0.0066</v>
+        <v>1.84</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.0366</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>685600</v>
+        <v>1027900</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="H139" t="n">
-        <v>49.79</v>
+        <v>31.44</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.759</v>
+        <v>1.943</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.742</v>
+        <v>2.007</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6716,39 +6716,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>0.0198</v>
+        <v>1.72</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>682800</v>
+        <v>1023000</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="H140" t="n">
-        <v>31.03</v>
-      </c>
-      <c r="I140" s="9" t="inlineStr">
+        <v>44.14</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.088</v>
+        <v>1.754</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6761,39 +6761,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>7.77</v>
+        <v>2.92</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>-0.0102</v>
+        <v>0.0104</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>673200</v>
+        <v>940500</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="H141" t="n">
-        <v>45.27</v>
+        <v>43.25</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>7.872</v>
+        <v>2.973</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>7.82</v>
+        <v>3.034</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6806,39 +6806,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.765</v>
+        <v>1.48</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.0268</v>
+        <v>-0.0067</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>669000</v>
+        <v>912400</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H142" t="n">
-        <v>69.95</v>
+        <v>32.31</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.72</v>
+        <v>1.535</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.713</v>
+        <v>1.649</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6851,39 +6851,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>0.0339</v>
+        <v>6.42</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>667000</v>
+        <v>876200</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1.27</v>
+        <v>0.21</v>
       </c>
       <c r="H143" t="n">
-        <v>82.59</v>
+        <v>29.72</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.647</v>
+        <v>6.623</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.563</v>
+        <v>6.868</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6896,39 +6896,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E144" s="8" t="n">
-        <v>-0.0204</v>
+        <v>7.85</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>657600</v>
+        <v>855900</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="H144" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
+        <v>49.2</v>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.698</v>
+        <v>7.879</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.627</v>
+        <v>7.822</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6952,19 +6952,19 @@
       <c r="D145" s="2" t="n">
         <v>1.72</v>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="3" t="n">
         <v>-0.0115</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>630000</v>
+        <v>833800</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H145" t="n">
         <v>24.92</v>
       </c>
-      <c r="I145" s="9" t="inlineStr">
+      <c r="I145" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6986,39 +6986,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.72</v>
+        <v>0.725</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.0118</v>
+        <v>-0.0136</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>629500</v>
+        <v>831800</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H146" t="n">
-        <v>44.14</v>
+        <v>59.74</v>
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.754</v>
+        <v>0.699</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>1.79</v>
+        <v>0.627</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7031,39 +7031,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.62</v>
+        <v>0.735</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>-0.0241</v>
+        <v>0.0068</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>606800</v>
+        <v>828200</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="H147" t="n">
-        <v>32.65</v>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
+        <v>49.62</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.724</v>
+        <v>0.732</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1.839</v>
+        <v>0.75</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7076,39 +7076,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>0.0309</v>
+        <v>1.84</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>0.0395</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>596800</v>
+        <v>816100</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.37</v>
+        <v>1.56</v>
       </c>
       <c r="H148" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
+        <v>83.09</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.021</v>
+        <v>1.648</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1.021</v>
+        <v>1.564</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7121,39 +7121,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>0.004</v>
+        <v>0.765</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>0.0268</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>567200</v>
+        <v>812400</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="H149" t="n">
-        <v>30.2</v>
+        <v>69.95</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2.63</v>
+        <v>0.72</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2.761</v>
+        <v>0.713</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7166,39 +7166,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.945</v>
+        <v>1.46</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.0069</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>564200</v>
+        <v>812300</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H150" t="n">
-        <v>34.19</v>
+        <v>45.53</v>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.985</v>
+        <v>1.47</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1.037</v>
+        <v>1.51</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7211,39 +7211,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E151" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.545</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>552100</v>
+        <v>807900</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H151" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
+        <v>36.47</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.615</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.653</v>
+        <v>0.59</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7256,39 +7256,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>544200</v>
+        <v>805100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1.32</v>
+        <v>0.2</v>
       </c>
       <c r="H152" t="n">
-        <v>54.24</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
+        <v>35.21</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.5</v>
+        <v>0.986</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0.499</v>
+        <v>1.037</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7301,39 +7301,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>0.0077</v>
+        <v>0.97</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>536500</v>
+        <v>800000</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H153" t="n">
-        <v>42.97</v>
+        <v>29.84</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>2.664</v>
+        <v>1.024</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>2.834</v>
+        <v>1.076</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7346,39 +7346,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.54</v>
+        <v>2.64</v>
       </c>
       <c r="E154" s="8" t="n">
-        <v>-0.0182</v>
+        <v>0.0154</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>533300</v>
+        <v>767200</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H154" t="n">
-        <v>34.54</v>
+        <v>44.91</v>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.665</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.59</v>
+        <v>2.834</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7391,45 +7391,1170 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.99</v>
+        <v>0.9</v>
       </c>
       <c r="E155" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>529000</v>
+        <v>744700</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.82</v>
+        <v>0.24</v>
       </c>
       <c r="H155" t="n">
-        <v>65.81999999999999</v>
+        <v>38.05</v>
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.989</v>
+        <v>0.92</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>1.983</v>
+        <v>0.968</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>744300</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H156" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>2.563</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>728500</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H157" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>720900</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H158" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H159" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E160" s="8" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>675600</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>669300</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H161" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>6.757</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>6.836</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>662000</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H162" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>661700</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H163" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>5.619</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>6.024</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H164" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>655800</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H165" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>4.986</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>5.045</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>635100</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H166" t="n">
+        <v>52.66</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>618000</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H167" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>609600</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H168" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>6.242</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>600900</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H169" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>598800</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H170" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>584800</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H171" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>572000</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H172" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>555700</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H173" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H174" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>1.513</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>532100</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H175" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E176" s="8" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>527700</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H176" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>527500</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H177" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>523700</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H178" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>523200</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="H179" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>510700</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H180" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M155"/>
+  <autoFilter ref="A1:M180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1212</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>206290000</v>
+        <v>241475600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.44</v>
+        <v>0.51</v>
       </c>
       <c r="H2" t="n">
-        <v>20.35</v>
+        <v>19.93</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         <v>0.0278</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>74105400</v>
+        <v>77218900</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="H3" t="n">
         <v>65.93000000000001</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.645</v>
+        <v>0.65</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.1622</v>
+        <v>0.1712</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>56411300</v>
+        <v>58548500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="H4" t="n">
-        <v>70.55</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.545</v>
+        <v>0.546</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.494</v>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.28</v>
+        <v>0.285</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>38767700</v>
+        <v>46748100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>68.06</v>
+        <v>69.36</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0133</v>
+        <v>0.775</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.0544</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>26621000</v>
+        <v>28384300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
-        <v>68.93000000000001</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.07</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.209</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.0544</v>
+        <v>0.375</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25969700</v>
+        <v>26821400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H7" t="n">
-        <v>60.07</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.16</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.125</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>24160300</v>
+        <v>25952500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>9.44</v>
+        <v>14.05</v>
       </c>
       <c r="H8" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.68</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.095</v>
+        <v>0.008</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.13</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.04</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17721100</v>
+        <v>24673100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.68</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>74.09999999999999</v>
+        <v>77.94</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.496</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.51</v>
+        <v>0.515</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.0303</v>
+        <v>0.0404</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17159800</v>
+        <v>19480000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="H10" t="n">
-        <v>64.04000000000001</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>16570000</v>
+        <v>18879600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>8.970000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H11" t="n">
-        <v>58.68</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.12</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.008</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.008</v>
+        <v>0.496</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.21</v>
+        <v>0.215</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.0244</v>
+        <v>0.0488</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>15648500</v>
+        <v>15672800</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.22</v>
@@ -1046,10 +1046,10 @@
         <v>0.05</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12248200</v>
+        <v>12653200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H13" t="n">
         <v>62.22</v>
@@ -1136,10 +1136,10 @@
         <v>0.0775</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10695700</v>
+        <v>11271200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H15" t="n">
         <v>64.09</v>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9043500</v>
+        <v>10798600</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.41</v>
+        <v>1.16</v>
       </c>
       <c r="H16" t="n">
-        <v>56.71</v>
+        <v>49.23</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.196</v>
+        <v>0.081</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.18</v>
+        <v>0.077</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0367</v>
+        <v>0.78</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8918800</v>
+        <v>10132000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H17" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5.665</v>
+        <v>0.774</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>5.215</v>
+        <v>0.775</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>5.54</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8654700</v>
+        <v>9511500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.09</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.774</v>
+        <v>5.668</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.775</v>
+        <v>5.216</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,31 +1301,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8246000</v>
-      </c>
-      <c r="G19" s="5" t="n"/>
+        <v>9043500</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H19" t="n">
+        <v>56.71</v>
+      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
     </row>
@@ -1337,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0382</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8160200</v>
+        <v>8895600</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.38</v>
+        <v>0.6</v>
       </c>
       <c r="H20" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.704</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.635</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1382,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.0124</v>
+        <v>0.75</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0446</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8139900</v>
+        <v>8653600</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.72</v>
+        <v>1.46</v>
       </c>
       <c r="H21" t="n">
-        <v>64.67</v>
+        <v>63.71</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1411,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.742</v>
+        <v>0.704</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.697</v>
+        <v>0.635</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1427,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>0105</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>ASIAPLY</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.095</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8103200</v>
+        <v>8514700</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.87</v>
+        <v>5.87</v>
       </c>
       <c r="H22" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.98</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.081</v>
+        <v>0.094</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.077</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,40 +1481,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0105</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASIAPLY</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.095</v>
+        <v>0.005</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8030400</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="H23" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0.08799999999999999</v>
-      </c>
+        <v>8246000</v>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1517,39 +1517,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+      <c r="E24" s="8" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7766600</v>
+        <v>8184600</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H24" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.741</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,33 +1562,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.865</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7756200</v>
+        <v>8052700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
+      </c>
+      <c r="H25" t="n">
+        <v>47.02</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+      <c r="J25" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.87</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1600,39 +1607,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.865</v>
+        <v>0.99</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.066</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7665700</v>
+        <v>8030200</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="H26" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.32</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.868</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.87</v>
+        <v>0.789</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,39 +1652,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-0.0849</v>
+        <v>0.205</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.1714</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7660400</v>
+        <v>8026000</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.93</v>
+        <v>1.58</v>
       </c>
       <c r="H27" t="n">
-        <v>58.41</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.59</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.166</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.788</v>
+        <v>0.165</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,19 +1706,19 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0339</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7565700</v>
+        <v>7921800</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H28" t="n">
-        <v>59.78</v>
+        <v>60.45</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1719,7 +1726,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.752</v>
+        <v>1.753</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1.575</v>
@@ -1735,40 +1742,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.33</v>
+        <v>0.265</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.0154</v>
+        <v>0.0392</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7565500</v>
+        <v>7807000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>53.89</v>
+        <v>0.58</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0.337</v>
-      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
     </row>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.515</v>
+        <v>0.335</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.0098</v>
+        <v>0.0308</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7481500</v>
+        <v>7677200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.2</v>
+        <v>1.43</v>
       </c>
       <c r="H30" t="n">
-        <v>28.59</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.04</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.594</v>
+        <v>0.321</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.804</v>
+        <v>0.337</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.155</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7423000</v>
+        <v>7612700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.13</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>52.92</v>
+        <v>32.21</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.367</v>
+        <v>0.174</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.367</v>
+        <v>0.21</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7341400</v>
+        <v>7550900</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="H32" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.41</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.282</v>
+        <v>0.594</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.272</v>
+        <v>0.804</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.0137</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7081200</v>
+        <v>7543000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="H33" t="n">
-        <v>71.11</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.92</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.166</v>
+        <v>0.367</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.165</v>
+        <v>0.367</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,28 +1960,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.002</v>
+        <v>0.305</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6946700</v>
+        <v>7411500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.28</v>
+        <v>1.21</v>
       </c>
       <c r="H34" t="n">
-        <v>69.95999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.862</v>
+        <v>0.283</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.581</v>
+        <v>0.272</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,28 +2005,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.026</v>
+        <v>5.1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6773500</v>
+        <v>7334700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>63.81</v>
+        <v>69.14</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.378</v>
+        <v>4.862</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.372</v>
+        <v>4.581</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.026</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6713300</v>
+        <v>7313600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H36" t="n">
-        <v>51.26</v>
+        <v>63.81</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.607</v>
+        <v>0.378</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.607</v>
+        <v>0.372</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.725</v>
+        <v>0.305</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6457200</v>
+        <v>7196400</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="H37" t="n">
-        <v>29.47</v>
+        <v>53.61</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.776</v>
+        <v>0.304</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.834</v>
+        <v>0.293</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,28 +2140,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6371400</v>
+        <v>6877800</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.33</v>
+        <v>1.44</v>
       </c>
       <c r="H38" t="n">
-        <v>53.61</v>
+        <v>28.63</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.304</v>
+        <v>0.776</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.293</v>
+        <v>0.834</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,28 +2185,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-0.0303</v>
+        <v>0.61</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5971900</v>
+        <v>6749300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="H39" t="n">
-        <v>51.88</v>
+        <v>51.26</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.158</v>
+        <v>0.607</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.147</v>
+        <v>0.607</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0221</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5929400</v>
+        <v>6541500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1.2</v>
+        <v>0.42</v>
       </c>
       <c r="H40" t="n">
-        <v>47.39</v>
+        <v>45.48</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.076</v>
+        <v>2.273</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.078</v>
+        <v>2.206</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5755100</v>
+        <v>6520000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="H41" t="n">
-        <v>27.69</v>
+        <v>64.67</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.545</v>
+        <v>1.028</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.582</v>
+        <v>0.875</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.0265</v>
+        <v>0.165</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5709000</v>
+        <v>6081100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="H42" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.272</v>
+        <v>0.159</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.206</v>
+        <v>0.148</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,40 +2365,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-0.0282</v>
+        <v>0.115</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5423700</v>
+        <v>6010800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H43" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0.317</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
     </row>
@@ -2410,33 +2403,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.075</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5416000</v>
+        <v>5929400</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.18</v>
+        <v>1.2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>47.39</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
+      <c r="J44" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.078</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
     </row>
@@ -2448,39 +2448,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>0.0291</v>
+        <v>0.355</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5031800</v>
+        <v>5819500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="H45" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.069</v>
+        <v>0.336</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.027</v>
+        <v>0.317</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2493,28 +2493,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.29</v>
+        <v>0.505</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4985000</v>
+        <v>5775500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.41</v>
+        <v>0.92</v>
       </c>
       <c r="H46" t="n">
-        <v>43.19</v>
+        <v>27.69</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.349</v>
+        <v>0.545</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.3</v>
+        <v>0.582</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2538,28 +2538,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.033</v>
+        <v>1.28</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4881300</v>
+        <v>5268400</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H47" t="n">
-        <v>57.82</v>
+        <v>42.17</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.617</v>
+        <v>1.348</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.543</v>
+        <v>1.3</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2583,39 +2583,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.0291</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4858900</v>
+        <v>5127000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H48" t="n">
-        <v>32.12</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.67</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.265</v>
+        <v>1.069</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.317</v>
+        <v>1.027</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2628,28 +2628,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.0185</v>
+        <v>3.75</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0.0302</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4767300</v>
+        <v>4983000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H49" t="n">
-        <v>64.67</v>
+        <v>57.65</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.028</v>
+        <v>3.616</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.875</v>
+        <v>2.543</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2673,28 +2673,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4414500</v>
+        <v>4940500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="H50" t="n">
-        <v>77.55</v>
+        <v>35.11</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.435</v>
+        <v>0.265</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.418</v>
+        <v>0.317</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2718,28 +2718,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>4.23</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4206100</v>
+        <v>4564700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="H51" t="n">
-        <v>54.93</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.795</v>
+        <v>3.797</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.666</v>
+        <v>3.325</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2763,39 +2763,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0125</v>
+        <v>0.525</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4097600</v>
+        <v>4535800</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.36</v>
+        <v>1.61</v>
       </c>
       <c r="H52" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.16</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.406</v>
+        <v>0.436</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.411</v>
+        <v>0.418</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2808,28 +2808,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.395</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4053100</v>
+        <v>4496400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H53" t="n">
-        <v>36.77</v>
+        <v>38.65</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.121</v>
+        <v>0.406</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.156</v>
+        <v>0.411</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2853,28 +2853,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.0323</v>
+        <v>0.13</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3948600</v>
+        <v>4449200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.19</v>
+        <v>5.01</v>
       </c>
       <c r="H54" t="n">
-        <v>35.9</v>
+        <v>47.54</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.174</v>
+        <v>0.131</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.21</v>
+        <v>0.131</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2898,39 +2898,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.0385</v>
+        <v>2.82</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3835000</v>
+        <v>4447500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>4.32</v>
+        <v>0.3</v>
       </c>
       <c r="H55" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.13</v>
+        <v>2.796</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.131</v>
+        <v>2.667</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2943,39 +2943,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0198</v>
+        <v>2.81</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3638800</v>
+        <v>4383600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H56" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.09</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.521</v>
+        <v>2.713</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.532</v>
+        <v>2.544</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2988,39 +2988,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.031</v>
+        <v>0.515</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0.0198</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3628500</v>
+        <v>3902700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="H57" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.713</v>
+        <v>0.521</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.544</v>
+        <v>0.532</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3033,28 +3033,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4.2</v>
+        <v>0.79</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3389900</v>
+        <v>3899200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="H58" t="n">
-        <v>69.31</v>
+        <v>64.37</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.794</v>
+        <v>0.772</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3.325</v>
+        <v>0.757</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3078,39 +3078,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3343600</v>
+        <v>3858500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.97</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.772</v>
+        <v>1.157</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.757</v>
+        <v>1.154</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3123,28 +3123,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.0183</v>
+        <v>0.0159</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3315100</v>
+        <v>3540200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="n">
-        <v>42.97</v>
+        <v>50.18</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.157</v>
+        <v>2.565</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.154</v>
+        <v>2.461</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3168,28 +3168,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.76</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3298800</v>
+        <v>3532000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="H61" t="n">
-        <v>35.71</v>
+        <v>44.45</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.142</v>
+        <v>0.769</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.15</v>
+        <v>0.771</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3213,28 +3213,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.17</v>
+        <v>1.66</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3221100</v>
+        <v>3428400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="H62" t="n">
-        <v>53.57</v>
+        <v>41.29</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.156</v>
+        <v>1.702</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.108</v>
+        <v>1.818</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3258,28 +3258,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0351</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3196100</v>
+        <v>3395500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>41.29</v>
+        <v>54.88</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.702</v>
+        <v>1.157</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.818</v>
+        <v>1.108</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3303,39 +3303,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.135</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3174700</v>
+        <v>3303300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.39</v>
+        <v>0.84</v>
       </c>
       <c r="H64" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.41</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.337</v>
+        <v>0.142</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.314</v>
+        <v>0.15</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.54</v>
+        <v>0.545</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.012</v>
+        <v>0.0283</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3169000</v>
+        <v>3287500</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.64</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.564</v>
+        <v>0.499</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.461</v>
+        <v>0.418</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3393,39 +3393,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.0066</v>
+        <v>0.115</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3146000</v>
+        <v>3286100</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H66" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.56</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.769</v>
+        <v>0.119</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.771</v>
+        <v>0.125</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3438,28 +3438,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3137300</v>
+        <v>3281800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
       <c r="H67" t="n">
-        <v>42.14</v>
+        <v>58.51</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.193</v>
+        <v>2.45</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.197</v>
+        <v>2.313</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3483,28 +3483,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.545</v>
+        <v>0.375</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.0417</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3076100</v>
+        <v>3244300</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H68" t="n">
-        <v>63.64</v>
+        <v>72.66</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.499</v>
+        <v>0.338</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.418</v>
+        <v>0.314</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3528,28 +3528,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.0289</v>
+        <v>0.18</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2989600</v>
+        <v>3237300</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="H69" t="n">
-        <v>57.61</v>
+        <v>39</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.449</v>
+        <v>0.192</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.313</v>
+        <v>0.197</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3573,33 +3573,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>7.44</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.0479</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2911000</v>
+        <v>3205800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.19</v>
+        <v>0.89</v>
+      </c>
+      <c r="H70" t="n">
+        <v>68.06999999999999</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
+      <c r="J70" s="2" t="n">
+        <v>6.759</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>6.583</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
     </row>
@@ -3611,28 +3618,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2862100</v>
+        <v>3001400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H71" t="n">
-        <v>35.15</v>
+        <v>43.4</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3640,10 +3647,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.294</v>
+        <v>2.108</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.31</v>
+        <v>2.071</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3656,40 +3663,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2.06</v>
+        <v>0.47</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>-0.0048</v>
+        <v>-0.0105</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2862000</v>
+        <v>2921900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H72" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>2.071</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3701,39 +3701,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.019</v>
+        <v>10.36</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.036</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2644000</v>
+        <v>2892300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H73" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.63</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>5.612</v>
+        <v>9.715</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5.737</v>
+        <v>9.241</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3746,39 +3746,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0175</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2617000</v>
+        <v>2887200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.48</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.518</v>
+        <v>0.295</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.475</v>
+        <v>0.31</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3791,39 +3791,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.031</v>
+        <v>5.17</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2582900</v>
+        <v>2834900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H75" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.62</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>6.747</v>
+        <v>5.613</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>6.581</v>
+        <v>5.737</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3836,39 +3836,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2563500</v>
+        <v>2781100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.8</v>
+        <v>0.27</v>
       </c>
       <c r="H76" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.84</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.236</v>
+        <v>0.267</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.212</v>
+        <v>0.308</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3881,28 +3881,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.425</v>
+        <v>0.55</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.0366</v>
+        <v>0.028</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2554500</v>
+        <v>2723700</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="H77" t="n">
-        <v>56.26</v>
+        <v>62.53</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.407</v>
+        <v>0.519</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.405</v>
+        <v>0.475</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3926,28 +3926,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0186</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2539000</v>
+        <v>2709700</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.53</v>
+        <v>0.84</v>
       </c>
       <c r="H78" t="n">
-        <v>41.4</v>
+        <v>49.68</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.797</v>
+        <v>0.806</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.806</v>
+        <v>0.736</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3971,28 +3971,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0.0556</v>
+        <v>0.305</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2512400</v>
+        <v>2675500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1.32</v>
+        <v>0.16</v>
       </c>
       <c r="H79" t="n">
-        <v>64.37</v>
+        <v>56.71</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.514</v>
+        <v>0.29</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.424</v>
+        <v>0.278</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4016,39 +4016,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.0161</v>
+        <v>0.26</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.04</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2506000</v>
+        <v>2663800</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.15</v>
+        <v>0.83</v>
       </c>
       <c r="H80" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.91</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.29</v>
+        <v>0.236</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.278</v>
+        <v>0.213</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4061,39 +4061,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>-0.0248</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2494200</v>
+        <v>2615200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.78</v>
+        <v>1.38</v>
       </c>
       <c r="H81" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.03</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.805</v>
+        <v>0.513</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.736</v>
+        <v>0.424</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4106,28 +4106,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.675</v>
+        <v>0.62</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.015</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2346800</v>
+        <v>2610100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.34</v>
+        <v>0.85</v>
       </c>
       <c r="H82" t="n">
-        <v>49.48</v>
+        <v>65.37</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.678</v>
+        <v>0.612</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.667</v>
+        <v>0.594</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4151,28 +4151,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10.26</v>
+        <v>0.425</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0366</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2339400</v>
+        <v>2581000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H83" t="n">
-        <v>70.08</v>
+        <v>56.26</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>9.705</v>
+        <v>0.407</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>9.239000000000001</v>
+        <v>0.405</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4196,28 +4196,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0109</v>
+        <v>0.775</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2310900</v>
+        <v>2551600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H84" t="n">
-        <v>53.14</v>
+        <v>41.4</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.451</v>
+        <v>0.797</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.417</v>
+        <v>0.806</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4241,39 +4241,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.86</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2275200</v>
+        <v>2519500</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.82</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.1</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.573</v>
+        <v>1.932</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.576</v>
+        <v>2.055</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4286,39 +4286,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0169</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2273700</v>
+        <v>2496400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="H86" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.93</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.371</v>
+        <v>0.573</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.388</v>
+        <v>0.576</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4331,28 +4331,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0.0059</v>
+        <v>3.79</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0332</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2258600</v>
+        <v>2484300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.39</v>
+        <v>0.82</v>
       </c>
       <c r="H87" t="n">
-        <v>36.32</v>
+        <v>53.03</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>3.552</v>
+        <v>3.8</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3.684</v>
+        <v>3.476</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4376,39 +4376,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4.3</v>
+        <v>0.675</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.0412</v>
+        <v>0.015</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2249300</v>
+        <v>2476700</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H88" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.48</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>4.465</v>
+        <v>0.678</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>4.504</v>
+        <v>0.667</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4421,39 +4421,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.605</v>
+        <v>7.21</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.0614</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2238500</v>
+        <v>2449400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2.92</v>
+        <v>0.35</v>
       </c>
       <c r="H89" t="n">
-        <v>84.13</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.08</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.544</v>
+        <v>7.563</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.531</v>
+        <v>7.793</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4466,28 +4466,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3.77</v>
+        <v>2.82</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.0383</v>
+        <v>-0.014</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2212800</v>
+        <v>2425200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H90" t="n">
-        <v>52</v>
+        <v>70.08</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>3.798</v>
+        <v>2.441</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3.476</v>
+        <v>1.887</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4511,28 +4511,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.865</v>
+        <v>0.455</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0109</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2193600</v>
+        <v>2422800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="H91" t="n">
-        <v>54.49</v>
+        <v>53.14</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4540,10 +4540,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.861</v>
+        <v>0.451</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.857</v>
+        <v>0.417</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4556,28 +4556,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0069</v>
+        <v>3.43</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2168900</v>
+        <v>2389100</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>0.42</v>
       </c>
       <c r="H92" t="n">
-        <v>40.6</v>
+        <v>37.28</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.467</v>
+        <v>3.553</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.47</v>
+        <v>3.684</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4601,39 +4601,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>13.02</v>
+        <v>4.3</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0412</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2154000</v>
+        <v>2305500</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H93" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.94</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>13.111</v>
+        <v>4.465</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>13.692</v>
+        <v>4.504</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4646,28 +4646,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>-0.021</v>
+        <v>10.02</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2140700</v>
+        <v>2298300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="H94" t="n">
-        <v>69.08</v>
+        <v>40.9</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.439</v>
+        <v>10.114</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.886</v>
+        <v>10.269</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4691,28 +4691,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>10.06</v>
+        <v>0.36</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>0.0111</v>
+        <v>0.0141</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2126700</v>
+        <v>2285700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="H95" t="n">
-        <v>43.84</v>
+        <v>39.92</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>10.118</v>
+        <v>0.371</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>10.27</v>
+        <v>0.388</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4736,28 +4736,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.0702</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2116700</v>
+        <v>2280400</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
       <c r="H96" t="n">
-        <v>42.84</v>
+        <v>84.87</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.267</v>
+        <v>0.545</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.308</v>
+        <v>0.531</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4781,28 +4781,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>1.44</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2098100</v>
+        <v>2214300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H97" t="n">
-        <v>31.52</v>
+        <v>40.6</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>7.562</v>
+        <v>1.467</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>7.793</v>
+        <v>1.47</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4826,28 +4826,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>-0.0119</v>
+        <v>13.04</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2082400</v>
+        <v>2201200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.79</v>
+        <v>0.26</v>
       </c>
       <c r="H98" t="n">
-        <v>62.45</v>
+        <v>43.08</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.388</v>
+        <v>13.113</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.352</v>
+        <v>13.693</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4871,28 +4871,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7.44</v>
+        <v>0.865</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.004</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2026400</v>
+        <v>2193600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="H99" t="n">
-        <v>24.29</v>
+        <v>54.49</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>7.814</v>
+        <v>0.861</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>0.857</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4916,39 +4916,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.69</v>
+        <v>7.46</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.0218</v>
+        <v>-0.0013</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2000400</v>
+        <v>2193200</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H100" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.81</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.551</v>
+        <v>7.816</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.198</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4961,39 +4961,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>0.016</v>
+        <v>0.42</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1950200</v>
+        <v>2119700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.17</v>
+        <v>0.8</v>
       </c>
       <c r="H101" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.5</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.31</v>
+        <v>0.389</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.416</v>
+        <v>0.352</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5006,28 +5006,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>-0.0211</v>
+        <v>1.27</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0.016</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1928400</v>
+        <v>2029400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="H102" t="n">
-        <v>35.1</v>
+        <v>36.83</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.932</v>
+        <v>1.31</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.055</v>
+        <v>1.416</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5051,28 +5051,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1870100</v>
+        <v>2020400</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H103" t="n">
-        <v>71.72</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.984</v>
+        <v>2.552</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.775</v>
+        <v>2.198</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>3.09</v>
+        <v>1.15</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>0.0164</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1803400</v>
+        <v>2017500</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="H104" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.72</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>3.235</v>
+        <v>0.984</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3.439</v>
+        <v>0.775</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1754000</v>
+        <v>1998900</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H105" t="n">
         <v>45.49</v>
@@ -5186,39 +5186,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>3.07</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1718900</v>
+        <v>1997800</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H106" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.17</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.451</v>
+        <v>3.233</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.034</v>
+        <v>3.439</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5231,39 +5231,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.0192</v>
+        <v>2.8</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1698800</v>
+        <v>1781300</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2.01</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.86</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.26</v>
+        <v>2.452</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.265</v>
+        <v>2.035</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5276,28 +5276,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1674600</v>
+        <v>1768000</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="H108" t="n">
-        <v>27.52</v>
+        <v>36.72</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.615</v>
+        <v>0.23</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.653</v>
+        <v>0.245</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5321,39 +5321,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>0.0101</v>
+        <v>0.555</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1641000</v>
+        <v>1713600</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.16</v>
+        <v>0.43</v>
       </c>
       <c r="H109" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.18</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.477</v>
+        <v>0.579</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.472</v>
+        <v>0.585</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5366,28 +5366,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.555</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1619200</v>
+        <v>1701900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="H110" t="n">
-        <v>65.26000000000001</v>
+        <v>26.65</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.222</v>
+        <v>0.615</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.193</v>
+        <v>0.653</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5411,39 +5411,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>0.0732</v>
+        <v>0.255</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1612800</v>
+        <v>1698800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="H111" t="n">
-        <v>61.31</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.4</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.208</v>
+        <v>0.26</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.201</v>
+        <v>0.265</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5456,28 +5456,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1577400</v>
+        <v>1685400</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H112" t="n">
-        <v>36.72</v>
+        <v>34.44</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.23</v>
+        <v>4.796</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.245</v>
+        <v>4.93</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5501,39 +5501,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1.24</v>
+        <v>0.5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0101</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1549100</v>
+        <v>1643000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.27</v>
+        <v>1.16</v>
       </c>
       <c r="H113" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.08</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.256</v>
+        <v>0.477</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1.296</v>
+        <v>0.472</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5555,19 +5555,19 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0159</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1545200</v>
+        <v>1631600</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="H114" t="n">
-        <v>54.56</v>
+        <v>53.24</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.608</v>
+        <v>0.607</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0.609</v>
@@ -5591,28 +5591,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.64</v>
+        <v>0.24</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0435</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1528200</v>
+        <v>1619200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H115" t="n">
-        <v>59.82</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.635</v>
+        <v>0.222</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.601</v>
+        <v>0.193</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5636,39 +5636,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>4.7</v>
+        <v>0.22</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.0732</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1516800</v>
+        <v>1613900</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.09</v>
+        <v>2.09</v>
       </c>
       <c r="H116" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.31</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>4.796</v>
+        <v>0.208</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>4.93</v>
+        <v>0.201</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5681,39 +5681,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.645</v>
+        <v>0.41</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>0.0238</v>
+        <v>0.0123</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1489700</v>
+        <v>1577200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.36</v>
+        <v>0.66</v>
       </c>
       <c r="H117" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.1</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.646</v>
+        <v>0.4</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.66</v>
+        <v>0.383</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         <v>-0.0163</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1446200</v>
+        <v>1570400</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H118" t="n">
         <v>48.44</v>
@@ -5771,39 +5771,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.67</v>
+        <v>1.23</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.025</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1423800</v>
+        <v>1558500</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>1.18</v>
+        <v>0.27</v>
       </c>
       <c r="H119" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.49</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.633</v>
+        <v>1.255</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.606</v>
+        <v>1.295</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5816,28 +5816,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.2</v>
+        <v>0.64</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>0.028</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1416300</v>
+        <v>1528200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H120" t="n">
-        <v>50.63</v>
+        <v>59.82</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.206</v>
+        <v>0.635</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.113</v>
+        <v>0.601</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5861,28 +5861,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1414300</v>
+        <v>1524300</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="H121" t="n">
-        <v>60.46</v>
+        <v>49.73</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.612</v>
+        <v>2.563</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.594</v>
+        <v>2.548</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5906,28 +5906,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.0106</v>
+        <v>0.65</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1351800</v>
+        <v>1508900</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.2</v>
+        <v>1.37</v>
       </c>
       <c r="H122" t="n">
-        <v>34.65</v>
+        <v>50.4</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.956</v>
+        <v>0.646</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.967</v>
+        <v>0.66</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5951,28 +5951,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>1.85</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1349100</v>
+        <v>1469400</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.82</v>
+        <v>0.21</v>
       </c>
       <c r="H123" t="n">
-        <v>39.48</v>
+        <v>33.7</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.237</v>
+        <v>1.956</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.243</v>
+        <v>1.967</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5996,28 +5996,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.08</v>
+        <v>2.19</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0234</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1338100</v>
+        <v>1449400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H124" t="n">
-        <v>72.54000000000001</v>
+        <v>49.94</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.008</v>
+        <v>2.205</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.84</v>
+        <v>2.113</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6041,28 +6041,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>0.67</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1333500</v>
+        <v>1442900</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.37</v>
+        <v>1.19</v>
       </c>
       <c r="H125" t="n">
-        <v>57.92</v>
+        <v>63.59</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.445</v>
+        <v>0.633</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.44</v>
+        <v>0.606</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6086,39 +6086,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0</v>
+        <v>4.3</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1302300</v>
+        <v>1376000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="H126" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.72</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.759</v>
+        <v>4.603</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.742</v>
+        <v>4.923</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6131,28 +6131,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>-0.0177</v>
+        <v>1.08</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1299200</v>
+        <v>1374200</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H127" t="n">
-        <v>28.18</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.579</v>
+        <v>1.008</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.585</v>
+        <v>0.84</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6176,28 +6176,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.41</v>
+        <v>2.93</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.039</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1279600</v>
+        <v>1365600</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H128" t="n">
-        <v>57.1</v>
+        <v>58.92</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.4</v>
+        <v>2.81</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.383</v>
+        <v>2.725</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6221,28 +6221,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E129" s="8" t="n">
-        <v>0.1042</v>
+        <v>0.225</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1275700</v>
+        <v>1349100</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.16</v>
+        <v>0.82</v>
       </c>
       <c r="H129" t="n">
-        <v>53.45</v>
+        <v>39.48</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.263</v>
+        <v>0.237</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.225</v>
+        <v>0.243</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6266,39 +6266,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>-0.0049</v>
+        <v>0.77</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1268300</v>
+        <v>1347500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H130" t="n">
-        <v>40.49</v>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.43</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>2.054</v>
+        <v>0.76</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>2.095</v>
+        <v>0.742</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6311,39 +6311,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>-0.0138</v>
+        <v>0.465</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1233400</v>
+        <v>1343500</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H131" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.92</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>4.602</v>
+        <v>0.445</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>4.922</v>
+        <v>0.44</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6356,28 +6356,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1206700</v>
+        <v>1281600</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.52</v>
+        <v>1.18</v>
       </c>
       <c r="H132" t="n">
-        <v>44.55</v>
+        <v>60.86</v>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
@@ -6385,10 +6385,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.629</v>
+        <v>1.183</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.637</v>
+        <v>1.196</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6401,39 +6401,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.91</v>
+        <v>0.265</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>0.0319</v>
+        <v>0.1042</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1191800</v>
+        <v>1275700</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="H133" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.809</v>
+        <v>0.263</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.724</v>
+        <v>0.225</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6446,39 +6446,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="E134" s="8" t="n">
-        <v>0.0033</v>
+        <v>2.02</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1163300</v>
+        <v>1273200</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H134" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.49</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.919</v>
+        <v>2.054</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.739</v>
+        <v>2.095</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6491,28 +6491,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1158900</v>
+        <v>1232700</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="H135" t="n">
-        <v>49.23</v>
+        <v>46.91</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.295</v>
+        <v>0.63</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.296</v>
+        <v>0.637</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6536,28 +6536,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.12</v>
+        <v>3.09</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0131</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1078200</v>
+        <v>1208700</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="H136" t="n">
-        <v>54.49</v>
+        <v>61.15</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.094</v>
+        <v>2.922</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.12</v>
+        <v>2.739</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6581,39 +6581,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>-0.016</v>
+        <v>0.24</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1053100</v>
+        <v>1207300</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="H137" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.31</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.349</v>
+        <v>0.223</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.318</v>
+        <v>0.203</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6626,28 +6626,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.011</v>
+        <v>1.13</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>0.0463</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1042000</v>
+        <v>1201100</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="H138" t="n">
-        <v>55.08</v>
+        <v>56.07</v>
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.894</v>
+        <v>1.095</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.854</v>
+        <v>1.12</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6671,39 +6671,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>-0.0366</v>
+        <v>0.295</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1027900</v>
+        <v>1158900</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="H139" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.943</v>
+        <v>0.295</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2.007</v>
+        <v>0.296</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6716,28 +6716,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E140" s="8" t="n">
-        <v>0.0118</v>
+        <v>1.71</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1023000</v>
+        <v>1103200</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="H140" t="n">
-        <v>44.14</v>
+        <v>24.21</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.754</v>
+        <v>1.859</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1.79</v>
+        <v>1.948</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6761,28 +6761,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E141" s="8" t="n">
-        <v>0.0104</v>
+        <v>1.22</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>940500</v>
+        <v>1073900</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H141" t="n">
-        <v>43.25</v>
+        <v>31.16</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.973</v>
+        <v>1.348</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>3.034</v>
+        <v>1.318</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6806,39 +6806,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0067</v>
+        <v>-0.011</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>912400</v>
+        <v>1066100</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H142" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.535</v>
+        <v>0.894</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.649</v>
+        <v>0.854</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6851,28 +6851,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="E143" s="8" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.84</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>-0.0366</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>876200</v>
+        <v>1057900</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="H143" t="n">
-        <v>29.72</v>
+        <v>31.44</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>6.623</v>
+        <v>1.943</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>6.868</v>
+        <v>2.007</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6896,28 +6896,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>1.82</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>855900</v>
+        <v>1031000</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.24</v>
+        <v>1.97</v>
       </c>
       <c r="H144" t="n">
-        <v>49.2</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>7.879</v>
+        <v>1.646</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>7.822</v>
+        <v>1.563</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6941,39 +6941,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-0.0115</v>
+        <v>0.34</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>833800</v>
+        <v>1024800</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="H145" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.68</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.86</v>
+        <v>0.339</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.948</v>
+        <v>0.334</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6986,39 +6986,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.0136</v>
+        <v>1.71</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>831800</v>
+        <v>1023200</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H146" t="n">
-        <v>59.74</v>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.66</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.699</v>
+        <v>1.754</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.627</v>
+        <v>1.789</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7031,28 +7031,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E147" s="8" t="n">
-        <v>0.0068</v>
+        <v>1.47</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>828200</v>
+        <v>961000</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="H147" t="n">
-        <v>49.62</v>
+        <v>31.03</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.732</v>
+        <v>1.534</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.75</v>
+        <v>1.649</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7076,39 +7076,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.84</v>
+        <v>2.91</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>0.0395</v>
+        <v>0.0069</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>816100</v>
+        <v>960900</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1.56</v>
+        <v>0.34</v>
       </c>
       <c r="H148" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.1</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.648</v>
+        <v>2.972</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1.564</v>
+        <v>3.034</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7121,28 +7121,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.765</v>
+        <v>7.87</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.0025</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>812400</v>
+        <v>905900</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H149" t="n">
-        <v>69.95</v>
+        <v>50.27</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.72</v>
+        <v>7.881</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.713</v>
+        <v>7.822</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7166,39 +7166,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.46</v>
+        <v>6.42</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>812300</v>
+        <v>904300</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="H150" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.72</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>1.47</v>
+        <v>6.623</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1.51</v>
+        <v>6.868</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7211,39 +7211,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.545</v>
+        <v>0.72</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.0091</v>
+        <v>-0.0204</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>807900</v>
+        <v>849500</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H151" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.59</v>
+        <v>0.627</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7256,28 +7256,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.95</v>
+        <v>0.965</v>
       </c>
       <c r="E152" s="3" t="n">
         <v>-0.0052</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>805100</v>
+        <v>843200</v>
       </c>
       <c r="G152" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="H152" t="n">
-        <v>35.21</v>
+        <v>29.01</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.986</v>
+        <v>1.023</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.037</v>
+        <v>1.076</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7301,39 +7301,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>800000</v>
+        <v>839400</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H153" t="n">
-        <v>29.84</v>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.024</v>
+        <v>1.47</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.076</v>
+        <v>1.51</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7346,39 +7346,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E154" s="8" t="n">
-        <v>0.0154</v>
+        <v>0.545</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>767200</v>
+        <v>838300</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="H154" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.47</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.665</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.834</v>
+        <v>0.59</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7391,28 +7391,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
+        <v>2.63</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>744700</v>
+        <v>837600</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H155" t="n">
-        <v>38.05</v>
+        <v>43.95</v>
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.92</v>
+        <v>2.665</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.968</v>
+        <v>2.834</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7436,39 +7436,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2.56</v>
+        <v>0.735</v>
       </c>
       <c r="E156" s="8" t="n">
-        <v>0.0039</v>
+        <v>0.0068</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>744300</v>
+        <v>831500</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H156" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="I156" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.62</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>2.563</v>
+        <v>0.732</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2.548</v>
+        <v>0.75</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7481,28 +7481,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.995</v>
+        <v>0.765</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>0.0258</v>
+        <v>0.0268</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>728500</v>
+        <v>812400</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H157" t="n">
-        <v>46.33</v>
+        <v>69.95</v>
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.021</v>
+        <v>0.72</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1.02</v>
+        <v>0.713</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7526,28 +7526,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.95</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>720900</v>
+        <v>807100</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H158" t="n">
-        <v>27.46</v>
+        <v>35.21</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.088</v>
+        <v>0.986</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.139</v>
+        <v>1.037</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7571,39 +7571,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.625</v>
+        <v>6.75</v>
       </c>
       <c r="E159" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>700000</v>
+        <v>804900</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H159" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.629</v>
+        <v>6.757</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0.636</v>
+        <v>6.836</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7616,39 +7616,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>2.53</v>
+        <v>5.59</v>
       </c>
       <c r="E160" s="8" t="n">
-        <v>0.008</v>
+        <v>0.0201</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>675600</v>
+        <v>793900</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="H160" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.08</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>2.631</v>
+        <v>5.619</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2.762</v>
+        <v>6.024</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7661,28 +7661,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>6.75</v>
+        <v>0.9</v>
       </c>
       <c r="E161" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>669300</v>
+        <v>777300</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H161" t="n">
-        <v>49.06</v>
+        <v>38.05</v>
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>6.757</v>
+        <v>0.92</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>6.836</v>
+        <v>0.968</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>-0.0033</v>
+        <v>-0.0066</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>662000</v>
+        <v>773500</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H162" t="n">
-        <v>55.58</v>
+        <v>54.47</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2.961</v>
+        <v>2.96</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>2.911</v>
@@ -7751,39 +7751,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E163" s="8" t="n">
-        <v>0.0201</v>
+        <v>1.51</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>661700</v>
+        <v>766200</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.35</v>
+        <v>1.01</v>
       </c>
       <c r="H163" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.83</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>5.619</v>
+        <v>1.565</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>6.024</v>
+        <v>1.513</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7796,39 +7796,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>-0.0181</v>
+        <v>0.995</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>0.0258</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>656600</v>
+        <v>745300</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H164" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.725</v>
+        <v>1.021</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1.839</v>
+        <v>1.02</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7841,39 +7841,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E165" s="8" t="n">
-        <v>0.006</v>
+        <v>0.62</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>655800</v>
+        <v>740000</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.14</v>
+        <v>0.73</v>
       </c>
       <c r="H165" t="n">
-        <v>52.72</v>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.04</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>4.986</v>
+        <v>0.629</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>5.045</v>
+        <v>0.636</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7886,39 +7886,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>635100</v>
+        <v>735800</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H166" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.46</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.634</v>
+        <v>1.088</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.629</v>
+        <v>1.139</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7931,28 +7931,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>-0.0166</v>
+        <v>5.03</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>0.006</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>618000</v>
+        <v>724200</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="H167" t="n">
-        <v>50.33</v>
+        <v>52.72</v>
       </c>
       <c r="I167" s="9" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.906</v>
+        <v>4.986</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>5.045</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7976,28 +7976,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>6.1</v>
+        <v>2.53</v>
       </c>
       <c r="E168" s="8" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>609600</v>
+        <v>694900</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="H168" t="n">
-        <v>38.07</v>
+        <v>32.01</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>6.242</v>
+        <v>2.631</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>6.451</v>
+        <v>2.762</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8021,28 +8021,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E169" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.895</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>600900</v>
+        <v>669700</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H169" t="n">
-        <v>58.46</v>
+        <v>51.2</v>
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.627</v>
+        <v>0.906</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.59</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8066,28 +8066,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.51</v>
+        <v>6.1</v>
       </c>
       <c r="E170" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>598800</v>
+        <v>661900</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1.46</v>
+        <v>0.05</v>
       </c>
       <c r="H170" t="n">
-        <v>56.71</v>
+        <v>38.07</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.501</v>
+        <v>6.242</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0.499</v>
+        <v>6.451</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8126,10 +8126,10 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>584800</v>
+        <v>658600</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H171" t="n">
         <v>61.09</v>
@@ -8156,28 +8156,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E172" s="8" t="n">
-        <v>0.0283</v>
+        <v>1.63</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>572000</v>
+        <v>656600</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H172" t="n">
-        <v>36.71</v>
+        <v>33.52</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>1.128</v>
+        <v>1.725</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>1.171</v>
+        <v>1.839</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8201,39 +8201,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.99</v>
+        <v>0.635</v>
       </c>
       <c r="E173" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>555700</v>
+        <v>635100</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.86</v>
+        <v>0.46</v>
       </c>
       <c r="H173" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.66</v>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1.989</v>
+        <v>0.634</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1.983</v>
+        <v>0.629</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8246,39 +8246,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>541200</v>
+        <v>627400</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.71</v>
+        <v>0.32</v>
       </c>
       <c r="H174" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="I174" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1.565</v>
+        <v>0.596</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>1.513</v>
+        <v>0.509</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8291,39 +8291,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0.65</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>532100</v>
+        <v>600900</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H175" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.46</v>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.963</v>
+        <v>0.627</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>1.001</v>
+        <v>0.59</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8336,39 +8336,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>MKH</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E176" s="8" t="n">
-        <v>0.0179</v>
+        <v>1.99</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>527700</v>
+        <v>600500</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.35</v>
+        <v>0.93</v>
       </c>
       <c r="H176" t="n">
-        <v>57.88</v>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.099</v>
+        <v>1.989</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.07</v>
+        <v>1.983</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8381,28 +8381,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>-0.0073</v>
+        <v>0.51</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>527500</v>
+        <v>598800</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.18</v>
+        <v>1.46</v>
       </c>
       <c r="H177" t="n">
-        <v>54.45</v>
+        <v>56.71</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>1.353</v>
+        <v>0.501</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1.19</v>
+        <v>0.499</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8426,39 +8426,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>-0.029</v>
+        <v>1.08</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>523700</v>
+        <v>588400</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="H178" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.38</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1.143</v>
+        <v>1.127</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.171</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8471,39 +8471,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>KKB</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E179" s="8" t="n">
-        <v>0.075</v>
+        <v>0.925</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>523200</v>
+        <v>583600</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>14.66</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="I179" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.86</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>1.139</v>
+        <v>0.964</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>1.09</v>
+        <v>1.001</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8516,45 +8516,315 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.665</v>
+        <v>1.35</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>-0.0075</v>
+        <v>-0.0146</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>510700</v>
+        <v>566200</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H180" t="n">
-        <v>72.95999999999999</v>
-      </c>
-      <c r="I180" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.24</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.597</v>
+        <v>1.352</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>0.509</v>
+        <v>1.19</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>561300</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H181" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>561000</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H182" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>539700</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H183" t="n">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>533000</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H184" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>4.607</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>523200</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="H185" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>505300</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H186" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M180"/>
+  <autoFilter ref="A1:M186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
+++ b/docs/downloads/2026-10-02/bursa-report-2026-10-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-02" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-02'!$A$1:$M$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.1212</v>
+        <v>-0.1515</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>241475600</v>
+        <v>366062000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="H2" t="n">
-        <v>19.93</v>
+        <v>19.52</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.237</v>
+        <v>0.236</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.449</v>
@@ -603,10 +603,10 @@
         <v>0.0278</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>77218900</v>
+        <v>78331300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
         <v>65.93000000000001</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.65</v>
+        <v>0.655</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.1712</v>
+        <v>0.1802</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>58548500</v>
+        <v>59612700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="H4" t="n">
-        <v>71.04000000000001</v>
+        <v>71.52</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.0556</v>
+        <v>0.0741</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46748100</v>
+        <v>50266500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>69.36</v>
+        <v>70.55</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.244</v>
+        <v>0.245</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0.234</v>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.775</v>
+        <v>0.77</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.0544</v>
+        <v>0.0476</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>28384300</v>
+        <v>29482700</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H6" t="n">
-        <v>60.07</v>
+        <v>59.21</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.6899999999999999</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>26821400</v>
+        <v>27127400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H7" t="n">
-        <v>71.16</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         <v>0.04</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>24673100</v>
+        <v>25067300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>77.94</v>
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.515</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.0404</v>
+        <v>0.0303</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>19480000</v>
+        <v>22972600</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>65.29000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.0083</v>
+        <v>0.605</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>18879600</v>
+        <v>19440000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H11" t="n">
-        <v>75.12</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>0.0488</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>15672800</v>
+        <v>17409100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         <v>0.05</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12653200</v>
+        <v>12776200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H13" t="n">
         <v>62.22</v>
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.0625</v>
+        <v>-0.0313</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12080000</v>
+        <v>12122000</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.46</v>
       </c>
       <c r="H14" t="n">
-        <v>37.25</v>
+        <v>46.33</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0.158</v>
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.695</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.0775</v>
+        <v>0.0698</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11271200</v>
+        <v>11671500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="H15" t="n">
-        <v>64.09</v>
+        <v>63.36</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10798600</v>
+        <v>10912900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.16</v>
+        <v>0.58</v>
       </c>
       <c r="H16" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.081</v>
+        <v>0.868</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.077</v>
+        <v>0.87</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.08</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10132000</v>
+        <v>10798700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.74</v>
+        <v>1.16</v>
       </c>
       <c r="H17" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.774</v>
+        <v>0.081</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.775</v>
+        <v>0.077</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.0315</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9511500</v>
+        <v>10721600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H18" t="n">
-        <v>48.09</v>
+        <v>50.19</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5.668</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5.216</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.2</v>
+        <v>0.155</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9043500</v>
+        <v>10586700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>56.71</v>
+        <v>32.21</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.196</v>
+        <v>0.174</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>5.59</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8895600</v>
+        <v>10432200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H20" t="n">
-        <v>50.19</v>
+        <v>49.88</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.673</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>5.217</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0446</v>
+        <v>0.78</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8653600</v>
+        <v>10132000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.46</v>
+        <v>0.74</v>
       </c>
       <c r="H21" t="n">
-        <v>63.71</v>
+        <v>52.97</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.704</v>
+        <v>0.774</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.635</v>
+        <v>0.775</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0105</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASIAPLY</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>1.84</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0395</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8514700</v>
+        <v>10098500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>5.87</v>
+        <v>0.45</v>
       </c>
       <c r="H22" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.1</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.094</v>
+        <v>1.753</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,31 +1481,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8246000</v>
-      </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+        <v>9565800</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H23" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.165</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1517,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.195</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8184600</v>
+        <v>9102000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.18</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.741</v>
+        <v>0.196</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.697</v>
+        <v>0.18</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8052700</v>
+        <v>9101400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>47.02</v>
+        <v>65.22</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.868</v>
+        <v>0.742</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.87</v>
+        <v>0.697</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1607,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.066</v>
+        <v>-0.0318</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8030200</v>
+        <v>9100600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.97</v>
+        <v>1.53</v>
       </c>
       <c r="H26" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.39</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.789</v>
+        <v>0.636</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1652,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.1714</v>
+        <v>0.305</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8026000</v>
+        <v>8660600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.58</v>
+        <v>0.44</v>
       </c>
       <c r="H27" t="n">
-        <v>72.59</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.166</v>
+        <v>0.304</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.165</v>
+        <v>0.293</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,28 +1706,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.985</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.0708</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7921800</v>
+        <v>8603400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.35</v>
+        <v>1.04</v>
       </c>
       <c r="H28" t="n">
-        <v>60.45</v>
+        <v>60.56</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1726,10 +1735,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.753</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.575</v>
+        <v>0.789</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1742,33 +1751,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.51</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7807000</v>
+        <v>8546200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
+        <v>0.23</v>
+      </c>
+      <c r="H29" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.804</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
     </row>
@@ -1780,28 +1796,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0105</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>ASIAPLY</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.0308</v>
+        <v>0.095</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7677200</v>
+        <v>8514700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.43</v>
+        <v>5.87</v>
       </c>
       <c r="H30" t="n">
-        <v>56.04</v>
+        <v>53.98</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1809,10 +1825,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.321</v>
+        <v>0.094</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.337</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,39 +1841,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>5.1</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7612700</v>
+        <v>8510700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="n">
-        <v>32.21</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.14</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.174</v>
+        <v>4.862</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.21</v>
+        <v>4.581</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.026</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7550900</v>
+        <v>8390800</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="H32" t="n">
-        <v>27.41</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.81</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.594</v>
+        <v>0.378</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.804</v>
+        <v>0.372</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,40 +1931,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.005</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7543000</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H33" t="n">
-        <v>52.92</v>
-      </c>
+        <v>8276000</v>
+      </c>
+      <c r="G33" s="5" t="n"/>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0.367</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
     </row>
@@ -1960,40 +1967,33 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.305</v>
+        <v>0.26</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.0167</v>
+        <v>0.0196</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7411500</v>
+        <v>7938400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H34" t="n">
-        <v>71.3</v>
+        <v>0.59</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0.272</v>
-      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2005,28 +2005,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0039</v>
+        <v>0.335</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7334700</v>
+        <v>7767200</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.3</v>
+        <v>1.44</v>
       </c>
       <c r="H35" t="n">
-        <v>69.14</v>
+        <v>56.04</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.862</v>
+        <v>0.321</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4.581</v>
+        <v>0.337</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,39 +2050,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.395</v>
+        <v>0.37</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0137</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>7313600</v>
+        <v>7711700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.66</v>
+        <v>1.17</v>
       </c>
       <c r="H36" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.92</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.378</v>
+        <v>0.367</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.372</v>
+        <v>0.367</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.305</v>
+        <v>0.3</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7196400</v>
+        <v>7644800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.37</v>
+        <v>1.25</v>
       </c>
       <c r="H37" t="n">
-        <v>53.61</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.89</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.304</v>
+        <v>0.282</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.293</v>
+        <v>0.272</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,39 +2140,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.61</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6877800</v>
+        <v>7544400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1.44</v>
+        <v>0.71</v>
       </c>
       <c r="H38" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.26</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.776</v>
+        <v>0.607</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.834</v>
+        <v>0.607</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.61</v>
+        <v>0.725</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6749300</v>
+        <v>7470400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.63</v>
+        <v>1.56</v>
       </c>
       <c r="H39" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.47</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.607</v>
+        <v>0.776</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.607</v>
+        <v>0.834</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.0221</v>
+        <v>0.045</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6541500</v>
+        <v>7093000</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.42</v>
+        <v>1.51</v>
       </c>
       <c r="H40" t="n">
-        <v>45.48</v>
+        <v>30.84</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.273</v>
+        <v>0.059</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.206</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.06</v>
+        <v>0.395</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.0185</v>
+        <v>-0.0125</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>6520000</v>
+        <v>6980600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="H41" t="n">
-        <v>64.67</v>
+        <v>38.65</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.028</v>
+        <v>0.406</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.875</v>
+        <v>0.411</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.165</v>
+        <v>1.08</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>6081100</v>
+        <v>6833900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.159</v>
+        <v>1.03</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.148</v>
+        <v>0.876</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,33 +2365,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.355</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>6010800</v>
+        <v>6749000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
+        <v>0.89</v>
+      </c>
+      <c r="H43" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.317</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
     </row>
@@ -2403,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.075</v>
+        <v>0.505</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5929400</v>
+        <v>6650100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="H44" t="n">
-        <v>47.39</v>
+        <v>27.69</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2432,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.076</v>
+        <v>0.545</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.078</v>
+        <v>0.582</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2448,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5819500</v>
+        <v>6648900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.77</v>
+        <v>0.43</v>
       </c>
       <c r="H45" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.18</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.336</v>
+        <v>2.274</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.317</v>
+        <v>2.206</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2493,39 +2500,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.505</v>
+        <v>0.165</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5775500</v>
+        <v>6421800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
-        <v>27.69</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.545</v>
+        <v>0.159</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.582</v>
+        <v>0.148</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2538,40 +2545,33 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.115</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5268400</v>
+        <v>6285200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H47" t="n">
-        <v>42.17</v>
+        <v>0.21</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J47" s="2" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
     </row>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.0291</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5127000</v>
+        <v>5934400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.46</v>
+        <v>1.2</v>
       </c>
       <c r="H48" t="n">
-        <v>49.67</v>
+        <v>40.23</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.069</v>
+        <v>0.075</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.027</v>
+        <v>0.078</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2628,28 +2628,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.0302</v>
+        <v>1.27</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4983000</v>
+        <v>5576200</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>57.65</v>
+        <v>41.19</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.616</v>
+        <v>1.347</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.543</v>
+        <v>1.3</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2673,39 +2673,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.245</v>
+        <v>3.74</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0275</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4940500</v>
+        <v>5539600</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.48</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.265</v>
+        <v>3.615</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.317</v>
+        <v>2.543</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.23</v>
+        <v>1.05</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.0071</v>
+        <v>0.0194</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4564700</v>
+        <v>5475500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="H51" t="n">
-        <v>69.93000000000001</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.03</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.797</v>
+        <v>1.068</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3.325</v>
+        <v>1.027</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2763,28 +2763,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.525</v>
+        <v>0.245</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0208</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4535800</v>
+        <v>5462100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.61</v>
+        <v>0.19</v>
       </c>
       <c r="H52" t="n">
-        <v>78.16</v>
+        <v>35.11</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.436</v>
+        <v>0.265</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.418</v>
+        <v>0.317</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2808,39 +2808,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.395</v>
+        <v>2.8</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0125</v>
+        <v>-0.0345</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4496400</v>
+        <v>5071400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.55</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.406</v>
+        <v>2.712</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.411</v>
+        <v>2.544</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2853,39 +2853,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>4.23</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4449200</v>
+        <v>5045200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>5.01</v>
+        <v>0.7</v>
       </c>
       <c r="H54" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.93000000000001</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.131</v>
+        <v>3.797</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.131</v>
+        <v>3.325</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2898,28 +2898,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.82</v>
+        <v>0.27</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.0036</v>
+        <v>0.0385</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4447500</v>
+        <v>4710900</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H55" t="n">
-        <v>55.84</v>
+        <v>47.9</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.796</v>
+        <v>0.268</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.667</v>
+        <v>0.308</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2943,28 +2943,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.031</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0561</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4383600</v>
+        <v>4680000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H56" t="n">
-        <v>57.09</v>
+        <v>65.55</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.713</v>
+        <v>0.52</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.544</v>
+        <v>0.476</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2988,39 +2988,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.0198</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3902700</v>
+        <v>4566900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.62</v>
+        <v>1.62</v>
       </c>
       <c r="H57" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.16</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.521</v>
+        <v>0.436</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.532</v>
+        <v>0.418</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3033,28 +3033,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3899200</v>
+        <v>4539300</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>64.37</v>
+        <v>55.84</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.772</v>
+        <v>2.796</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.757</v>
+        <v>2.667</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3078,28 +3078,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0.0183</v>
+        <v>0.13</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3858500</v>
+        <v>4449200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="H59" t="n">
-        <v>42.97</v>
+        <v>47.54</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.157</v>
+        <v>0.131</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.154</v>
+        <v>0.131</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3123,39 +3123,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.0159</v>
+        <v>0.79</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3540200</v>
+        <v>4438800</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.2</v>
+        <v>0.71</v>
       </c>
       <c r="H60" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.565</v>
+        <v>0.772</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.461</v>
+        <v>0.757</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3168,39 +3168,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.76</v>
+        <v>0.55</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.0066</v>
+        <v>0.0377</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3532000</v>
+        <v>4299500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.54</v>
+        <v>0.28</v>
       </c>
       <c r="H61" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.34999999999999</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.769</v>
+        <v>0.5</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.771</v>
+        <v>0.419</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3213,28 +3213,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.66</v>
+        <v>0.515</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0198</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3428400</v>
+        <v>4030700</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="H62" t="n">
-        <v>41.29</v>
+        <v>47.67</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.702</v>
+        <v>0.521</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.818</v>
+        <v>0.532</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3258,28 +3258,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0367</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3395500</v>
+        <v>4024600</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H63" t="n">
-        <v>54.88</v>
+        <v>45.88</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.157</v>
+        <v>1.159</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.108</v>
+        <v>1.154</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3303,28 +3303,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.0239</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3303300</v>
+        <v>4023000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.84</v>
+        <v>0.23</v>
       </c>
       <c r="H64" t="n">
-        <v>39.41</v>
+        <v>51.72</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.142</v>
+        <v>2.567</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.15</v>
+        <v>2.461</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3348,28 +3348,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.545</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3287500</v>
+        <v>3831500</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>63.64</v>
+        <v>52.35</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.499</v>
+        <v>0.68</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.418</v>
+        <v>0.667</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3393,39 +3393,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3286100</v>
+        <v>3716200</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="H66" t="n">
-        <v>37.56</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.119</v>
+        <v>1.156</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.125</v>
+        <v>1.108</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3438,28 +3438,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.5</v>
+        <v>0.76</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0066</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3281800</v>
+        <v>3668300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>58.51</v>
+        <v>44.45</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.45</v>
+        <v>0.769</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.313</v>
+        <v>0.771</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3483,28 +3483,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.375</v>
+        <v>7.46</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0507</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3244300</v>
+        <v>3609000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>72.66</v>
+        <v>68.36</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.338</v>
+        <v>6.76</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.314</v>
+        <v>6.584</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3528,39 +3528,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.115</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3237300</v>
+        <v>3595400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.4</v>
+        <v>1.09</v>
       </c>
       <c r="H69" t="n">
-        <v>39</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.56</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.192</v>
+        <v>0.119</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.197</v>
+        <v>0.125</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3573,28 +3573,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>7.44</v>
+        <v>0.6</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0.0479</v>
+        <v>0.0169</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3205800</v>
+        <v>3565100</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.89</v>
+        <v>1.28</v>
       </c>
       <c r="H70" t="n">
-        <v>68.06999999999999</v>
+        <v>57.93</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6.759</v>
+        <v>0.573</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>6.583</v>
+        <v>0.576</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3618,28 +3618,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>-0.0048</v>
+        <v>1.65</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3001400</v>
+        <v>3549300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="H71" t="n">
-        <v>43.4</v>
+        <v>39.86</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.108</v>
+        <v>1.701</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.071</v>
+        <v>1.818</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3663,33 +3663,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0105</v>
+        <v>0.375</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2921900</v>
+        <v>3524900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
+      </c>
+      <c r="H72" t="n">
+        <v>72.66</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
+      <c r="J72" s="2" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.314</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3701,39 +3708,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10.36</v>
+        <v>2.5</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.036</v>
+        <v>0.0331</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2892300</v>
+        <v>3516300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.89</v>
+        <v>0.23</v>
       </c>
       <c r="H73" t="n">
-        <v>71.63</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.51</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9.715</v>
+        <v>2.45</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>9.241</v>
+        <v>2.313</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3746,28 +3753,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.0175</v>
+        <v>0.18</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2887200</v>
+        <v>3360100</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H74" t="n">
-        <v>41.48</v>
+        <v>39</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3775,10 +3782,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.295</v>
+        <v>0.192</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.31</v>
+        <v>0.197</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3791,39 +3798,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.0171</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.0463</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2834900</v>
+        <v>3355200</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.89</v>
+        <v>1.77</v>
       </c>
       <c r="H75" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.71</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>5.613</v>
+        <v>0.513</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>5.737</v>
+        <v>0.424</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3836,39 +3843,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.26</v>
+        <v>0.135</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2781100</v>
+        <v>3303300</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.27</v>
+        <v>0.84</v>
       </c>
       <c r="H76" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.41</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.267</v>
+        <v>0.142</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.308</v>
+        <v>0.15</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3881,39 +3888,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0.028</v>
+        <v>0.28</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2723700</v>
+        <v>3241300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H77" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.72</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.519</v>
+        <v>0.294</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.475</v>
+        <v>0.31</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3926,28 +3933,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.79</v>
+        <v>5.21</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0095</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2709700</v>
+        <v>3234500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H78" t="n">
-        <v>49.68</v>
+        <v>37.41</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3955,10 +3962,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.806</v>
+        <v>5.617</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.736</v>
+        <v>5.738</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3971,39 +3978,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>-0.0161</v>
+        <v>2.07</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2675500</v>
+        <v>3226100</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H79" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.68</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.29</v>
+        <v>2.109</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.278</v>
+        <v>2.071</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4016,39 +4023,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.26</v>
+        <v>10.34</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.04</v>
+        <v>0.034</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2663800</v>
+        <v>3223000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>64.91</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.33</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.236</v>
+        <v>9.712999999999999</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.213</v>
+        <v>9.24</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4061,39 +4068,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0176</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KRONO</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.13</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2615200</v>
+        <v>3171000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1.38</v>
+        <v>0.59</v>
       </c>
       <c r="H81" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.75</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.513</v>
+        <v>0.137</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.424</v>
+        <v>0.129</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4106,39 +4113,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>3.8</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0306</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2610100</v>
+        <v>3124400</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H82" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.612</v>
+        <v>3.801</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.594</v>
+        <v>3.477</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4151,39 +4158,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.425</v>
+        <v>0.255</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.0366</v>
+        <v>0.02</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2581000</v>
+        <v>3051700</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="H83" t="n">
-        <v>56.26</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.2</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.407</v>
+        <v>0.236</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.405</v>
+        <v>0.212</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4196,28 +4203,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0</v>
+        <v>7.19</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2551600</v>
+        <v>3039900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="H84" t="n">
-        <v>41.4</v>
+        <v>30.96</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4225,10 +4232,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.797</v>
+        <v>7.561</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.806</v>
+        <v>7.793</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4241,28 +4248,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.86</v>
+        <v>0.3</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0211</v>
+        <v>-0.0164</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2519500</v>
+        <v>2974900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="H85" t="n">
-        <v>35.1</v>
+        <v>45.59</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4270,10 +4277,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.932</v>
+        <v>0.305</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2.055</v>
+        <v>0.297</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4286,28 +4293,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2496400</v>
+        <v>2936900</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H86" t="n">
-        <v>57.93</v>
+        <v>65.37</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
@@ -4315,10 +4322,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.573</v>
+        <v>0.612</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.576</v>
+        <v>0.594</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4331,40 +4338,33 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3.79</v>
+        <v>0.47</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>-0.0332</v>
+        <v>-0.0105</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2484300</v>
+        <v>2926900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H87" t="n">
-        <v>53.03</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>3.476</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
     </row>
@@ -4376,28 +4376,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0.015</v>
+        <v>0.305</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2476700</v>
+        <v>2895900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="H88" t="n">
-        <v>49.48</v>
+        <v>56.71</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.678</v>
+        <v>0.29</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.667</v>
+        <v>0.278</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4421,28 +4421,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.79</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0186</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2449400</v>
+        <v>2888400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H89" t="n">
-        <v>32.08</v>
+        <v>49.68</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>7.563</v>
+        <v>0.806</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>7.793</v>
+        <v>0.736</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4466,28 +4466,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.82</v>
+        <v>0.455</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.014</v>
+        <v>-0.0109</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2425200</v>
+        <v>2767800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="H90" t="n">
-        <v>70.08</v>
+        <v>53.14</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.441</v>
+        <v>0.451</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.887</v>
+        <v>0.417</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4511,39 +4511,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.0109</v>
+        <v>13.06</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2422800</v>
+        <v>2694300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H91" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.85</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.451</v>
+        <v>13.115</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.417</v>
+        <v>13.693</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4556,28 +4556,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.87</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2389100</v>
+        <v>2636400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="H92" t="n">
-        <v>37.28</v>
+        <v>36.11</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3.553</v>
+        <v>1.933</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3.684</v>
+        <v>2.055</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4601,39 +4601,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4.3</v>
+        <v>0.43</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>0.0412</v>
+        <v>0.0488</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2305500</v>
+        <v>2624000</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H93" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.43</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>4.465</v>
+        <v>0.407</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>4.504</v>
+        <v>0.405</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4646,28 +4646,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.77</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2298300</v>
+        <v>2615300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="H94" t="n">
-        <v>40.9</v>
+        <v>40.09</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>10.114</v>
+        <v>0.796</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>10.269</v>
+        <v>0.806</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4691,28 +4691,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>0.0141</v>
+        <v>2.86</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2285700</v>
+        <v>2582300</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="H95" t="n">
-        <v>39.92</v>
+        <v>72.17</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.371</v>
+        <v>2.445</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.388</v>
+        <v>1.888</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4736,39 +4736,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.61</v>
+        <v>3.43</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>0.0702</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2280400</v>
+        <v>2580600</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>2.97</v>
+        <v>0.45</v>
       </c>
       <c r="H96" t="n">
-        <v>84.87</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.28</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.545</v>
+        <v>3.553</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.531</v>
+        <v>3.684</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4781,28 +4781,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>-0.0069</v>
+        <v>10.04</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2214300</v>
+        <v>2485200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="H97" t="n">
-        <v>40.6</v>
+        <v>42.41</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.467</v>
+        <v>10.116</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.47</v>
+        <v>10.269</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4826,39 +4826,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>0.0109</v>
+        <v>1.43</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2201200</v>
+        <v>2467200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="H98" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.08</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>13.113</v>
+        <v>1.466</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>13.693</v>
+        <v>1.47</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4871,39 +4871,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.22</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2193600</v>
+        <v>2401600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.72</v>
+        <v>3.11</v>
       </c>
       <c r="H99" t="n">
-        <v>54.49</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.31</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.861</v>
+        <v>0.208</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.857</v>
+        <v>0.201</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4916,28 +4916,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0013</v>
+        <v>4.26</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0.0315</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2193200</v>
+        <v>2395300</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H100" t="n">
-        <v>24.81</v>
+        <v>42.51</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>7.816</v>
+        <v>4.461</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>4.503</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4961,28 +4961,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>2.8</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2119700</v>
+        <v>2375800</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H101" t="n">
-        <v>64.5</v>
+        <v>74.86</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.389</v>
+        <v>2.452</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.352</v>
+        <v>2.035</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5006,28 +5006,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>0.016</v>
+        <v>7.45</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2029400</v>
+        <v>2372300</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H102" t="n">
-        <v>36.83</v>
+        <v>24.55</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.31</v>
+        <v>7.815</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.416</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5051,39 +5051,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>-0.0182</v>
+        <v>0.36</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2020400</v>
+        <v>2358300</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="H103" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.552</v>
+        <v>0.371</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.198</v>
+        <v>0.388</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5096,28 +5096,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1.15</v>
+        <v>0.61</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2017500</v>
+        <v>2350300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.3</v>
+        <v>3.07</v>
       </c>
       <c r="H104" t="n">
-        <v>71.72</v>
+        <v>84.87</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.984</v>
+        <v>0.545</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.775</v>
+        <v>0.531</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5141,28 +5141,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>0.024</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1998900</v>
+        <v>2250600</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H105" t="n">
-        <v>45.49</v>
+        <v>39.23</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>7.782</v>
+        <v>1.311</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>7.749</v>
+        <v>1.416</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5186,39 +5186,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>1.14</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1997800</v>
+        <v>2246000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H106" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.19</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>3.233</v>
+        <v>0.983</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.439</v>
+        <v>0.775</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5231,28 +5231,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0.0036</v>
+        <v>0.42</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1781300</v>
+        <v>2219800</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H107" t="n">
-        <v>74.86</v>
+        <v>64.5</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.452</v>
+        <v>0.389</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2.035</v>
+        <v>0.352</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5276,28 +5276,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>3.06</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1768000</v>
+        <v>2204400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="H108" t="n">
-        <v>36.72</v>
+        <v>27.81</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.23</v>
+        <v>3.232</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.245</v>
+        <v>3.439</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5321,28 +5321,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.555</v>
+        <v>0.865</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0177</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1713600</v>
+        <v>2193600</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.43</v>
+        <v>0.72</v>
       </c>
       <c r="H109" t="n">
-        <v>28.18</v>
+        <v>54.49</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.579</v>
+        <v>0.861</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.585</v>
+        <v>0.857</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5366,28 +5366,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>-0.0177</v>
+        <v>4.71</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1701900</v>
+        <v>2169000</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="H110" t="n">
-        <v>26.65</v>
+        <v>35.97</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.615</v>
+        <v>4.797</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.653</v>
+        <v>4.93</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5411,28 +5411,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.255</v>
+        <v>0.555</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.0177</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1698800</v>
+        <v>2160100</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2.01</v>
+        <v>0.54</v>
       </c>
       <c r="H111" t="n">
-        <v>37.4</v>
+        <v>28.18</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.26</v>
+        <v>0.579</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.265</v>
+        <v>0.585</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5456,28 +5456,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.215</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1685400</v>
+        <v>2121800</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="H112" t="n">
-        <v>34.44</v>
+        <v>36.72</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>4.796</v>
+        <v>0.23</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>4.93</v>
+        <v>0.245</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5501,39 +5501,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>0.0101</v>
+        <v>7.68</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1643000</v>
+        <v>2114700</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.16</v>
+        <v>0.17</v>
       </c>
       <c r="H113" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.03</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.477</v>
+        <v>7.781</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.472</v>
+        <v>7.748</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5546,28 +5546,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.62</v>
+        <v>2.69</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0218</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1631600</v>
+        <v>2087400</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="H114" t="n">
-        <v>53.24</v>
+        <v>72.27</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.607</v>
+        <v>2.551</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.609</v>
+        <v>2.198</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5591,28 +5591,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.24</v>
+        <v>1.24</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0333</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1619200</v>
+        <v>2009600</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>1.06</v>
+        <v>0.34</v>
       </c>
       <c r="H115" t="n">
-        <v>65.26000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.222</v>
+        <v>1.256</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.193</v>
+        <v>1.296</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5636,28 +5636,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.22</v>
+        <v>0.505</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>0.0732</v>
+        <v>0.0202</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1613900</v>
+        <v>1936200</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="H116" t="n">
-        <v>61.31</v>
+        <v>60.44</v>
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.208</v>
+        <v>0.477</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.201</v>
+        <v>0.472</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5681,28 +5681,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.41</v>
+        <v>3.13</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.0262</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1577200</v>
+        <v>1870600</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H117" t="n">
-        <v>57.1</v>
+        <v>62.76</v>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4</v>
+        <v>2.926</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.383</v>
+        <v>2.74</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5726,28 +5726,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0163</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1570400</v>
+        <v>1833600</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="H118" t="n">
-        <v>48.44</v>
+        <v>27.52</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.242</v>
+        <v>0.615</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.159</v>
+        <v>0.653</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5771,39 +5771,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.23</v>
+        <v>0.41</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>0.025</v>
+        <v>0.0123</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1558500</v>
+        <v>1829000</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.27</v>
+        <v>0.77</v>
       </c>
       <c r="H119" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.1</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.255</v>
+        <v>0.4</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.295</v>
+        <v>0.383</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5816,28 +5816,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>1785600</v>
+      </c>
+      <c r="G120" s="5" t="n">
         <v>0.64</v>
       </c>
-      <c r="E120" s="8" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="F120" s="4" t="n">
-        <v>1528200</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.48</v>
-      </c>
       <c r="H120" t="n">
-        <v>59.82</v>
+        <v>29.57</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.635</v>
+        <v>1.346</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.601</v>
+        <v>1.317</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5861,39 +5861,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>0.0039</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1524300</v>
+        <v>1774500</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="H121" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.53</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2.563</v>
+        <v>1.244</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.548</v>
+        <v>1.16</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5906,28 +5906,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.65</v>
+        <v>2.95</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>0.0317</v>
+        <v>0.0208</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1508900</v>
+        <v>1714400</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>1.37</v>
+        <v>0.61</v>
       </c>
       <c r="H122" t="n">
-        <v>50.4</v>
+        <v>46.43</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.646</v>
+        <v>2.976</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.66</v>
+        <v>3.035</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5951,39 +5951,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1.85</v>
+        <v>0.62</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.0159</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1469400</v>
+        <v>1706900</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="H123" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.24</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.956</v>
+        <v>0.607</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1.967</v>
+        <v>0.609</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5996,28 +5996,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>0.0234</v>
+        <v>0.255</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1449400</v>
+        <v>1698800</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.24</v>
+        <v>2.01</v>
       </c>
       <c r="H124" t="n">
-        <v>49.94</v>
+        <v>37.4</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.205</v>
+        <v>0.26</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.113</v>
+        <v>0.265</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6041,39 +6041,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>0.0152</v>
+        <v>1.84</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1442900</v>
+        <v>1657600</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.19</v>
+        <v>0.24</v>
       </c>
       <c r="H125" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.8</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.633</v>
+        <v>1.955</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.606</v>
+        <v>1.966</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6086,39 +6086,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0115</v>
+        <v>0.68</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1376000</v>
+        <v>1625900</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.27</v>
+        <v>1.34</v>
       </c>
       <c r="H126" t="n">
-        <v>26.72</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.67</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>4.603</v>
+        <v>0.634</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>4.923</v>
+        <v>0.607</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6131,39 +6131,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>0.009300000000000001</v>
+        <v>2.55</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1374200</v>
+        <v>1623000</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>72.54000000000001</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.44</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.008</v>
+        <v>2.562</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.84</v>
+        <v>2.548</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6176,39 +6176,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.93</v>
+        <v>0.24</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0435</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1365600</v>
+        <v>1619200</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.51</v>
+        <v>1.06</v>
       </c>
       <c r="H128" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>2.81</v>
+        <v>0.222</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>2.725</v>
+        <v>0.193</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6221,39 +6221,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1349100</v>
+        <v>1611400</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="H129" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.43</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.237</v>
+        <v>0.76</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.243</v>
+        <v>0.742</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6266,39 +6266,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.77</v>
+        <v>2.17</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>0.0132</v>
+        <v>0.014</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1347500</v>
+        <v>1573100</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="H130" t="n">
-        <v>53.43</v>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.5</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.76</v>
+        <v>2.203</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.742</v>
+        <v>2.113</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6311,39 +6311,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1343500</v>
+        <v>1563200</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="H131" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.82</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.445</v>
+        <v>0.635</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.44</v>
+        <v>0.601</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6356,28 +6356,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0.0165</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1281600</v>
+        <v>1548400</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.18</v>
+        <v>0.61</v>
       </c>
       <c r="H132" t="n">
-        <v>60.86</v>
+        <v>58.94</v>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
@@ -6385,10 +6385,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.183</v>
+        <v>1.096</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1.196</v>
+        <v>1.12</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6401,28 +6401,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.265</v>
+        <v>0.645</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>0.1042</v>
+        <v>0.0238</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1275700</v>
+        <v>1533000</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.16</v>
+        <v>1.39</v>
       </c>
       <c r="H133" t="n">
-        <v>53.45</v>
+        <v>49.29</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.263</v>
+        <v>0.646</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.225</v>
+        <v>0.66</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6446,28 +6446,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>-0.0049</v>
+        <v>1.08</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1273200</v>
+        <v>1493700</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H134" t="n">
-        <v>40.49</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.054</v>
+        <v>1.008</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.095</v>
+        <v>0.84</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6491,28 +6491,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.625</v>
+        <v>2.95</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>0.0246</v>
+        <v>0.0461</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1232700</v>
+        <v>1493600</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H135" t="n">
-        <v>46.91</v>
+        <v>59.82</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.63</v>
+        <v>2.812</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.637</v>
+        <v>2.725</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6536,39 +6536,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>3.09</v>
+        <v>1.72</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>0.0131</v>
+        <v>0.0118</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1208700</v>
+        <v>1467800</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="H136" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.14</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.922</v>
+        <v>1.754</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.739</v>
+        <v>1.79</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6581,39 +6581,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>0.0213</v>
+        <v>4.3</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1207300</v>
+        <v>1466300</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.83</v>
+        <v>0.29</v>
       </c>
       <c r="H137" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.72</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.223</v>
+        <v>4.603</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.203</v>
+        <v>4.923</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6626,39 +6626,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>0.0463</v>
+        <v>2.03</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1201100</v>
+        <v>1447000</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H138" t="n">
-        <v>56.07</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.23</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.095</v>
+        <v>2.055</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.12</v>
+        <v>2.095</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6671,28 +6671,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1158900</v>
+        <v>1401800</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.51</v>
+        <v>1.29</v>
       </c>
       <c r="H139" t="n">
-        <v>49.23</v>
+        <v>62.54</v>
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.295</v>
+        <v>1.184</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.296</v>
+        <v>1.196</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6716,39 +6716,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.465</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1103200</v>
+        <v>1384600</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="H140" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.92</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.859</v>
+        <v>0.445</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1.948</v>
+        <v>0.44</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6761,28 +6761,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>-0.024</v>
+        <v>0.225</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1073900</v>
+        <v>1363100</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="H141" t="n">
-        <v>31.16</v>
+        <v>39.48</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.348</v>
+        <v>0.237</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1.318</v>
+        <v>0.243</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6806,39 +6806,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.26</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1066100</v>
+        <v>1327300</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H142" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.894</v>
+        <v>0.262</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.854</v>
+        <v>0.225</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6851,39 +6851,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>-0.0366</v>
+        <v>0.22</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1057900</v>
+        <v>1292800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H143" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.75</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.943</v>
+        <v>0.196</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>2.007</v>
+        <v>0.162</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6896,39 +6896,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E144" s="8" t="n">
-        <v>0.0282</v>
+        <v>1.71</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1031000</v>
+        <v>1263400</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1.97</v>
+        <v>0.92</v>
       </c>
       <c r="H144" t="n">
-        <v>82.06999999999999</v>
-      </c>
-      <c r="I144" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.21</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.646</v>
+        <v>1.859</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>1.563</v>
+        <v>1.948</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6941,28 +6941,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>0.0149</v>
+        <v>0.0164</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1024800</v>
+        <v>1249000</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.26</v>
+        <v>0.53</v>
       </c>
       <c r="H145" t="n">
-        <v>51.68</v>
+        <v>44.55</v>
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.339</v>
+        <v>0.629</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.334</v>
+        <v>0.637</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6986,39 +6986,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>0.0059</v>
+        <v>0.0169</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1023200</v>
+        <v>1242900</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.19</v>
+        <v>2.37</v>
       </c>
       <c r="H146" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.92</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.754</v>
+        <v>1.644</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>1.789</v>
+        <v>1.563</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7031,28 +7031,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.0134</v>
+        <v>-0.0366</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>961000</v>
+        <v>1209400</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="H147" t="n">
-        <v>31.03</v>
+        <v>31.44</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.534</v>
+        <v>1.943</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1.649</v>
+        <v>2.007</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7076,39 +7076,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.91</v>
+        <v>0.24</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.0213</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>960900</v>
+        <v>1207800</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.34</v>
+        <v>0.83</v>
       </c>
       <c r="H148" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.31</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>2.972</v>
+        <v>0.223</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>3.034</v>
+        <v>0.203</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7121,28 +7121,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>7.87</v>
+        <v>0.245</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>0.0025</v>
+        <v>0.0208</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>905900</v>
+        <v>1188300</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H149" t="n">
-        <v>50.27</v>
+        <v>48.99</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>7.881</v>
+        <v>0.245</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>7.822</v>
+        <v>0.251</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7166,28 +7166,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>6.42</v>
+        <v>6.09</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>904300</v>
+        <v>1184800</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="H150" t="n">
-        <v>29.72</v>
+        <v>37.29</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>6.623</v>
+        <v>6.241</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>6.868</v>
+        <v>6.451</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7211,28 +7211,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>-0.0204</v>
+        <v>0.295</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>849500</v>
+        <v>1158900</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="H151" t="n">
-        <v>58.53</v>
+        <v>49.23</v>
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.698</v>
+        <v>0.295</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.627</v>
+        <v>0.296</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7256,39 +7256,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.965</v>
+        <v>0.9</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>-0.0052</v>
+        <v>-0.011</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>843200</v>
+        <v>1119600</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H152" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.023</v>
+        <v>0.894</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.076</v>
+        <v>0.854</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7301,28 +7301,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.46</v>
+        <v>6.77</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.003</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>839400</v>
+        <v>1107100</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H153" t="n">
-        <v>45.53</v>
+        <v>50.57</v>
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.47</v>
+        <v>6.759</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.51</v>
+        <v>6.837</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7346,39 +7346,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>-0.0091</v>
+        <v>0.775</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>0.0403</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>838300</v>
+        <v>1104500</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H154" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.15000000000001</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.721</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.59</v>
+        <v>0.713</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7391,28 +7391,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2.63</v>
+        <v>0.34</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>0.0115</v>
+        <v>0.0149</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>837600</v>
+        <v>1076900</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H155" t="n">
-        <v>43.95</v>
+        <v>51.68</v>
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>2.665</v>
+        <v>0.339</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>2.834</v>
+        <v>0.334</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7436,28 +7436,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E156" s="8" t="n">
-        <v>0.0068</v>
+        <v>0.33</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>831500</v>
+        <v>1036200</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H156" t="n">
-        <v>49.62</v>
+        <v>47.79</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.732</v>
+        <v>0.335</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7481,28 +7481,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E157" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.72</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>812400</v>
+        <v>1025200</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H157" t="n">
-        <v>69.95</v>
+        <v>58.53</v>
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.72</v>
+        <v>0.698</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.713</v>
+        <v>0.627</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7526,39 +7526,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0090</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>ELSOFT</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>-0.0052</v>
+        <v>0.28</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>0.0566</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>807100</v>
+        <v>1017900</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.2</v>
+        <v>3.93</v>
       </c>
       <c r="H158" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.96</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.986</v>
+        <v>0.262</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.037</v>
+        <v>0.264</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7571,39 +7571,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>6.75</v>
+        <v>1.39</v>
       </c>
       <c r="E159" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>804900</v>
+        <v>1000000</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="H159" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I159" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>6.757</v>
+        <v>1.367</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>6.836</v>
+        <v>1.331</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7616,39 +7616,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E160" s="8" t="n">
-        <v>0.0201</v>
+        <v>1.47</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>793900</v>
+        <v>997000</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="H160" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="I160" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.03</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>5.619</v>
+        <v>1.534</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>6.024</v>
+        <v>1.649</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7661,28 +7661,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.9</v>
+        <v>7.85</v>
       </c>
       <c r="E161" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>777300</v>
+        <v>991400</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H161" t="n">
-        <v>38.05</v>
+        <v>49.2</v>
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.92</v>
+        <v>7.879</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.968</v>
+        <v>7.822</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7706,39 +7706,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>-0.0066</v>
+        <v>5.6</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>773500</v>
+        <v>964700</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H162" t="n">
-        <v>54.47</v>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2.96</v>
+        <v>5.62</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2.911</v>
+        <v>6.024</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7751,39 +7751,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.51</v>
+        <v>0.905</v>
       </c>
       <c r="E163" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>766200</v>
+        <v>964000</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1.01</v>
+        <v>0.53</v>
       </c>
       <c r="H163" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.05</v>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.565</v>
+        <v>0.907</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.513</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7796,39 +7796,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.995</v>
+        <v>6.4</v>
       </c>
       <c r="E164" s="8" t="n">
-        <v>0.0258</v>
+        <v>0.0016</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>745300</v>
+        <v>938600</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H164" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.54</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.021</v>
+        <v>6.621</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1.02</v>
+        <v>6.868</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7841,28 +7841,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>-0.008</v>
+        <v>0.735</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>740000</v>
+        <v>931800</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="H165" t="n">
-        <v>36.04</v>
+        <v>49.62</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.629</v>
+        <v>0.732</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.636</v>
+        <v>0.75</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7886,39 +7886,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E166" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.66</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>735800</v>
+        <v>928600</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="H166" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.088</v>
+        <v>0.596</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1.139</v>
+        <v>0.509</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7931,39 +7931,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E167" s="8" t="n">
-        <v>0.006</v>
+        <v>0.97</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>724200</v>
+        <v>908900</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H167" t="n">
-        <v>52.72</v>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.84</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>4.986</v>
+        <v>1.024</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>5.045</v>
+        <v>1.076</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7976,39 +7976,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="E168" s="8" t="n">
-        <v>0.008</v>
+        <v>0.0115</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>694900</v>
+        <v>906500</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H168" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.95</v>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>2.631</v>
+        <v>2.665</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>2.762</v>
+        <v>2.834</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8021,28 +8021,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>-0.011</v>
+        <v>5.04</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>0.008</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>669700</v>
+        <v>871400</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="H169" t="n">
-        <v>51.2</v>
+        <v>53.31</v>
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.906</v>
+        <v>4.987</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>5.045</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8066,39 +8066,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>6.1</v>
+        <v>1.46</v>
       </c>
       <c r="E170" s="8" t="n">
-        <v>0.0083</v>
+        <v>0.0069</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>661900</v>
+        <v>866500</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="H170" t="n">
-        <v>38.07</v>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>6.242</v>
+        <v>1.47</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>6.451</v>
+        <v>1.51</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8111,39 +8111,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.17</v>
+        <v>3</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>658600</v>
+        <v>866100</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.16</v>
+        <v>0.74</v>
       </c>
       <c r="H171" t="n">
-        <v>61.09</v>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.58</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.129</v>
+        <v>2.961</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1.035</v>
+        <v>2.911</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8156,28 +8156,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.63</v>
+        <v>0.545</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>-0.0181</v>
+        <v>-0.0091</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>656600</v>
+        <v>864700</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="H172" t="n">
-        <v>33.52</v>
+        <v>36.47</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>1.725</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>1.839</v>
+        <v>0.59</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8201,39 +8201,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>635100</v>
+        <v>861200</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
       <c r="H173" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.21</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.634</v>
+        <v>0.986</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0.629</v>
+        <v>1.037</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8246,39 +8246,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>-0.0149</v>
+        <v>4.69</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>0.0043</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>627400</v>
+        <v>828400</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="H174" t="n">
-        <v>71.23</v>
-      </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.31</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.596</v>
+        <v>4.725</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0.509</v>
+        <v>4.607</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8291,39 +8291,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0.65</v>
+        <v>1.52</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.0066</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>600900</v>
+        <v>794200</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H175" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.12</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.627</v>
+        <v>1.566</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0.59</v>
+        <v>1.513</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8336,28 +8336,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="E176" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>600500</v>
+        <v>793400</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="H176" t="n">
-        <v>65.81999999999999</v>
+        <v>23.51</v>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.989</v>
+        <v>1.087</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.983</v>
+        <v>1.139</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8381,39 +8381,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E177" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.9</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>598800</v>
+        <v>790600</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1.46</v>
+        <v>0.25</v>
       </c>
       <c r="H177" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.05</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.501</v>
+        <v>0.92</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>0.499</v>
+        <v>0.968</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8426,28 +8426,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E178" s="8" t="n">
-        <v>0.0189</v>
+        <v>2.51</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>588400</v>
+        <v>788500</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
       <c r="H178" t="n">
-        <v>33.38</v>
+        <v>28.3</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1.127</v>
+        <v>2.629</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1.171</v>
+        <v>2.761</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8471,39 +8471,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E179" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>583600</v>
+        <v>785900</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="H179" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="I179" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.964</v>
+        <v>1.021</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>1.001</v>
+        <v>1.021</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8516,28 +8516,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.35</v>
+        <v>0.62</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>-0.0146</v>
+        <v>-0.008</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>566200</v>
+        <v>740000</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="H180" t="n">
-        <v>53.24</v>
+        <v>36.04</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1.352</v>
+        <v>0.629</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1.19</v>
+        <v>0.636</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8561,28 +8561,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>-0.0217</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>561300</v>
+        <v>739000</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H181" t="n">
-        <v>78.63</v>
+        <v>61.09</v>
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>1.144</v>
+        <v>1.129</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.035</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8606,28 +8606,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.15</v>
+        <v>1.82</v>
       </c>
       <c r="E182" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>561000</v>
+        <v>691800</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H182" t="n">
-        <v>59.13</v>
+        <v>50.15</v>
       </c>
       <c r="I182" s="9" t="inlineStr">
         <is>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1.1</v>
+        <v>1.813</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>1.071</v>
+        <v>1.839</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8651,28 +8651,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>539700</v>
+        <v>681700</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="H183" t="n">
-        <v>65.26000000000001</v>
+        <v>32.65</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>1.367</v>
+        <v>1.724</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>1.331</v>
+        <v>1.839</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8696,39 +8696,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>4.69</v>
+        <v>0.78</v>
       </c>
       <c r="E184" s="8" t="n">
-        <v>0.0043</v>
+        <v>0.0196</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>533000</v>
+        <v>666200</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="H184" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.67</v>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>4.725</v>
+        <v>0.773</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>4.607</v>
+        <v>0.766</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8741,28 +8741,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>KKB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E185" s="8" t="n">
-        <v>0.075</v>
+        <v>0.635</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>523200</v>
+        <v>635100</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>14.66</v>
+        <v>0.46</v>
       </c>
       <c r="H185" t="n">
-        <v>72.27</v>
+        <v>52.66</v>
       </c>
       <c r="I185" s="9" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.139</v>
+        <v>0.634</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1.09</v>
+        <v>0.629</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8786,28 +8786,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>-0.0229</v>
+        <v>0.65</v>
+      </c>
+      <c r="E186" s="8" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>505300</v>
+        <v>618500</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H186" t="n">
-        <v>62.19</v>
+        <v>58.46</v>
       </c>
       <c r="I186" s="9" t="inlineStr">
         <is>
@@ -8815,16 +8815,691 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>1.995</v>
+        <v>0.627</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>1.913</v>
+        <v>0.59</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>616500</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H187" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>616100</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H188" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>MKH</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H189" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E190" s="8" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>598800</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H190" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>597100</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H191" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="I191" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>595800</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H192" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>588800</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H193" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>578400</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H194" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="I194" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>576500</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H195" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="I195" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>7.863</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>8.048</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>570600</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H196" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>4.392</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H197" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="I197" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="7" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E198" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>545900</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H198" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="I198" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="7" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>537200</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="H199" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="I199" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="7" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E200" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="F200" s="4" t="n">
+        <v>537000</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H200" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="I200" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="7" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v>516600</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H201" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I201" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>4.494</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M186"/>
+  <autoFilter ref="A1:M201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>